--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.9 → 53.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,8 +750,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1431.8</v>
+        <v>1429.6</v>
       </c>
       <c r="D2">
-        <v>0.76</v>
+        <v>-0.15</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,25 +895,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.14</v>
+        <v>-2.29</v>
       </c>
       <c r="H2">
-        <v>18.73</v>
+        <v>18.55</v>
       </c>
       <c r="I2">
-        <v>-1.93</v>
+        <v>-1.72</v>
       </c>
       <c r="J2">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="K2">
-        <v>15.44</v>
+        <v>15.7</v>
       </c>
       <c r="L2">
-        <v>-1.39</v>
+        <v>-0.26</v>
       </c>
       <c r="M2">
-        <v>16.06</v>
+        <v>16.27</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -951,19 +922,19 @@
         <v>64</v>
       </c>
       <c r="P2">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="Q2">
-        <v>1438.83</v>
+        <v>1439.92</v>
       </c>
       <c r="R2">
-        <v>1379.64</v>
+        <v>1383.44</v>
       </c>
       <c r="S2">
-        <v>1349.7</v>
+        <v>1349.94</v>
       </c>
       <c r="T2">
-        <v>6.08</v>
+        <v>5.9</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +949,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.12</v>
+        <v>52.38</v>
       </c>
       <c r="Z2">
-        <v>15.41</v>
+        <v>13.53</v>
       </c>
       <c r="AA2">
-        <v>20.54</v>
+        <v>19.14</v>
       </c>
       <c r="AB2">
-        <v>-5.14</v>
+        <v>-5.61</v>
       </c>
       <c r="AC2">
-        <v>16.98</v>
+        <v>11.88</v>
       </c>
       <c r="AD2">
-        <v>19.81</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>24.62</v>
+        <v>24.42</v>
       </c>
       <c r="AF2">
-        <v>2.66</v>
+        <v>-18.74</v>
       </c>
       <c r="AG2">
-        <v>1470.38</v>
+        <v>1468.28</v>
       </c>
       <c r="AH2">
-        <v>1407.28</v>
+        <v>1411.57</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>20.47</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1648.8</v>
+        <v>1643.5</v>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,25 +1008,25 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-18.98</v>
+        <v>-19.25</v>
       </c>
       <c r="H3">
-        <v>4.12</v>
+        <v>3.79</v>
       </c>
       <c r="I3">
-        <v>-1.56</v>
+        <v>-0.08</v>
       </c>
       <c r="J3">
-        <v>-9.710000000000001</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="K3">
-        <v>-7.17</v>
+        <v>-8.56</v>
       </c>
       <c r="L3">
-        <v>-12.41</v>
+        <v>-12.9</v>
       </c>
       <c r="M3">
-        <v>3.54</v>
+        <v>3.41</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1064,19 +1035,19 @@
         <v>29</v>
       </c>
       <c r="P3">
-        <v>1654.92</v>
+        <v>1654.66</v>
       </c>
       <c r="Q3">
-        <v>1658.67</v>
+        <v>1651.44</v>
       </c>
       <c r="R3">
-        <v>1729.88</v>
+        <v>1727.79</v>
       </c>
       <c r="S3">
-        <v>1844.99</v>
+        <v>1843.24</v>
       </c>
       <c r="T3">
-        <v>-10.63</v>
+        <v>-10.84</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,34 +1062,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>44.67</v>
+        <v>43.99</v>
       </c>
       <c r="Z3">
-        <v>-25.65</v>
+        <v>-24.9</v>
       </c>
       <c r="AA3">
-        <v>-29.75</v>
+        <v>-28.78</v>
       </c>
       <c r="AB3">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AC3">
-        <v>78.39</v>
+        <v>72.2</v>
       </c>
       <c r="AD3">
-        <v>83.68000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AE3">
-        <v>51.51</v>
+        <v>49.65</v>
       </c>
       <c r="AF3">
-        <v>-59.47</v>
+        <v>-69.94</v>
       </c>
       <c r="AG3">
-        <v>1769.85</v>
+        <v>1744.52</v>
       </c>
       <c r="AH3">
-        <v>1547.49</v>
+        <v>1558.36</v>
       </c>
       <c r="AI3">
         <v>1756.21</v>
@@ -1127,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>22.1</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>499.75</v>
+        <v>501.5</v>
       </c>
       <c r="D4">
-        <v>-0.26</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,25 +1121,25 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.16</v>
+        <v>-26.9</v>
       </c>
       <c r="H4">
-        <v>8.550000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="I4">
-        <v>-4.33</v>
+        <v>-2.35</v>
       </c>
       <c r="J4">
-        <v>-2.08</v>
+        <v>-3.5</v>
       </c>
       <c r="K4">
-        <v>-7.39</v>
+        <v>-7.24</v>
       </c>
       <c r="L4">
-        <v>-17.99</v>
+        <v>-18.14</v>
       </c>
       <c r="M4">
-        <v>-5.22</v>
+        <v>-5.09</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1177,19 +1148,19 @@
         <v>27</v>
       </c>
       <c r="P4">
-        <v>507.58</v>
+        <v>505.17</v>
       </c>
       <c r="Q4">
-        <v>507.67</v>
+        <v>507.54</v>
       </c>
       <c r="R4">
-        <v>496.39</v>
+        <v>496.69</v>
       </c>
       <c r="S4">
-        <v>574.8</v>
+        <v>574.34</v>
       </c>
       <c r="T4">
-        <v>-13.06</v>
+        <v>-12.68</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>46.26</v>
+        <v>47.45</v>
       </c>
       <c r="Z4">
-        <v>1.98</v>
+        <v>1.34</v>
       </c>
       <c r="AA4">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AB4">
-        <v>-1.13</v>
+        <v>-1.41</v>
       </c>
       <c r="AC4">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>22.15</v>
+        <v>9.68</v>
       </c>
       <c r="AE4">
-        <v>12.06</v>
+        <v>11.99</v>
       </c>
       <c r="AF4">
-        <v>-56.08</v>
+        <v>-26.5</v>
       </c>
       <c r="AG4">
-        <v>523.92</v>
+        <v>523.95</v>
       </c>
       <c r="AH4">
-        <v>491.41</v>
+        <v>491.14</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.09</v>
+        <v>25.14</v>
       </c>
     </row>
   </sheetData>
@@ -1401,47 +1372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,428 +1385,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>2.18</v>
       </c>
-      <c r="E7" s="7">
+      <c r="D7" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-2.08</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-3.5</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-1.93</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-1.72</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.33</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.35</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.39</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.26</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-12.41</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-12.9</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-17.99</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-18.14</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>15.44</v>
+      </c>
+      <c r="D16" s="5">
+        <v>15.7</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.17</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-8.56</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-7.39</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-7.24</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-2.14</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.29</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-18.98</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-19.25</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-27.16</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-26.9</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1431.8</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1429.6</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1648.8</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1643.5</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>499.75</v>
+      </c>
+      <c r="D24" s="5">
+        <v>501.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>53.12</v>
+      </c>
+      <c r="D25" s="5">
+        <v>52.38</v>
+      </c>
+      <c r="E25" s="6">
         <v>-0.74</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-8.68</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>44.67</v>
+      </c>
+      <c r="D26" s="5">
+        <v>43.99</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2.11</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-2.08</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>46.26</v>
+      </c>
+      <c r="D27" s="5">
+        <v>47.45</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-18.74</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-21.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-59.47</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-69.94</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-10.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-11.61</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-12.41</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-16.35</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-17.99</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>12.21</v>
-      </c>
-      <c r="D16" s="6">
-        <v>15.44</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.39</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-19.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-18.98</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-26.97</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-27.16</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1421</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1431.8</v>
-      </c>
-      <c r="E22" s="8">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1639</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1648.8</v>
-      </c>
-      <c r="E23" s="8">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>501.05</v>
-      </c>
-      <c r="D24" s="6">
-        <v>499.75</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>49.91</v>
-      </c>
-      <c r="D25" s="6">
-        <v>53.12</v>
-      </c>
-      <c r="E25" s="8">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>43.17</v>
-      </c>
-      <c r="D26" s="6">
-        <v>44.67</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>46.99</v>
-      </c>
-      <c r="D27" s="6">
-        <v>46.26</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>16.17</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2.66</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-13.51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-76.81999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-59.47</v>
-      </c>
-      <c r="E29" s="8">
-        <v>17.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-56.3</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-56.08</v>
       </c>
-      <c r="E30" s="8">
-        <v>0.22</v>
+      <c r="D30" s="5">
+        <v>-26.5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>29.58</v>
       </c>
     </row>
   </sheetData>
@@ -1896,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>48</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>47.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2051,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1606</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0354</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0522</v>
+      <c r="A2" s="13">
+        <v>0.1627</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0341</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0509</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.5 → 50.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>50.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -750,7 +778,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -883,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1429.6</v>
+        <v>1431.7</v>
       </c>
       <c r="D2">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -895,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.29</v>
+        <v>-2.15</v>
       </c>
       <c r="H2">
-        <v>18.55</v>
+        <v>18.72</v>
       </c>
       <c r="I2">
-        <v>-1.72</v>
+        <v>-1.27</v>
       </c>
       <c r="J2">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="K2">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="L2">
-        <v>-0.26</v>
+        <v>-0.06</v>
       </c>
       <c r="M2">
-        <v>16.27</v>
+        <v>16.05</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>1438</v>
+        <v>1434.32</v>
       </c>
       <c r="Q2">
-        <v>1439.92</v>
+        <v>1440.7</v>
       </c>
       <c r="R2">
-        <v>1383.44</v>
+        <v>1387.54</v>
       </c>
       <c r="S2">
-        <v>1349.94</v>
+        <v>1350.28</v>
       </c>
       <c r="T2">
-        <v>5.9</v>
+        <v>6.03</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.38</v>
+        <v>53.05</v>
       </c>
       <c r="Z2">
-        <v>13.53</v>
+        <v>12.07</v>
       </c>
       <c r="AA2">
-        <v>19.14</v>
+        <v>17.73</v>
       </c>
       <c r="AB2">
-        <v>-5.61</v>
+        <v>-5.66</v>
       </c>
       <c r="AC2">
-        <v>11.88</v>
+        <v>18.45</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>15.77</v>
       </c>
       <c r="AE2">
-        <v>24.42</v>
+        <v>23.85</v>
       </c>
       <c r="AF2">
-        <v>-18.74</v>
+        <v>-35.54</v>
       </c>
       <c r="AG2">
-        <v>1468.28</v>
+        <v>1467.11</v>
       </c>
       <c r="AH2">
-        <v>1411.57</v>
+        <v>1414.29</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -985,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>21.82</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1643.5</v>
+        <v>1635</v>
       </c>
       <c r="D3">
-        <v>-0.32</v>
+        <v>-0.52</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1008,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-19.25</v>
+        <v>-19.66</v>
       </c>
       <c r="H3">
-        <v>3.79</v>
+        <v>3.25</v>
       </c>
       <c r="I3">
-        <v>-0.08</v>
+        <v>-2.91</v>
       </c>
       <c r="J3">
-        <v>-8.050000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="K3">
-        <v>-8.56</v>
+        <v>-11.23</v>
       </c>
       <c r="L3">
-        <v>-12.9</v>
+        <v>-12.6</v>
       </c>
       <c r="M3">
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>1654.66</v>
+        <v>1644.86</v>
       </c>
       <c r="Q3">
-        <v>1651.44</v>
+        <v>1642.46</v>
       </c>
       <c r="R3">
-        <v>1727.79</v>
+        <v>1725.56</v>
       </c>
       <c r="S3">
-        <v>1843.24</v>
+        <v>1841.56</v>
       </c>
       <c r="T3">
-        <v>-10.84</v>
+        <v>-11.22</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,34 +1091,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>43.99</v>
+        <v>42.87</v>
       </c>
       <c r="Z3">
-        <v>-24.9</v>
+        <v>-24.71</v>
       </c>
       <c r="AA3">
-        <v>-28.78</v>
+        <v>-27.96</v>
       </c>
       <c r="AB3">
-        <v>3.88</v>
+        <v>3.26</v>
       </c>
       <c r="AC3">
-        <v>72.2</v>
+        <v>62.86</v>
       </c>
       <c r="AD3">
-        <v>78.56999999999999</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AE3">
-        <v>49.65</v>
+        <v>48.15</v>
       </c>
       <c r="AF3">
-        <v>-69.94</v>
+        <v>-55.11</v>
       </c>
       <c r="AG3">
-        <v>1744.52</v>
+        <v>1695.15</v>
       </c>
       <c r="AH3">
-        <v>1558.36</v>
+        <v>1589.77</v>
       </c>
       <c r="AI3">
         <v>1756.21</v>
@@ -1098,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>20.09</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>501.5</v>
+        <v>506.4</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>0.98</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1121,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-26.9</v>
+        <v>-26.19</v>
       </c>
       <c r="H4">
-        <v>8.93</v>
+        <v>9.99</v>
       </c>
       <c r="I4">
-        <v>-2.35</v>
+        <v>-1.96</v>
       </c>
       <c r="J4">
-        <v>-3.5</v>
+        <v>0.49</v>
       </c>
       <c r="K4">
-        <v>-7.24</v>
+        <v>-6.19</v>
       </c>
       <c r="L4">
-        <v>-18.14</v>
+        <v>-17.96</v>
       </c>
       <c r="M4">
-        <v>-5.09</v>
+        <v>-5.29</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>505.17</v>
+        <v>503.14</v>
       </c>
       <c r="Q4">
-        <v>507.54</v>
+        <v>506.61</v>
       </c>
       <c r="R4">
-        <v>496.69</v>
+        <v>497.2</v>
       </c>
       <c r="S4">
-        <v>574.34</v>
+        <v>573.85</v>
       </c>
       <c r="T4">
-        <v>-12.68</v>
+        <v>-11.75</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.45</v>
+        <v>50.72</v>
       </c>
       <c r="Z4">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AA4">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AB4">
-        <v>-1.41</v>
+        <v>-1.22</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>12.88</v>
       </c>
       <c r="AD4">
-        <v>9.68</v>
+        <v>6.1</v>
       </c>
       <c r="AE4">
         <v>11.99</v>
       </c>
       <c r="AF4">
-        <v>-26.5</v>
+        <v>-39.89</v>
       </c>
       <c r="AG4">
-        <v>523.95</v>
+        <v>520.77</v>
       </c>
       <c r="AH4">
-        <v>491.14</v>
+        <v>492.45</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1211,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.14</v>
+        <v>24.29</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1372,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1385,428 +1449,462 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>2.18</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>1.43</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.75</v>
+      <c r="D7" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-8.050000000000001</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.66</v>
+      <c r="D8" s="6">
+        <v>-8.56</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-2.08</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-3.5</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.42</v>
+      <c r="D9" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.93</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.72</v>
       </c>
+      <c r="D10" s="6">
+        <v>-1.27</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-0.08</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.48</v>
+      <c r="D11" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.83</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.33</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-2.35</v>
       </c>
+      <c r="D12" s="6">
+        <v>-1.96</v>
+      </c>
       <c r="E12" s="7">
-        <v>1.98</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.39</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-0.26</v>
       </c>
+      <c r="D13" s="6">
+        <v>-0.06</v>
+      </c>
       <c r="E13" s="7">
-        <v>1.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-12.41</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-12.9</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.49</v>
+      <c r="D14" s="6">
+        <v>-12.6</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-17.99</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-18.14</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.15</v>
+      <c r="D15" s="6">
+        <v>-17.96</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.18</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>15.44</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>15.7</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.26</v>
+      <c r="D16" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-7.17</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-8.56</v>
       </c>
-      <c r="E17" s="6">
-        <v>-1.39</v>
+      <c r="D17" s="6">
+        <v>-11.23</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>-7.39</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-7.24</v>
       </c>
+      <c r="D18" s="6">
+        <v>-6.19</v>
+      </c>
       <c r="E18" s="7">
-        <v>0.15</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-2.14</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-2.29</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.15</v>
+      <c r="D19" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-18.98</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-19.25</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.27</v>
+      <c r="D20" s="6">
+        <v>-19.66</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-27.16</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-26.9</v>
       </c>
+      <c r="D21" s="6">
+        <v>-26.19</v>
+      </c>
       <c r="E21" s="7">
-        <v>0.26</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1431.8</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>1429.6</v>
       </c>
-      <c r="E22" s="6">
-        <v>-2.2</v>
+      <c r="D22" s="6">
+        <v>1431.7</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>1648.8</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>1643.5</v>
       </c>
-      <c r="E23" s="6">
-        <v>-5.3</v>
+      <c r="D23" s="6">
+        <v>1635</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>499.75</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>501.5</v>
       </c>
+      <c r="D24" s="6">
+        <v>506.4</v>
+      </c>
       <c r="E24" s="7">
-        <v>1.75</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="6">
+        <v>66</v>
+      </c>
+      <c r="D25" s="6">
+        <v>34</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>34</v>
+      </c>
+      <c r="D26" s="6">
+        <v>66</v>
+      </c>
+      <c r="E26" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>53.12</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C27" s="6">
         <v>52.38</v>
       </c>
-      <c r="E25" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D27" s="6">
+        <v>53.05</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>44.67</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C28" s="6">
         <v>43.99</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D28" s="6">
+        <v>42.87</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>46.26</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C29" s="6">
         <v>47.45</v>
       </c>
-      <c r="E27" s="7">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D29" s="6">
+        <v>50.72</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C30" s="6">
         <v>-18.74</v>
       </c>
-      <c r="E28" s="6">
-        <v>-21.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-35.54</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-16.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-59.47</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C31" s="6">
         <v>-69.94</v>
       </c>
-      <c r="E29" s="6">
-        <v>-10.47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-55.11</v>
+      </c>
+      <c r="E31" s="7">
+        <v>14.83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-56.08</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C32" s="6">
         <v>-26.5</v>
       </c>
-      <c r="E30" s="7">
-        <v>29.58</v>
+      <c r="D32" s="6">
+        <v>-39.89</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-13.39</v>
       </c>
     </row>
   </sheetData>
@@ -1832,60 +1930,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>47.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>48.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1987,25 +2085,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1627</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0341</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0509</v>
+      <c r="A2" s="14">
+        <v>0.1605</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0318</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0529</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.5 → 50.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.5</t>
-  </si>
-  <si>
-    <t>50.7</t>
+    <t>53.0 → 45.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>45.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1431.7</v>
+        <v>1406.8</v>
       </c>
       <c r="D2">
-        <v>0.15</v>
+        <v>-1.74</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.15</v>
+        <v>-3.85</v>
       </c>
       <c r="H2">
-        <v>18.72</v>
+        <v>16.66</v>
       </c>
       <c r="I2">
-        <v>-1.27</v>
+        <v>-3.48</v>
       </c>
       <c r="J2">
-        <v>1.7</v>
+        <v>-0.66</v>
       </c>
       <c r="K2">
-        <v>14.9</v>
+        <v>13.04</v>
       </c>
       <c r="L2">
-        <v>-0.06</v>
+        <v>-1.57</v>
       </c>
       <c r="M2">
-        <v>16.05</v>
+        <v>15.53</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>1434.32</v>
+        <v>1424.18</v>
       </c>
       <c r="Q2">
-        <v>1440.7</v>
+        <v>1440.13</v>
       </c>
       <c r="R2">
-        <v>1387.54</v>
+        <v>1390.83</v>
       </c>
       <c r="S2">
-        <v>1350.28</v>
+        <v>1350.42</v>
       </c>
       <c r="T2">
-        <v>6.03</v>
+        <v>4.17</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>53.05</v>
+        <v>44.98</v>
       </c>
       <c r="Z2">
-        <v>12.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA2">
-        <v>17.73</v>
+        <v>15.94</v>
       </c>
       <c r="AB2">
-        <v>-5.66</v>
+        <v>-7.14</v>
       </c>
       <c r="AC2">
-        <v>18.45</v>
+        <v>11.74</v>
       </c>
       <c r="AD2">
-        <v>15.77</v>
+        <v>14.02</v>
       </c>
       <c r="AE2">
-        <v>23.85</v>
+        <v>23.95</v>
       </c>
       <c r="AF2">
-        <v>-35.54</v>
+        <v>-8.59</v>
       </c>
       <c r="AG2">
-        <v>1467.11</v>
+        <v>1468.96</v>
       </c>
       <c r="AH2">
-        <v>1414.29</v>
+        <v>1411.3</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>22.69</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1635</v>
+        <v>1628</v>
       </c>
       <c r="D3">
-        <v>-0.52</v>
+        <v>-0.43</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-19.66</v>
+        <v>-20.01</v>
       </c>
       <c r="H3">
-        <v>3.25</v>
+        <v>2.81</v>
       </c>
       <c r="I3">
-        <v>-2.91</v>
+        <v>-1.81</v>
       </c>
       <c r="J3">
-        <v>-8.56</v>
+        <v>-10.28</v>
       </c>
       <c r="K3">
-        <v>-11.23</v>
+        <v>-10.95</v>
       </c>
       <c r="L3">
-        <v>-12.6</v>
+        <v>-13.87</v>
       </c>
       <c r="M3">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>1644.86</v>
+        <v>1638.86</v>
       </c>
       <c r="Q3">
-        <v>1642.46</v>
+        <v>1642.67</v>
       </c>
       <c r="R3">
-        <v>1725.56</v>
+        <v>1723.3</v>
       </c>
       <c r="S3">
-        <v>1841.56</v>
+        <v>1839.76</v>
       </c>
       <c r="T3">
-        <v>-11.22</v>
+        <v>-11.51</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,34 +1091,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.87</v>
+        <v>41.92</v>
       </c>
       <c r="Z3">
-        <v>-24.71</v>
+        <v>-24.83</v>
       </c>
       <c r="AA3">
-        <v>-27.96</v>
+        <v>-27.34</v>
       </c>
       <c r="AB3">
-        <v>3.26</v>
+        <v>2.51</v>
       </c>
       <c r="AC3">
-        <v>62.86</v>
+        <v>47.79</v>
       </c>
       <c r="AD3">
-        <v>71.15000000000001</v>
+        <v>60.95</v>
       </c>
       <c r="AE3">
-        <v>48.15</v>
+        <v>45.93</v>
       </c>
       <c r="AF3">
-        <v>-55.11</v>
+        <v>-79.15000000000001</v>
       </c>
       <c r="AG3">
-        <v>1695.15</v>
+        <v>1695.08</v>
       </c>
       <c r="AH3">
-        <v>1589.77</v>
+        <v>1590.26</v>
       </c>
       <c r="AI3">
         <v>1756.21</v>
@@ -1127,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.6</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>506.4</v>
+        <v>507</v>
       </c>
       <c r="D4">
-        <v>0.98</v>
+        <v>0.12</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-26.19</v>
+        <v>-26.1</v>
       </c>
       <c r="H4">
-        <v>9.99</v>
+        <v>10.12</v>
       </c>
       <c r="I4">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.49</v>
+        <v>-3.46</v>
       </c>
       <c r="K4">
-        <v>-6.19</v>
+        <v>-5.01</v>
       </c>
       <c r="L4">
-        <v>-17.96</v>
+        <v>-17.77</v>
       </c>
       <c r="M4">
-        <v>-5.29</v>
+        <v>-5.31</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P4">
         <v>503.14</v>
       </c>
       <c r="Q4">
-        <v>506.61</v>
+        <v>506.51</v>
       </c>
       <c r="R4">
-        <v>497.2</v>
+        <v>497.83</v>
       </c>
       <c r="S4">
-        <v>573.85</v>
+        <v>573.39</v>
       </c>
       <c r="T4">
-        <v>-11.75</v>
+        <v>-11.58</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.72</v>
+        <v>51.13</v>
       </c>
       <c r="Z4">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AA4">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AB4">
-        <v>-1.22</v>
+        <v>-1.03</v>
       </c>
       <c r="AC4">
-        <v>12.88</v>
+        <v>23.98</v>
       </c>
       <c r="AD4">
-        <v>6.1</v>
+        <v>13.19</v>
       </c>
       <c r="AE4">
-        <v>11.99</v>
+        <v>11.62</v>
       </c>
       <c r="AF4">
-        <v>-39.89</v>
+        <v>-54.49</v>
       </c>
       <c r="AG4">
-        <v>520.77</v>
+        <v>520.64</v>
       </c>
       <c r="AH4">
-        <v>492.45</v>
+        <v>492.39</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>24.29</v>
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1473,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="D7" s="6">
-        <v>1.7</v>
+        <v>-0.66</v>
       </c>
       <c r="E7" s="7">
-        <v>0.27</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-8.050000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="D8" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.51</v>
+        <v>-10.28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.5</v>
+        <v>0.49</v>
       </c>
       <c r="D9" s="6">
-        <v>0.49</v>
+        <v>-3.46</v>
       </c>
       <c r="E9" s="7">
-        <v>3.99</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.72</v>
+        <v>-1.27</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.27</v>
+        <v>-3.48</v>
       </c>
       <c r="E10" s="7">
-        <v>0.45</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.08</v>
+        <v>-2.91</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.91</v>
+        <v>-1.81</v>
       </c>
       <c r="E11" s="8">
-        <v>-2.83</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.35</v>
+        <v>-1.96</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.39</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.26</v>
+        <v>-0.06</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.06</v>
+        <v>-1.57</v>
       </c>
       <c r="E13" s="7">
-        <v>0.2</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-12.9</v>
+        <v>-12.6</v>
       </c>
       <c r="D14" s="6">
-        <v>-12.6</v>
+        <v>-13.87</v>
       </c>
       <c r="E14" s="7">
-        <v>0.3</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-18.14</v>
+        <v>-17.96</v>
       </c>
       <c r="D15" s="6">
-        <v>-17.96</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.18</v>
+        <v>-17.77</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="D16" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.8</v>
+        <v>13.04</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.56</v>
+        <v>-11.23</v>
       </c>
       <c r="D17" s="6">
-        <v>-11.23</v>
+        <v>-10.95</v>
       </c>
       <c r="E17" s="8">
-        <v>-2.67</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.24</v>
+        <v>-6.19</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.19</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.05</v>
+        <v>-5.01</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.29</v>
+        <v>-2.15</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.15</v>
+        <v>-3.85</v>
       </c>
       <c r="E19" s="7">
-        <v>0.14</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1694,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-19.25</v>
+        <v>-19.66</v>
       </c>
       <c r="D20" s="6">
-        <v>-19.66</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.41</v>
+        <v>-20.01</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1711,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-26.9</v>
+        <v>-26.19</v>
       </c>
       <c r="D21" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.71</v>
+        <v>-26.1</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1728,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>1429.6</v>
+        <v>1431.7</v>
       </c>
       <c r="D22" s="6">
-        <v>1431.7</v>
+        <v>1406.8</v>
       </c>
       <c r="E22" s="7">
-        <v>2.1</v>
+        <v>-24.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1745,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>1643.5</v>
+        <v>1635</v>
       </c>
       <c r="D23" s="6">
-        <v>1635</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-8.5</v>
+        <v>1628</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1762,149 +1762,115 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>501.5</v>
+        <v>506.4</v>
       </c>
       <c r="D24" s="6">
-        <v>506.4</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4.9</v>
+        <v>507</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>66</v>
+        <v>53.05</v>
       </c>
       <c r="D25" s="6">
-        <v>34</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-32</v>
+        <v>44.98</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-8.07</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>34</v>
+        <v>42.87</v>
       </c>
       <c r="D26" s="6">
-        <v>66</v>
+        <v>41.92</v>
       </c>
       <c r="E26" s="7">
-        <v>32</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>52.38</v>
+        <v>50.72</v>
       </c>
       <c r="D27" s="6">
-        <v>53.05</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.67</v>
+        <v>51.13</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>43.99</v>
+        <v>-35.54</v>
       </c>
       <c r="D28" s="6">
-        <v>42.87</v>
+        <v>-8.59</v>
       </c>
       <c r="E28" s="8">
-        <v>-1.12</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>47.45</v>
+        <v>-55.11</v>
       </c>
       <c r="D29" s="6">
-        <v>50.72</v>
+        <v>-79.15000000000001</v>
       </c>
       <c r="E29" s="7">
-        <v>3.27</v>
+        <v>-24.04</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-18.74</v>
+        <v>-39.89</v>
       </c>
       <c r="D30" s="6">
-        <v>-35.54</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-16.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-69.94</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-55.11</v>
-      </c>
-      <c r="E31" s="7">
-        <v>14.83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-26.5</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-39.89</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-13.39</v>
+        <v>-54.49</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-14.6</v>
       </c>
     </row>
   </sheetData>
@@ -1969,16 +1935,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>48.9</v>
+        <v>46</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.1</v>
+        <v>-4.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2097,13 +2063,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1605</v>
+        <v>0.1553</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0318</v>
+        <v>0.0309</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0529</v>
+        <v>-0.05309999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.0 → 45.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>45.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -912,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1406.8</v>
+        <v>1417</v>
       </c>
       <c r="D2">
-        <v>-1.74</v>
+        <v>0.73</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.85</v>
+        <v>-3.15</v>
       </c>
       <c r="H2">
-        <v>16.66</v>
+        <v>17.51</v>
       </c>
       <c r="I2">
-        <v>-3.48</v>
+        <v>-0.28</v>
       </c>
       <c r="J2">
-        <v>-0.66</v>
+        <v>-0.08</v>
       </c>
       <c r="K2">
-        <v>13.04</v>
+        <v>13.26</v>
       </c>
       <c r="L2">
-        <v>-1.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M2">
-        <v>15.53</v>
+        <v>15.78</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>1424.18</v>
+        <v>1423.38</v>
       </c>
       <c r="Q2">
-        <v>1440.13</v>
+        <v>1438.76</v>
       </c>
       <c r="R2">
-        <v>1390.83</v>
+        <v>1394.14</v>
       </c>
       <c r="S2">
-        <v>1350.42</v>
+        <v>1350.62</v>
       </c>
       <c r="T2">
-        <v>4.17</v>
+        <v>4.91</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +950,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.98</v>
+        <v>48.44</v>
       </c>
       <c r="Z2">
-        <v>8.800000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="AA2">
-        <v>15.94</v>
+        <v>14.14</v>
       </c>
       <c r="AB2">
-        <v>-7.14</v>
+        <v>-7.19</v>
       </c>
       <c r="AC2">
-        <v>11.74</v>
+        <v>12.09</v>
       </c>
       <c r="AD2">
-        <v>14.02</v>
+        <v>14.09</v>
       </c>
       <c r="AE2">
-        <v>23.95</v>
+        <v>23.44</v>
       </c>
       <c r="AF2">
-        <v>-8.59</v>
+        <v>-50.75</v>
       </c>
       <c r="AG2">
-        <v>1468.96</v>
+        <v>1469.3</v>
       </c>
       <c r="AH2">
-        <v>1411.3</v>
+        <v>1408.23</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.34</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D3">
-        <v>-0.43</v>
+        <v>0.12</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1009,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.01</v>
+        <v>-19.91</v>
       </c>
       <c r="H3">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="I3">
-        <v>-1.81</v>
+        <v>-0.55</v>
       </c>
       <c r="J3">
-        <v>-10.28</v>
+        <v>0.38</v>
       </c>
       <c r="K3">
-        <v>-10.95</v>
+        <v>-9.75</v>
       </c>
       <c r="L3">
-        <v>-13.87</v>
+        <v>-13.36</v>
       </c>
       <c r="M3">
-        <v>3.09</v>
+        <v>3.24</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P3">
-        <v>1638.86</v>
+        <v>1637.06</v>
       </c>
       <c r="Q3">
-        <v>1642.67</v>
+        <v>1643.56</v>
       </c>
       <c r="R3">
-        <v>1723.3</v>
+        <v>1721.25</v>
       </c>
       <c r="S3">
-        <v>1839.76</v>
+        <v>1838.02</v>
       </c>
       <c r="T3">
-        <v>-11.51</v>
+        <v>-11.32</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,34 +1063,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.92</v>
+        <v>42.31</v>
       </c>
       <c r="Z3">
-        <v>-24.83</v>
+        <v>-24.49</v>
       </c>
       <c r="AA3">
-        <v>-27.34</v>
+        <v>-26.77</v>
       </c>
       <c r="AB3">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="AC3">
-        <v>47.79</v>
+        <v>38.97</v>
       </c>
       <c r="AD3">
-        <v>60.95</v>
+        <v>49.87</v>
       </c>
       <c r="AE3">
-        <v>45.93</v>
+        <v>43.92</v>
       </c>
       <c r="AF3">
-        <v>-79.15000000000001</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="AG3">
-        <v>1695.08</v>
+        <v>1694.37</v>
       </c>
       <c r="AH3">
-        <v>1590.26</v>
+        <v>1592.75</v>
       </c>
       <c r="AI3">
         <v>1756.21</v>
@@ -1127,7 +1099,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>15.35</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>507</v>
+        <v>509.15</v>
       </c>
       <c r="D4">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1122,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-26.1</v>
+        <v>-25.79</v>
       </c>
       <c r="H4">
-        <v>10.12</v>
+        <v>10.59</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="J4">
-        <v>-3.46</v>
+        <v>0.06</v>
       </c>
       <c r="K4">
-        <v>-5.01</v>
+        <v>-0.87</v>
       </c>
       <c r="L4">
-        <v>-17.77</v>
+        <v>-16.25</v>
       </c>
       <c r="M4">
-        <v>-5.31</v>
+        <v>-5.25</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>503.14</v>
+        <v>504.76</v>
       </c>
       <c r="Q4">
-        <v>506.51</v>
+        <v>507.11</v>
       </c>
       <c r="R4">
-        <v>497.83</v>
+        <v>498.51</v>
       </c>
       <c r="S4">
-        <v>573.39</v>
+        <v>572.9400000000001</v>
       </c>
       <c r="T4">
-        <v>-11.58</v>
+        <v>-11.13</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>51.13</v>
+        <v>52.62</v>
       </c>
       <c r="Z4">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AA4">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>-1.03</v>
+        <v>-0.73</v>
       </c>
       <c r="AC4">
-        <v>23.98</v>
+        <v>35.77</v>
       </c>
       <c r="AD4">
-        <v>13.19</v>
+        <v>24.21</v>
       </c>
       <c r="AE4">
-        <v>11.62</v>
+        <v>11.58</v>
       </c>
       <c r="AF4">
-        <v>-54.49</v>
+        <v>-57.41</v>
       </c>
       <c r="AG4">
-        <v>520.64</v>
+        <v>520.5700000000001</v>
       </c>
       <c r="AH4">
-        <v>492.39</v>
+        <v>493.66</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.5</v>
+        <v>20.09</v>
       </c>
     </row>
   </sheetData>
@@ -1401,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-0.66</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.36</v>
+      <c r="D7" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-10.28</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.72</v>
+      <c r="D8" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="E8" s="6">
+        <v>10.66</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-3.46</v>
       </c>
-      <c r="E9" s="7">
-        <v>-3.95</v>
+      <c r="D9" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.27</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-3.48</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.21</v>
+      <c r="D10" s="5">
+        <v>-0.28</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-1.81</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.1</v>
+      <c r="D11" s="5">
+        <v>-0.55</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>0</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.96</v>
+      <c r="D12" s="5">
+        <v>1.62</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-1.57</v>
       </c>
-      <c r="E13" s="7">
-        <v>-1.51</v>
+      <c r="D13" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.01</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-12.6</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-13.87</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.27</v>
+      <c r="D14" s="5">
+        <v>-13.36</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-17.96</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-17.77</v>
       </c>
-      <c r="E15" s="8">
-        <v>0.19</v>
+      <c r="D15" s="5">
+        <v>-16.25</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>14.9</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>13.04</v>
       </c>
-      <c r="E16" s="7">
-        <v>-1.86</v>
+      <c r="D16" s="5">
+        <v>13.26</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-11.23</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-10.95</v>
       </c>
-      <c r="E17" s="8">
-        <v>0.28</v>
+      <c r="D17" s="5">
+        <v>-9.75</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-6.19</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-5.01</v>
       </c>
-      <c r="E18" s="8">
-        <v>1.18</v>
+      <c r="D18" s="5">
+        <v>-0.87</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-3.85</v>
       </c>
-      <c r="E19" s="7">
-        <v>-1.7</v>
+      <c r="D19" s="5">
+        <v>-3.15</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-19.66</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-20.01</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.35</v>
+      <c r="D20" s="5">
+        <v>-19.91</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-26.1</v>
       </c>
-      <c r="E21" s="8">
-        <v>0.09</v>
+      <c r="D21" s="5">
+        <v>-25.79</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.31</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>1431.7</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>1406.8</v>
       </c>
-      <c r="E22" s="7">
-        <v>-24.9</v>
+      <c r="D22" s="5">
+        <v>1417</v>
+      </c>
+      <c r="E22" s="6">
+        <v>10.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>1635</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>1628</v>
       </c>
-      <c r="E23" s="7">
-        <v>-7</v>
+      <c r="D23" s="5">
+        <v>1630</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>506.4</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>507</v>
       </c>
-      <c r="E24" s="8">
-        <v>0.6</v>
+      <c r="D24" s="5">
+        <v>509.15</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>53.05</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>44.98</v>
       </c>
-      <c r="E25" s="7">
-        <v>-8.07</v>
+      <c r="D25" s="5">
+        <v>48.44</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>42.87</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>41.92</v>
       </c>
-      <c r="E26" s="7">
-        <v>-0.95</v>
+      <c r="D26" s="5">
+        <v>42.31</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.39</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>50.72</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>51.13</v>
       </c>
-      <c r="E27" s="8">
-        <v>0.41</v>
+      <c r="D27" s="5">
+        <v>52.62</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.49</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-35.54</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>-8.59</v>
       </c>
-      <c r="E28" s="8">
-        <v>26.95</v>
+      <c r="D28" s="5">
+        <v>-50.75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-42.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-55.11</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-79.15000000000001</v>
       </c>
-      <c r="E29" s="7">
-        <v>-24.04</v>
+      <c r="D29" s="5">
+        <v>-67.20999999999999</v>
+      </c>
+      <c r="E29" s="6">
+        <v>11.94</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-39.89</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-54.49</v>
       </c>
+      <c r="D30" s="5">
+        <v>-57.41</v>
+      </c>
       <c r="E30" s="7">
-        <v>-14.6</v>
+        <v>-2.92</v>
       </c>
     </row>
   </sheetData>
@@ -1896,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>46</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>47.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2051,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1553</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0309</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.05309999999999999</v>
+      <c r="A2" s="13">
+        <v>0.1578</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.03240000000000001</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0525</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1417</v>
+        <v>1415.3</v>
       </c>
       <c r="D2">
-        <v>0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.15</v>
+        <v>-3.27</v>
       </c>
       <c r="H2">
-        <v>17.51</v>
+        <v>17.36</v>
       </c>
       <c r="I2">
-        <v>-0.28</v>
+        <v>-1.15</v>
       </c>
       <c r="J2">
-        <v>-0.08</v>
+        <v>-2.01</v>
       </c>
       <c r="K2">
-        <v>13.26</v>
+        <v>14.06</v>
       </c>
       <c r="L2">
-        <v>-0.5600000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="M2">
-        <v>15.78</v>
+        <v>15.79</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +923,19 @@
         <v>60</v>
       </c>
       <c r="P2">
-        <v>1423.38</v>
+        <v>1420.08</v>
       </c>
       <c r="Q2">
-        <v>1438.76</v>
+        <v>1436.52</v>
       </c>
       <c r="R2">
-        <v>1394.14</v>
+        <v>1397.2</v>
       </c>
       <c r="S2">
-        <v>1350.62</v>
+        <v>1350.88</v>
       </c>
       <c r="T2">
-        <v>4.91</v>
+        <v>4.77</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +950,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.44</v>
+        <v>47.9</v>
       </c>
       <c r="Z2">
-        <v>6.96</v>
+        <v>5.3</v>
       </c>
       <c r="AA2">
-        <v>14.14</v>
+        <v>12.38</v>
       </c>
       <c r="AB2">
-        <v>-7.19</v>
+        <v>-7.08</v>
       </c>
       <c r="AC2">
-        <v>12.09</v>
+        <v>10.19</v>
       </c>
       <c r="AD2">
-        <v>14.09</v>
+        <v>11.34</v>
       </c>
       <c r="AE2">
-        <v>23.44</v>
+        <v>22.95</v>
       </c>
       <c r="AF2">
-        <v>-50.75</v>
+        <v>-53.94</v>
       </c>
       <c r="AG2">
-        <v>1469.3</v>
+        <v>1467.02</v>
       </c>
       <c r="AH2">
-        <v>1408.23</v>
+        <v>1406.02</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -986,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>28.34</v>
+        <v>28.92</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1630</v>
+        <v>1626.3</v>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>-0.23</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,25 +1009,25 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-19.91</v>
+        <v>-20.09</v>
       </c>
       <c r="H3">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="I3">
-        <v>-0.55</v>
+        <v>-1.36</v>
       </c>
       <c r="J3">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="K3">
-        <v>-9.75</v>
+        <v>-10.44</v>
       </c>
       <c r="L3">
-        <v>-13.36</v>
+        <v>-13.88</v>
       </c>
       <c r="M3">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1036,19 +1036,19 @@
         <v>29</v>
       </c>
       <c r="P3">
-        <v>1637.06</v>
+        <v>1632.56</v>
       </c>
       <c r="Q3">
-        <v>1643.56</v>
+        <v>1643.8</v>
       </c>
       <c r="R3">
-        <v>1721.25</v>
+        <v>1718.61</v>
       </c>
       <c r="S3">
-        <v>1838.02</v>
+        <v>1836.1</v>
       </c>
       <c r="T3">
-        <v>-11.32</v>
+        <v>-11.43</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.31</v>
+        <v>41.74</v>
       </c>
       <c r="Z3">
-        <v>-24.49</v>
+        <v>-24.24</v>
       </c>
       <c r="AA3">
-        <v>-26.77</v>
+        <v>-26.26</v>
       </c>
       <c r="AB3">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AC3">
-        <v>38.97</v>
+        <v>35.29</v>
       </c>
       <c r="AD3">
-        <v>49.87</v>
+        <v>40.68</v>
       </c>
       <c r="AE3">
-        <v>43.92</v>
+        <v>42.02</v>
       </c>
       <c r="AF3">
-        <v>-67.20999999999999</v>
+        <v>-71.06999999999999</v>
       </c>
       <c r="AG3">
-        <v>1694.37</v>
+        <v>1694.22</v>
       </c>
       <c r="AH3">
-        <v>1592.75</v>
+        <v>1593.37</v>
       </c>
       <c r="AI3">
-        <v>1756.21</v>
+        <v>1754.71</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>13.6</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1113,7 +1113,7 @@
         <v>509.15</v>
       </c>
       <c r="D4">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1128,40 +1128,40 @@
         <v>10.59</v>
       </c>
       <c r="I4">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="J4">
-        <v>0.06</v>
+        <v>2.41</v>
       </c>
       <c r="K4">
-        <v>-0.87</v>
+        <v>-2.15</v>
       </c>
       <c r="L4">
-        <v>-16.25</v>
+        <v>-16.19</v>
       </c>
       <c r="M4">
-        <v>-5.25</v>
+        <v>-5.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>504.76</v>
+        <v>506.64</v>
       </c>
       <c r="Q4">
-        <v>507.11</v>
+        <v>507.65</v>
       </c>
       <c r="R4">
-        <v>498.51</v>
+        <v>499.02</v>
       </c>
       <c r="S4">
-        <v>572.9400000000001</v>
+        <v>572.49</v>
       </c>
       <c r="T4">
-        <v>-11.13</v>
+        <v>-11.06</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1179,31 +1179,31 @@
         <v>52.62</v>
       </c>
       <c r="Z4">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB4">
-        <v>-0.73</v>
+        <v>-0.53</v>
       </c>
       <c r="AC4">
-        <v>35.77</v>
+        <v>40.09</v>
       </c>
       <c r="AD4">
-        <v>24.21</v>
+        <v>33.28</v>
       </c>
       <c r="AE4">
-        <v>11.58</v>
+        <v>11.53</v>
       </c>
       <c r="AF4">
-        <v>-57.41</v>
+        <v>-7.09</v>
       </c>
       <c r="AG4">
-        <v>520.5700000000001</v>
+        <v>520.48</v>
       </c>
       <c r="AH4">
-        <v>493.66</v>
+        <v>494.82</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1212,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>20.09</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-0.66</v>
+        <v>-0.08</v>
       </c>
       <c r="D7" s="5">
-        <v>-0.08</v>
+        <v>-2.01</v>
       </c>
       <c r="E7" s="6">
-        <v>0.58</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.28</v>
+        <v>0.38</v>
       </c>
       <c r="D8" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="E8" s="6">
-        <v>10.66</v>
+        <v>0.87</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-3.46</v>
+        <v>0.06</v>
       </c>
       <c r="D9" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.52</v>
+        <v>2.41</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-3.48</v>
+        <v>-0.28</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.28</v>
+        <v>-1.15</v>
       </c>
       <c r="E10" s="6">
-        <v>3.2</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.81</v>
+        <v>-0.55</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.55</v>
+        <v>-1.36</v>
       </c>
       <c r="E11" s="6">
-        <v>1.26</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="D12" s="5">
-        <v>1.62</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.62</v>
+        <v>1.88</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.5600000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" s="6">
-        <v>1.01</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-13.87</v>
+        <v>-13.36</v>
       </c>
       <c r="D14" s="5">
-        <v>-13.36</v>
+        <v>-13.88</v>
       </c>
       <c r="E14" s="6">
-        <v>0.51</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-17.77</v>
+        <v>-16.25</v>
       </c>
       <c r="D15" s="5">
-        <v>-16.25</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.52</v>
+        <v>-16.19</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>13.04</v>
+        <v>13.26</v>
       </c>
       <c r="D16" s="5">
-        <v>13.26</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.22</v>
+        <v>14.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-10.95</v>
+        <v>-9.75</v>
       </c>
       <c r="D17" s="5">
-        <v>-9.75</v>
+        <v>-10.44</v>
       </c>
       <c r="E17" s="6">
-        <v>1.2</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.01</v>
+        <v>-0.87</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.87</v>
+        <v>-2.15</v>
       </c>
       <c r="E18" s="6">
-        <v>4.14</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.85</v>
+        <v>-3.15</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.15</v>
+        <v>-3.27</v>
       </c>
       <c r="E19" s="6">
-        <v>0.7</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,81 +1631,81 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-20.01</v>
+        <v>-19.91</v>
       </c>
       <c r="D20" s="5">
-        <v>-19.91</v>
+        <v>-20.09</v>
       </c>
       <c r="E20" s="6">
-        <v>0.1</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="5">
-        <v>-26.1</v>
+        <v>1417</v>
       </c>
       <c r="D21" s="5">
-        <v>-25.79</v>
+        <v>1415.3</v>
       </c>
       <c r="E21" s="6">
-        <v>0.31</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1406.8</v>
+        <v>1630</v>
       </c>
       <c r="D22" s="5">
-        <v>1417</v>
+        <v>1626.3</v>
       </c>
       <c r="E22" s="6">
-        <v>10.2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C23" s="5">
-        <v>1628</v>
+        <v>48.44</v>
       </c>
       <c r="D23" s="5">
-        <v>1630</v>
+        <v>47.9</v>
       </c>
       <c r="E23" s="6">
-        <v>2</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5">
-        <v>507</v>
+        <v>42.31</v>
       </c>
       <c r="D24" s="5">
-        <v>509.15</v>
+        <v>41.74</v>
       </c>
       <c r="E24" s="6">
-        <v>2.15</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1713,16 +1713,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C25" s="5">
-        <v>44.98</v>
+        <v>-50.75</v>
       </c>
       <c r="D25" s="5">
-        <v>48.44</v>
+        <v>-53.94</v>
       </c>
       <c r="E25" s="6">
-        <v>3.46</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1730,16 +1730,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C26" s="5">
-        <v>41.92</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="D26" s="5">
-        <v>42.31</v>
+        <v>-71.06999999999999</v>
       </c>
       <c r="E26" s="6">
-        <v>0.39</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1747,67 +1747,16 @@
         <v>39</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="5">
-        <v>51.13</v>
+        <v>-57.41</v>
       </c>
       <c r="D27" s="5">
-        <v>52.62</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-8.59</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-50.75</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-42.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-79.15000000000001</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-67.20999999999999</v>
-      </c>
-      <c r="E29" s="6">
-        <v>11.94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-54.49</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-57.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.92</v>
+        <v>-7.09</v>
+      </c>
+      <c r="E27" s="7">
+        <v>50.32</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1821,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="G2" s="10">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +1949,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="B2" s="13">
-        <v>0.03240000000000001</v>
+        <v>0.0306</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0525</v>
+        <v>-0.0537</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.6 → 44.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>44.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -884,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1415.3</v>
+        <v>1412</v>
       </c>
       <c r="D2">
-        <v>-0.12</v>
+        <v>-0.23</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +924,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.27</v>
+        <v>-3.49</v>
       </c>
       <c r="H2">
-        <v>17.36</v>
+        <v>17.09</v>
       </c>
       <c r="I2">
-        <v>-1.15</v>
+        <v>-1.23</v>
       </c>
       <c r="J2">
-        <v>-2.01</v>
+        <v>-3.3</v>
       </c>
       <c r="K2">
-        <v>14.06</v>
+        <v>14.12</v>
       </c>
       <c r="L2">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="M2">
-        <v>15.79</v>
+        <v>16.16</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +951,19 @@
         <v>60</v>
       </c>
       <c r="P2">
-        <v>1420.08</v>
+        <v>1416.56</v>
       </c>
       <c r="Q2">
-        <v>1436.52</v>
+        <v>1433.97</v>
       </c>
       <c r="R2">
-        <v>1397.2</v>
+        <v>1400.44</v>
       </c>
       <c r="S2">
-        <v>1350.88</v>
+        <v>1351.09</v>
       </c>
       <c r="T2">
-        <v>4.77</v>
+        <v>4.51</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.9</v>
+        <v>46.81</v>
       </c>
       <c r="Z2">
-        <v>5.3</v>
+        <v>3.67</v>
       </c>
       <c r="AA2">
-        <v>12.38</v>
+        <v>10.63</v>
       </c>
       <c r="AB2">
-        <v>-7.08</v>
+        <v>-6.96</v>
       </c>
       <c r="AC2">
-        <v>10.19</v>
+        <v>13.1</v>
       </c>
       <c r="AD2">
-        <v>11.34</v>
+        <v>11.79</v>
       </c>
       <c r="AE2">
-        <v>22.95</v>
+        <v>22.05</v>
       </c>
       <c r="AF2">
-        <v>-53.94</v>
+        <v>-30.35</v>
       </c>
       <c r="AG2">
-        <v>1467.02</v>
+        <v>1463.64</v>
       </c>
       <c r="AH2">
-        <v>1406.02</v>
+        <v>1404.29</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -986,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>28.92</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1626.3</v>
+        <v>1623.8</v>
       </c>
       <c r="D3">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.09</v>
+        <v>-20.21</v>
       </c>
       <c r="H3">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>-1.36</v>
+        <v>-1.2</v>
       </c>
       <c r="J3">
-        <v>0.87</v>
+        <v>0.14</v>
       </c>
       <c r="K3">
-        <v>-10.44</v>
+        <v>-8.68</v>
       </c>
       <c r="L3">
-        <v>-13.88</v>
+        <v>-14.06</v>
       </c>
       <c r="M3">
-        <v>3.06</v>
+        <v>2.55</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P3">
-        <v>1632.56</v>
+        <v>1628.62</v>
       </c>
       <c r="Q3">
-        <v>1643.8</v>
+        <v>1643.79</v>
       </c>
       <c r="R3">
-        <v>1718.61</v>
+        <v>1716.32</v>
       </c>
       <c r="S3">
-        <v>1836.1</v>
+        <v>1834.1</v>
       </c>
       <c r="T3">
-        <v>-11.43</v>
+        <v>-11.47</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.74</v>
+        <v>41.34</v>
       </c>
       <c r="Z3">
-        <v>-24.24</v>
+        <v>-23.96</v>
       </c>
       <c r="AA3">
-        <v>-26.26</v>
+        <v>-25.8</v>
       </c>
       <c r="AB3">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="AC3">
-        <v>35.29</v>
+        <v>33.42</v>
       </c>
       <c r="AD3">
-        <v>40.68</v>
+        <v>35.89</v>
       </c>
       <c r="AE3">
-        <v>42.02</v>
+        <v>40.61</v>
       </c>
       <c r="AF3">
-        <v>-71.06999999999999</v>
+        <v>-27.15</v>
       </c>
       <c r="AG3">
-        <v>1694.22</v>
+        <v>1694.23</v>
       </c>
       <c r="AH3">
-        <v>1593.37</v>
+        <v>1593.34</v>
       </c>
       <c r="AI3">
-        <v>1754.71</v>
+        <v>1748.19</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>11.91</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>509.15</v>
+        <v>498.2</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-2.15</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-25.79</v>
+        <v>-27.38</v>
       </c>
       <c r="H4">
-        <v>10.59</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I4">
-        <v>1.88</v>
+        <v>-0.66</v>
       </c>
       <c r="J4">
-        <v>2.41</v>
+        <v>-0.04</v>
       </c>
       <c r="K4">
-        <v>-2.15</v>
+        <v>-1.83</v>
       </c>
       <c r="L4">
-        <v>-16.19</v>
+        <v>-18.95</v>
       </c>
       <c r="M4">
-        <v>-5.37</v>
+        <v>-5.9</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>506.64</v>
+        <v>505.98</v>
       </c>
       <c r="Q4">
-        <v>507.65</v>
+        <v>507.54</v>
       </c>
       <c r="R4">
-        <v>499.02</v>
+        <v>499.48</v>
       </c>
       <c r="S4">
-        <v>572.49</v>
+        <v>571.99</v>
       </c>
       <c r="T4">
-        <v>-11.06</v>
+        <v>-12.9</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>52.62</v>
+        <v>44.58</v>
       </c>
       <c r="Z4">
-        <v>1.34</v>
+        <v>0.51</v>
       </c>
       <c r="AA4">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AB4">
-        <v>-0.53</v>
+        <v>-1.09</v>
       </c>
       <c r="AC4">
-        <v>40.09</v>
+        <v>28.99</v>
       </c>
       <c r="AD4">
-        <v>33.28</v>
+        <v>34.95</v>
       </c>
       <c r="AE4">
-        <v>11.53</v>
+        <v>11.6</v>
       </c>
       <c r="AF4">
-        <v>-7.09</v>
+        <v>1.36</v>
       </c>
       <c r="AG4">
-        <v>520.48</v>
+        <v>520.6799999999999</v>
       </c>
       <c r="AH4">
-        <v>494.82</v>
+        <v>494.4</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1212,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>18</v>
+        <v>16.68</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1373,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,377 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <v>-0.08</v>
       </c>
-      <c r="D7" s="5">
-        <v>-2.01</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.93</v>
+      <c r="D7" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-3.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>0.38</v>
       </c>
-      <c r="D8" s="5">
-        <v>0.87</v>
+      <c r="D8" s="6">
+        <v>0.14</v>
       </c>
       <c r="E8" s="7">
-        <v>0.49</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>0.06</v>
       </c>
-      <c r="D9" s="5">
-        <v>2.41</v>
+      <c r="D9" s="6">
+        <v>-0.04</v>
       </c>
       <c r="E9" s="7">
-        <v>2.35</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="6">
         <v>-0.28</v>
       </c>
-      <c r="D10" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="6">
+        <v>-1.23</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.2</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.62</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-0.7</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-13.36</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-14.06</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-16.25</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-18.95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>13.26</v>
+      </c>
+      <c r="D16" s="6">
+        <v>14.12</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-9.75</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-8.68</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
         <v>-0.87</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-1.83</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.15</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.49</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-1.36</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-19.91</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-20.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1.62</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-25.79</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-27.38</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-0.72</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1417</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1412</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-13.36</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-13.88</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1630</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1623.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-16.25</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-16.19</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>509.15</v>
+      </c>
+      <c r="D24" s="6">
+        <v>498.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-10.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>13.26</v>
-      </c>
-      <c r="D16" s="5">
-        <v>14.06</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>48.44</v>
+      </c>
+      <c r="D25" s="6">
+        <v>46.81</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-9.75</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-10.44</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>42.31</v>
+      </c>
+      <c r="D26" s="6">
+        <v>41.34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.15</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>52.62</v>
+      </c>
+      <c r="D27" s="6">
+        <v>44.58</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.039999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.15</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-50.75</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-30.35</v>
+      </c>
+      <c r="E28" s="8">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-19.91</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-20.09</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1417</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1415.3</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1630</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1626.3</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="5">
-        <v>48.44</v>
-      </c>
-      <c r="D23" s="5">
-        <v>47.9</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="5">
-        <v>42.31</v>
-      </c>
-      <c r="D24" s="5">
-        <v>41.74</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="5">
-        <v>-50.75</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-53.94</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="C29" s="6">
+        <v>-67.20999999999999</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-27.15</v>
+      </c>
+      <c r="E29" s="8">
+        <v>40.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="5">
-        <v>-67.20999999999999</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-71.06999999999999</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="5">
+      <c r="C30" s="6">
         <v>-57.41</v>
       </c>
-      <c r="D27" s="5">
-        <v>-7.09</v>
-      </c>
-      <c r="E27" s="7">
-        <v>50.32</v>
+      <c r="D30" s="6">
+        <v>1.36</v>
+      </c>
+      <c r="E30" s="8">
+        <v>58.77</v>
       </c>
     </row>
   </sheetData>
@@ -1782,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>47.4</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>44.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-1.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1937,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1579</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0306</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0537</v>
+      <c r="A2" s="14">
+        <v>0.1616</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0255</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.059</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.6 → 44.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>44.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -389,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -912,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1412</v>
+        <v>1402</v>
       </c>
       <c r="D2">
-        <v>-0.23</v>
+        <v>-0.71</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.49</v>
+        <v>-4.18</v>
       </c>
       <c r="H2">
-        <v>17.09</v>
+        <v>16.26</v>
       </c>
       <c r="I2">
-        <v>-1.23</v>
+        <v>-2.07</v>
       </c>
       <c r="J2">
-        <v>-3.3</v>
+        <v>-4.18</v>
       </c>
       <c r="K2">
-        <v>14.12</v>
+        <v>12.81</v>
       </c>
       <c r="L2">
-        <v>-0.7</v>
+        <v>-1.32</v>
       </c>
       <c r="M2">
-        <v>16.16</v>
+        <v>16.26</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -951,19 +923,19 @@
         <v>60</v>
       </c>
       <c r="P2">
-        <v>1416.56</v>
+        <v>1410.62</v>
       </c>
       <c r="Q2">
-        <v>1433.97</v>
+        <v>1432.03</v>
       </c>
       <c r="R2">
-        <v>1400.44</v>
+        <v>1402.98</v>
       </c>
       <c r="S2">
-        <v>1351.09</v>
+        <v>1351.29</v>
       </c>
       <c r="T2">
-        <v>4.51</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +950,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>46.81</v>
+        <v>43.57</v>
       </c>
       <c r="Z2">
-        <v>3.67</v>
+        <v>1.56</v>
       </c>
       <c r="AA2">
-        <v>10.63</v>
+        <v>8.82</v>
       </c>
       <c r="AB2">
-        <v>-6.96</v>
+        <v>-7.26</v>
       </c>
       <c r="AC2">
-        <v>13.1</v>
+        <v>7.58</v>
       </c>
       <c r="AD2">
-        <v>11.79</v>
+        <v>10.29</v>
       </c>
       <c r="AE2">
-        <v>22.05</v>
+        <v>22.22</v>
       </c>
       <c r="AF2">
-        <v>-30.35</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AG2">
-        <v>1463.64</v>
+        <v>1464.75</v>
       </c>
       <c r="AH2">
-        <v>1404.29</v>
+        <v>1399.31</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.55</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1623.8</v>
+        <v>1615.7</v>
       </c>
       <c r="D3">
-        <v>-0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1009,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.21</v>
+        <v>-20.61</v>
       </c>
       <c r="H3">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="I3">
-        <v>-1.2</v>
+        <v>-1.18</v>
       </c>
       <c r="J3">
-        <v>0.14</v>
+        <v>-0.51</v>
       </c>
       <c r="K3">
-        <v>-8.68</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L3">
-        <v>-14.06</v>
+        <v>-14.93</v>
       </c>
       <c r="M3">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P3">
-        <v>1628.62</v>
+        <v>1624.76</v>
       </c>
       <c r="Q3">
-        <v>1643.79</v>
+        <v>1645.4</v>
       </c>
       <c r="R3">
-        <v>1716.32</v>
+        <v>1713.08</v>
       </c>
       <c r="S3">
-        <v>1834.1</v>
+        <v>1832.15</v>
       </c>
       <c r="T3">
-        <v>-11.47</v>
+        <v>-11.81</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.34</v>
+        <v>40</v>
       </c>
       <c r="Z3">
-        <v>-23.96</v>
+        <v>-24.12</v>
       </c>
       <c r="AA3">
-        <v>-25.8</v>
+        <v>-25.47</v>
       </c>
       <c r="AB3">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AC3">
-        <v>33.42</v>
+        <v>25.87</v>
       </c>
       <c r="AD3">
-        <v>35.89</v>
+        <v>31.53</v>
       </c>
       <c r="AE3">
-        <v>40.61</v>
+        <v>39.27</v>
       </c>
       <c r="AF3">
-        <v>-27.15</v>
+        <v>-62.36</v>
       </c>
       <c r="AG3">
-        <v>1694.23</v>
+        <v>1689.38</v>
       </c>
       <c r="AH3">
-        <v>1593.34</v>
+        <v>1601.41</v>
       </c>
       <c r="AI3">
-        <v>1748.19</v>
+        <v>1739.71</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>10.82</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>498.2</v>
+        <v>499.5</v>
       </c>
       <c r="D4">
-        <v>-2.15</v>
+        <v>0.26</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,25 +1122,25 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.38</v>
+        <v>-27.19</v>
       </c>
       <c r="H4">
-        <v>8.210000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="I4">
-        <v>-0.66</v>
+        <v>-1.36</v>
       </c>
       <c r="J4">
-        <v>-0.04</v>
+        <v>-0.2</v>
       </c>
       <c r="K4">
-        <v>-1.83</v>
+        <v>-1.74</v>
       </c>
       <c r="L4">
-        <v>-18.95</v>
+        <v>-19.32</v>
       </c>
       <c r="M4">
-        <v>-5.9</v>
+        <v>-5.45</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1177,19 +1149,19 @@
         <v>34</v>
       </c>
       <c r="P4">
-        <v>505.98</v>
+        <v>504.6</v>
       </c>
       <c r="Q4">
         <v>507.54</v>
       </c>
       <c r="R4">
-        <v>499.48</v>
+        <v>499.98</v>
       </c>
       <c r="S4">
-        <v>571.99</v>
+        <v>571.49</v>
       </c>
       <c r="T4">
-        <v>-12.9</v>
+        <v>-12.6</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,28 +1176,28 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.58</v>
+        <v>45.64</v>
       </c>
       <c r="Z4">
-        <v>0.51</v>
+        <v>-0.05</v>
       </c>
       <c r="AA4">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="AB4">
-        <v>-1.09</v>
+        <v>-1.32</v>
       </c>
       <c r="AC4">
-        <v>28.99</v>
+        <v>16.67</v>
       </c>
       <c r="AD4">
-        <v>34.95</v>
+        <v>28.58</v>
       </c>
       <c r="AE4">
-        <v>11.6</v>
+        <v>11.36</v>
       </c>
       <c r="AF4">
-        <v>1.36</v>
+        <v>-58.05</v>
       </c>
       <c r="AG4">
         <v>520.6799999999999</v>
@@ -1240,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>16.68</v>
+        <v>17.69</v>
       </c>
     </row>
   </sheetData>
@@ -1401,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-0.08</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-3.3</v>
       </c>
-      <c r="E7" s="7">
-        <v>-3.22</v>
+      <c r="D7" s="5">
+        <v>-4.18</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>0.14</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.24</v>
+      <c r="D8" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-0.04</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.1</v>
+      <c r="D9" s="5">
+        <v>-0.2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-1.23</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.95</v>
+      <c r="D10" s="5">
+        <v>-2.07</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-1.2</v>
       </c>
+      <c r="D11" s="5">
+        <v>-1.18</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.65</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>1.62</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-0.66</v>
       </c>
-      <c r="E12" s="7">
-        <v>-2.28</v>
+      <c r="D12" s="5">
+        <v>-1.36</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-0.7</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.14</v>
+      <c r="D13" s="5">
+        <v>-1.32</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-13.36</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-14.06</v>
       </c>
-      <c r="E14" s="7">
-        <v>-0.7</v>
+      <c r="D14" s="5">
+        <v>-14.93</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-16.25</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-18.95</v>
       </c>
-      <c r="E15" s="7">
-        <v>-2.7</v>
+      <c r="D15" s="5">
+        <v>-19.32</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>13.26</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>14.12</v>
       </c>
-      <c r="E16" s="8">
-        <v>0.86</v>
+      <c r="D16" s="5">
+        <v>12.81</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-8.68</v>
       </c>
-      <c r="E17" s="8">
-        <v>1.07</v>
+      <c r="D17" s="5">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-1.83</v>
       </c>
+      <c r="D18" s="5">
+        <v>-1.74</v>
+      </c>
       <c r="E18" s="7">
-        <v>-0.96</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-3.15</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-3.49</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.34</v>
+      <c r="D19" s="5">
+        <v>-4.18</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-19.91</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-20.21</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.3</v>
+      <c r="D20" s="5">
+        <v>-20.61</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-25.79</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-27.38</v>
       </c>
+      <c r="D21" s="5">
+        <v>-27.19</v>
+      </c>
       <c r="E21" s="7">
-        <v>-1.59</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>1417</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>1412</v>
       </c>
-      <c r="E22" s="7">
-        <v>-5</v>
+      <c r="D22" s="5">
+        <v>1402</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-10</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>1630</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>1623.8</v>
       </c>
-      <c r="E23" s="7">
-        <v>-6.2</v>
+      <c r="D23" s="5">
+        <v>1615.7</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-8.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>509.15</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>498.2</v>
       </c>
+      <c r="D24" s="5">
+        <v>499.5</v>
+      </c>
       <c r="E24" s="7">
-        <v>-10.95</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>48.44</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>46.81</v>
       </c>
-      <c r="E25" s="7">
-        <v>-1.63</v>
+      <c r="D25" s="5">
+        <v>43.57</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>42.31</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>41.34</v>
       </c>
-      <c r="E26" s="7">
-        <v>-0.97</v>
+      <c r="D26" s="5">
+        <v>40</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>52.62</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>44.58</v>
       </c>
+      <c r="D27" s="5">
+        <v>45.64</v>
+      </c>
       <c r="E27" s="7">
-        <v>-8.039999999999999</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-50.75</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>-30.35</v>
       </c>
-      <c r="E28" s="8">
-        <v>20.4</v>
+      <c r="D28" s="5">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E28" s="7">
+        <v>21.98</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-67.20999999999999</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-27.15</v>
       </c>
-      <c r="E29" s="8">
-        <v>40.06</v>
+      <c r="D29" s="5">
+        <v>-62.36</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-35.21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-57.41</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>1.36</v>
       </c>
-      <c r="E30" s="8">
-        <v>58.77</v>
+      <c r="D30" s="5">
+        <v>-58.05</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-59.41</v>
       </c>
     </row>
   </sheetData>
@@ -1896,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>43.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-1.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2051,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1616</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0255</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.059</v>
+      <c r="A2" s="13">
+        <v>0.1626</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0262</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0545</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +744,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -884,10 +886,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1402</v>
+        <v>1411.9</v>
       </c>
       <c r="D2">
-        <v>-0.71</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +898,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.18</v>
+        <v>-3.5</v>
       </c>
       <c r="H2">
-        <v>16.26</v>
+        <v>17.08</v>
       </c>
       <c r="I2">
-        <v>-2.07</v>
+        <v>0.36</v>
       </c>
       <c r="J2">
-        <v>-4.18</v>
+        <v>-2</v>
       </c>
       <c r="K2">
-        <v>12.81</v>
+        <v>11.67</v>
       </c>
       <c r="L2">
-        <v>-1.32</v>
+        <v>-1.08</v>
       </c>
       <c r="M2">
-        <v>16.26</v>
+        <v>16.42</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>1410.62</v>
+        <v>1411.64</v>
       </c>
       <c r="Q2">
-        <v>1432.03</v>
+        <v>1430.9</v>
       </c>
       <c r="R2">
-        <v>1402.98</v>
+        <v>1405.35</v>
       </c>
       <c r="S2">
-        <v>1351.29</v>
+        <v>1351.62</v>
       </c>
       <c r="T2">
-        <v>3.75</v>
+        <v>4.46</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +952,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>43.57</v>
+        <v>47.45</v>
       </c>
       <c r="Z2">
-        <v>1.56</v>
+        <v>0.68</v>
       </c>
       <c r="AA2">
-        <v>8.82</v>
+        <v>7.19</v>
       </c>
       <c r="AB2">
-        <v>-7.26</v>
+        <v>-6.51</v>
       </c>
       <c r="AC2">
-        <v>7.58</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AD2">
-        <v>10.29</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE2">
-        <v>22.22</v>
+        <v>21.42</v>
       </c>
       <c r="AF2">
-        <v>-8.369999999999999</v>
+        <v>-22.71</v>
       </c>
       <c r="AG2">
-        <v>1464.75</v>
+        <v>1464.79</v>
       </c>
       <c r="AH2">
-        <v>1399.31</v>
+        <v>1397</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -986,7 +988,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>32.36</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +999,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1615.7</v>
+        <v>1625</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>0.58</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1011,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.61</v>
+        <v>-20.15</v>
       </c>
       <c r="H3">
-        <v>2.03</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
-        <v>-1.18</v>
+        <v>-0.18</v>
       </c>
       <c r="J3">
-        <v>-0.51</v>
+        <v>2.62</v>
       </c>
       <c r="K3">
-        <v>-9.949999999999999</v>
+        <v>-10.68</v>
       </c>
       <c r="L3">
-        <v>-14.93</v>
+        <v>-13.79</v>
       </c>
       <c r="M3">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>1624.76</v>
+        <v>1624.16</v>
       </c>
       <c r="Q3">
-        <v>1645.4</v>
+        <v>1645.7</v>
       </c>
       <c r="R3">
-        <v>1713.08</v>
+        <v>1710.94</v>
       </c>
       <c r="S3">
-        <v>1832.15</v>
+        <v>1830.34</v>
       </c>
       <c r="T3">
-        <v>-11.81</v>
+        <v>-11.22</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,34 +1065,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40</v>
+        <v>42.32</v>
       </c>
       <c r="Z3">
-        <v>-24.12</v>
+        <v>-23.23</v>
       </c>
       <c r="AA3">
-        <v>-25.47</v>
+        <v>-25.02</v>
       </c>
       <c r="AB3">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AC3">
-        <v>25.87</v>
+        <v>23.9</v>
       </c>
       <c r="AD3">
-        <v>31.53</v>
+        <v>27.73</v>
       </c>
       <c r="AE3">
-        <v>39.27</v>
+        <v>38.91</v>
       </c>
       <c r="AF3">
-        <v>-62.36</v>
+        <v>-21.95</v>
       </c>
       <c r="AG3">
-        <v>1689.38</v>
+        <v>1689</v>
       </c>
       <c r="AH3">
-        <v>1601.41</v>
+        <v>1602.39</v>
       </c>
       <c r="AI3">
         <v>1739.71</v>
@@ -1099,7 +1101,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>10.45</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1112,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>499.5</v>
+        <v>502</v>
       </c>
       <c r="D4">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1124,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.19</v>
+        <v>-26.83</v>
       </c>
       <c r="H4">
-        <v>8.49</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I4">
-        <v>-1.36</v>
+        <v>-0.99</v>
       </c>
       <c r="J4">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K4">
-        <v>-1.74</v>
+        <v>-3.14</v>
       </c>
       <c r="L4">
-        <v>-19.32</v>
+        <v>-19.61</v>
       </c>
       <c r="M4">
-        <v>-5.45</v>
+        <v>-5.35</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>504.6</v>
+        <v>503.6</v>
       </c>
       <c r="Q4">
-        <v>507.54</v>
+        <v>507.56</v>
       </c>
       <c r="R4">
-        <v>499.98</v>
+        <v>500.7</v>
       </c>
       <c r="S4">
-        <v>571.49</v>
+        <v>571.0599999999999</v>
       </c>
       <c r="T4">
-        <v>-12.6</v>
+        <v>-12.09</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1178,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>45.64</v>
+        <v>47.72</v>
       </c>
       <c r="Z4">
-        <v>-0.05</v>
+        <v>-0.28</v>
       </c>
       <c r="AA4">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
       <c r="AB4">
-        <v>-1.32</v>
+        <v>-1.24</v>
       </c>
       <c r="AC4">
-        <v>16.67</v>
+        <v>8.58</v>
       </c>
       <c r="AD4">
-        <v>28.58</v>
+        <v>18.08</v>
       </c>
       <c r="AE4">
-        <v>11.36</v>
+        <v>11.04</v>
       </c>
       <c r="AF4">
-        <v>-58.05</v>
+        <v>-59.43</v>
       </c>
       <c r="AG4">
-        <v>520.6799999999999</v>
+        <v>520.65</v>
       </c>
       <c r="AH4">
-        <v>494.4</v>
+        <v>494.47</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1212,7 +1214,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>17.69</v>
+        <v>15.87</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1412,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.3</v>
+        <v>-4.18</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.18</v>
+        <v>-2</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.88</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1429,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>0.14</v>
+        <v>-0.51</v>
       </c>
       <c r="D8" s="5">
-        <v>-0.51</v>
+        <v>2.62</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.65</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1446,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-0.04</v>
+        <v>-0.2</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.16</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1463,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.23</v>
+        <v>-2.07</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.07</v>
+        <v>0.36</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.84</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1480,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.2</v>
+        <v>-1.18</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.02</v>
+        <v>-0.18</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1497,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.66</v>
+        <v>-1.36</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.36</v>
+        <v>-0.99</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.7</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1514,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.7</v>
+        <v>-1.32</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.32</v>
+        <v>-1.08</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.62</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1531,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>-14.06</v>
+        <v>-14.93</v>
       </c>
       <c r="D14" s="5">
-        <v>-14.93</v>
+        <v>-13.79</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.87</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1548,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-18.95</v>
+        <v>-19.32</v>
       </c>
       <c r="D15" s="5">
-        <v>-19.32</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.37</v>
+        <v>-19.61</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1565,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>14.12</v>
+        <v>12.81</v>
       </c>
       <c r="D16" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.31</v>
+        <v>11.67</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1582,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>-8.68</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.27</v>
+        <v>-10.68</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1599,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-1.83</v>
+        <v>-1.74</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.74</v>
+        <v>-3.14</v>
       </c>
       <c r="E18" s="7">
-        <v>0.09</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1616,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.49</v>
+        <v>-4.18</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.18</v>
+        <v>-3.5</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.6899999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1633,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-20.21</v>
+        <v>-20.61</v>
       </c>
       <c r="D20" s="5">
-        <v>-20.61</v>
+        <v>-20.15</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1650,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.38</v>
+        <v>-27.19</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.19</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.19</v>
+        <v>-26.83</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.36</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1667,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>1412</v>
+        <v>1402</v>
       </c>
       <c r="D22" s="5">
-        <v>1402</v>
+        <v>1411.9</v>
       </c>
       <c r="E22" s="6">
-        <v>-10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1684,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>1623.8</v>
+        <v>1615.7</v>
       </c>
       <c r="D23" s="5">
-        <v>1615.7</v>
+        <v>1625</v>
       </c>
       <c r="E23" s="6">
-        <v>-8.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1701,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>498.2</v>
+        <v>499.5</v>
       </c>
       <c r="D24" s="5">
-        <v>499.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.3</v>
+        <v>502</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1718,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>46.81</v>
+        <v>43.57</v>
       </c>
       <c r="D25" s="5">
-        <v>43.57</v>
+        <v>47.45</v>
       </c>
       <c r="E25" s="6">
-        <v>-3.24</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1735,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>41.34</v>
+        <v>40</v>
       </c>
       <c r="D26" s="5">
-        <v>40</v>
+        <v>42.32</v>
       </c>
       <c r="E26" s="6">
-        <v>-1.34</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1752,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>44.58</v>
+        <v>45.64</v>
       </c>
       <c r="D27" s="5">
-        <v>45.64</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.06</v>
+        <v>47.72</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.08</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1769,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-30.35</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D28" s="5">
-        <v>-8.369999999999999</v>
+        <v>-22.71</v>
       </c>
       <c r="E28" s="7">
-        <v>21.98</v>
+        <v>-14.34</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1786,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-27.15</v>
+        <v>-62.36</v>
       </c>
       <c r="D29" s="5">
-        <v>-62.36</v>
+        <v>-21.95</v>
       </c>
       <c r="E29" s="6">
-        <v>-35.21</v>
+        <v>40.41</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1803,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>1.36</v>
+        <v>-58.05</v>
       </c>
       <c r="D30" s="5">
-        <v>-58.05</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-59.41</v>
+        <v>-59.43</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.38</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1874,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>43.1</v>
+        <v>45.8</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-1.6</v>
+        <v>0.4</v>
       </c>
       <c r="G2" s="10">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2002,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.1626</v>
+        <v>0.1642</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0262</v>
+        <v>0.0274</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0545</v>
+        <v>-0.0535</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.5 → 48.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>48.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -744,9 +772,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -886,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1411.9</v>
+        <v>1415</v>
       </c>
       <c r="D2">
-        <v>0.71</v>
+        <v>-0.35</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -898,25 +924,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.5</v>
+        <v>-3.29</v>
       </c>
       <c r="H2">
-        <v>17.08</v>
+        <v>17.34</v>
       </c>
       <c r="I2">
-        <v>0.36</v>
+        <v>-0.02</v>
       </c>
       <c r="J2">
-        <v>-2</v>
+        <v>-1.25</v>
       </c>
       <c r="K2">
-        <v>11.67</v>
+        <v>10.62</v>
       </c>
       <c r="L2">
-        <v>-1.08</v>
+        <v>-1.48</v>
       </c>
       <c r="M2">
-        <v>16.42</v>
+        <v>16</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -925,19 +951,19 @@
         <v>58</v>
       </c>
       <c r="P2">
-        <v>1411.64</v>
+        <v>1412.18</v>
       </c>
       <c r="Q2">
-        <v>1430.9</v>
+        <v>1428.72</v>
       </c>
       <c r="R2">
-        <v>1405.35</v>
+        <v>1408.9</v>
       </c>
       <c r="S2">
-        <v>1351.62</v>
+        <v>1352.38</v>
       </c>
       <c r="T2">
-        <v>4.46</v>
+        <v>4.63</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -952,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.45</v>
+        <v>48.6</v>
       </c>
       <c r="Z2">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="AA2">
-        <v>7.19</v>
+        <v>4.74</v>
       </c>
       <c r="AB2">
-        <v>-6.51</v>
+        <v>-4.56</v>
       </c>
       <c r="AC2">
-        <v>8.720000000000001</v>
+        <v>25.67</v>
       </c>
       <c r="AD2">
-        <v>9.800000000000001</v>
+        <v>17.22</v>
       </c>
       <c r="AE2">
-        <v>21.42</v>
+        <v>20.25</v>
       </c>
       <c r="AF2">
-        <v>-22.71</v>
+        <v>-49.44</v>
       </c>
       <c r="AG2">
-        <v>1464.79</v>
+        <v>1462.78</v>
       </c>
       <c r="AH2">
-        <v>1397</v>
+        <v>1394.65</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -988,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>34.79</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -999,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="D3">
-        <v>0.58</v>
+        <v>0.19</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1011,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.15</v>
+        <v>-20.4</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="I3">
-        <v>-0.18</v>
+        <v>-0.39</v>
       </c>
       <c r="J3">
-        <v>2.62</v>
+        <v>-2.52</v>
       </c>
       <c r="K3">
-        <v>-10.68</v>
+        <v>-12.59</v>
       </c>
       <c r="L3">
-        <v>-13.79</v>
+        <v>-16.46</v>
       </c>
       <c r="M3">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>1624.16</v>
+        <v>1620.3</v>
       </c>
       <c r="Q3">
-        <v>1645.7</v>
+        <v>1640.41</v>
       </c>
       <c r="R3">
-        <v>1710.94</v>
+        <v>1707.51</v>
       </c>
       <c r="S3">
-        <v>1830.34</v>
+        <v>1826.37</v>
       </c>
       <c r="T3">
-        <v>-11.22</v>
+        <v>-11.3</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1065,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.32</v>
+        <v>41.67</v>
       </c>
       <c r="Z3">
-        <v>-23.23</v>
+        <v>-22.14</v>
       </c>
       <c r="AA3">
-        <v>-25.02</v>
+        <v>-24.1</v>
       </c>
       <c r="AB3">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AC3">
-        <v>23.9</v>
+        <v>18.8</v>
       </c>
       <c r="AD3">
-        <v>27.73</v>
+        <v>20.09</v>
       </c>
       <c r="AE3">
-        <v>38.91</v>
+        <v>35.95</v>
       </c>
       <c r="AF3">
-        <v>-21.95</v>
+        <v>-22.65</v>
       </c>
       <c r="AG3">
-        <v>1689</v>
+        <v>1682.27</v>
       </c>
       <c r="AH3">
-        <v>1602.39</v>
+        <v>1598.54</v>
       </c>
       <c r="AI3">
-        <v>1739.71</v>
+        <v>1727.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1112,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>502</v>
+        <v>511.25</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>-0.73</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1124,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-26.83</v>
+        <v>-25.48</v>
       </c>
       <c r="H4">
-        <v>9.039999999999999</v>
+        <v>11.04</v>
       </c>
       <c r="I4">
-        <v>-0.99</v>
+        <v>0.41</v>
       </c>
       <c r="J4">
-        <v>0.5</v>
+        <v>2.14</v>
       </c>
       <c r="K4">
-        <v>-3.14</v>
+        <v>-1.85</v>
       </c>
       <c r="L4">
-        <v>-19.61</v>
+        <v>-19.01</v>
       </c>
       <c r="M4">
-        <v>-5.35</v>
+        <v>-5.09</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>503.6</v>
+        <v>505.19</v>
       </c>
       <c r="Q4">
-        <v>507.56</v>
+        <v>508.36</v>
       </c>
       <c r="R4">
-        <v>500.7</v>
+        <v>502.65</v>
       </c>
       <c r="S4">
-        <v>571.0599999999999</v>
+        <v>570.1799999999999</v>
       </c>
       <c r="T4">
-        <v>-12.09</v>
+        <v>-10.33</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1178,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.72</v>
+        <v>53.97</v>
       </c>
       <c r="Z4">
-        <v>-0.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AA4">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="AB4">
-        <v>-1.24</v>
+        <v>0.05</v>
       </c>
       <c r="AC4">
-        <v>8.58</v>
+        <v>65.11</v>
       </c>
       <c r="AD4">
-        <v>18.08</v>
+        <v>38.54</v>
       </c>
       <c r="AE4">
-        <v>11.04</v>
+        <v>11.86</v>
       </c>
       <c r="AF4">
-        <v>-59.43</v>
+        <v>-46.49</v>
       </c>
       <c r="AG4">
-        <v>520.65</v>
+        <v>521.47</v>
       </c>
       <c r="AH4">
-        <v>494.47</v>
+        <v>495.25</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1214,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>15.87</v>
+        <v>21.14</v>
       </c>
     </row>
   </sheetData>
@@ -1375,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1388,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2.18</v>
+      <c r="C7" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.25</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2.62</v>
-      </c>
-      <c r="E8" s="6">
-        <v>3.13</v>
+      <c r="C8" s="6">
+        <v>-0.12</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.52</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-0.2</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="C9" s="6">
+        <v>2.69</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2.14</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.15</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-1.48</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-16.34</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-16.46</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-18.8</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-19.01</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>9.92</v>
+      </c>
+      <c r="D16" s="6">
+        <v>10.62</v>
+      </c>
+      <c r="E16" s="8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-12.47</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-12.59</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-2.07</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.95</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.29</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-0.18</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-20.55</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-20.4</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-1.36</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-24.93</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-25.48</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-1.32</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.08</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1420</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1415</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-14.93</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-13.79</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1617</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1620</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-19.32</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-19.61</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>515</v>
+      </c>
+      <c r="D24" s="6">
+        <v>511.25</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="D16" s="5">
-        <v>11.67</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>50.45</v>
+      </c>
+      <c r="D25" s="6">
+        <v>48.6</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-10.68</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>40.86</v>
+      </c>
+      <c r="D26" s="6">
+        <v>41.67</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.14</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>56.92</v>
+      </c>
+      <c r="D27" s="6">
+        <v>53.97</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-3.5</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-58</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-49.44</v>
+      </c>
+      <c r="E28" s="8">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-20.61</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-20.15</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>11.05</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-22.65</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-33.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-27.19</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-26.83</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1402</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1411.9</v>
-      </c>
-      <c r="E22" s="6">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1615.7</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1625</v>
-      </c>
-      <c r="E23" s="6">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>499.5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>502</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>43.57</v>
-      </c>
-      <c r="D25" s="5">
-        <v>47.45</v>
-      </c>
-      <c r="E25" s="6">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>40</v>
-      </c>
-      <c r="D26" s="5">
-        <v>42.32</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>45.64</v>
-      </c>
-      <c r="D27" s="5">
-        <v>47.72</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-22.71</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-14.34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-62.36</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-21.95</v>
-      </c>
-      <c r="E29" s="6">
-        <v>40.41</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-58.05</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-59.43</v>
+      <c r="C30" s="6">
+        <v>11.66</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-46.49</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.38</v>
+        <v>-58.15</v>
       </c>
     </row>
   </sheetData>
@@ -1835,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>48.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-0.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1990,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1642</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0274</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0535</v>
+      <c r="A2" s="14">
+        <v>0.16</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0277</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0509</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.5 → 48.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.5</t>
+    <t>48.6 → 51.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>48.6</t>
+  </si>
+  <si>
+    <t>51.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +399,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -912,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1415</v>
+        <v>1422.7</v>
       </c>
       <c r="D2">
-        <v>-0.35</v>
+        <v>0.54</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-3.29</v>
+        <v>-2.76</v>
       </c>
       <c r="H2">
-        <v>17.34</v>
+        <v>17.98</v>
       </c>
       <c r="I2">
-        <v>-0.02</v>
+        <v>0.76</v>
       </c>
       <c r="J2">
-        <v>-1.25</v>
+        <v>-1.59</v>
       </c>
       <c r="K2">
-        <v>10.62</v>
+        <v>11.79</v>
       </c>
       <c r="L2">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
       <c r="M2">
-        <v>16</v>
+        <v>16.24</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>1412.18</v>
+        <v>1414.32</v>
       </c>
       <c r="Q2">
-        <v>1428.72</v>
+        <v>1428.31</v>
       </c>
       <c r="R2">
-        <v>1408.9</v>
+        <v>1410.8</v>
       </c>
       <c r="S2">
-        <v>1352.38</v>
+        <v>1352.89</v>
       </c>
       <c r="T2">
-        <v>4.63</v>
+        <v>5.16</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.6</v>
+        <v>51.54</v>
       </c>
       <c r="Z2">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="AA2">
-        <v>4.74</v>
+        <v>3.88</v>
       </c>
       <c r="AB2">
-        <v>-4.56</v>
+        <v>-3.44</v>
       </c>
       <c r="AC2">
-        <v>25.67</v>
+        <v>33.16</v>
       </c>
       <c r="AD2">
-        <v>17.22</v>
+        <v>25.37</v>
       </c>
       <c r="AE2">
-        <v>20.25</v>
+        <v>20.01</v>
       </c>
       <c r="AF2">
-        <v>-49.44</v>
+        <v>-22.06</v>
       </c>
       <c r="AG2">
-        <v>1462.78</v>
+        <v>1462.46</v>
       </c>
       <c r="AH2">
-        <v>1394.65</v>
+        <v>1394.16</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>31.6</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="D3">
-        <v>0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.4</v>
+        <v>-20.6</v>
       </c>
       <c r="H3">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="I3">
-        <v>-0.39</v>
+        <v>-0.48</v>
       </c>
       <c r="J3">
-        <v>-2.52</v>
+        <v>-3.87</v>
       </c>
       <c r="K3">
-        <v>-12.59</v>
+        <v>-12.35</v>
       </c>
       <c r="L3">
-        <v>-16.46</v>
+        <v>-17.33</v>
       </c>
       <c r="M3">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>1620.3</v>
+        <v>1618.74</v>
       </c>
       <c r="Q3">
-        <v>1640.41</v>
+        <v>1637.02</v>
       </c>
       <c r="R3">
-        <v>1707.51</v>
+        <v>1705.15</v>
       </c>
       <c r="S3">
-        <v>1826.37</v>
+        <v>1824.48</v>
       </c>
       <c r="T3">
-        <v>-11.3</v>
+        <v>-11.43</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.67</v>
+        <v>40.86</v>
       </c>
       <c r="Z3">
-        <v>-22.14</v>
+        <v>-21.62</v>
       </c>
       <c r="AA3">
-        <v>-24.1</v>
+        <v>-23.61</v>
       </c>
       <c r="AB3">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>18.8</v>
+        <v>15.13</v>
       </c>
       <c r="AD3">
-        <v>20.09</v>
+        <v>17.17</v>
       </c>
       <c r="AE3">
-        <v>35.95</v>
+        <v>34.83</v>
       </c>
       <c r="AF3">
-        <v>-22.65</v>
+        <v>-6.16</v>
       </c>
       <c r="AG3">
-        <v>1682.27</v>
+        <v>1674.87</v>
       </c>
       <c r="AH3">
-        <v>1598.54</v>
+        <v>1599.16</v>
       </c>
       <c r="AI3">
-        <v>1727.35</v>
+        <v>1716.65</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>511.25</v>
+        <v>510</v>
       </c>
       <c r="D4">
-        <v>-0.73</v>
+        <v>-0.24</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,25 +1150,25 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-25.48</v>
+        <v>-25.66</v>
       </c>
       <c r="H4">
-        <v>11.04</v>
+        <v>10.77</v>
       </c>
       <c r="I4">
-        <v>0.41</v>
+        <v>2.37</v>
       </c>
       <c r="J4">
-        <v>2.14</v>
+        <v>0.04</v>
       </c>
       <c r="K4">
-        <v>-1.85</v>
+        <v>-2.13</v>
       </c>
       <c r="L4">
-        <v>-19.01</v>
+        <v>-19.03</v>
       </c>
       <c r="M4">
-        <v>-5.09</v>
+        <v>-4.74</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1177,19 +1177,19 @@
         <v>35</v>
       </c>
       <c r="P4">
-        <v>505.19</v>
+        <v>507.55</v>
       </c>
       <c r="Q4">
-        <v>508.36</v>
+        <v>508.35</v>
       </c>
       <c r="R4">
-        <v>502.65</v>
+        <v>503.13</v>
       </c>
       <c r="S4">
-        <v>570.1799999999999</v>
+        <v>569.72</v>
       </c>
       <c r="T4">
-        <v>-10.33</v>
+        <v>-10.48</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,31 +1204,31 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>53.97</v>
+        <v>52.98</v>
       </c>
       <c r="Z4">
+        <v>1.12</v>
+      </c>
+      <c r="AA4">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AA4">
-        <v>0.9</v>
-      </c>
       <c r="AB4">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="AC4">
-        <v>65.11</v>
+        <v>81.39</v>
       </c>
       <c r="AD4">
-        <v>38.54</v>
+        <v>62.8</v>
       </c>
       <c r="AE4">
-        <v>11.86</v>
+        <v>11.52</v>
       </c>
       <c r="AF4">
-        <v>-46.49</v>
+        <v>-35.34</v>
       </c>
       <c r="AG4">
-        <v>521.47</v>
+        <v>521.46</v>
       </c>
       <c r="AH4">
         <v>495.25</v>
@@ -1240,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>21.14</v>
+        <v>23.29</v>
       </c>
     </row>
   </sheetData>
@@ -1473,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.02</v>
+        <v>-1.25</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.25</v>
+        <v>-1.59</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.12</v>
+        <v>-2.52</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.52</v>
+        <v>-3.87</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.4</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>2.69</v>
+        <v>2.14</v>
       </c>
       <c r="D9" s="6">
-        <v>2.14</v>
+        <v>0.04</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.55</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.23</v>
+        <v>0.76</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.8</v>
+        <v>-0.39</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.41</v>
+        <v>-0.48</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.15</v>
+        <v>0.41</v>
       </c>
       <c r="D12" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.74</v>
+        <v>2.37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.02</v>
+        <v>-1.48</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.46</v>
+        <v>-0.55</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-16.34</v>
+        <v>-16.46</v>
       </c>
       <c r="D14" s="6">
-        <v>-16.46</v>
+        <v>-17.33</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.12</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-18.8</v>
+        <v>-19.01</v>
       </c>
       <c r="D15" s="6">
-        <v>-19.01</v>
+        <v>-19.03</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.21</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>9.92</v>
+        <v>10.62</v>
       </c>
       <c r="D16" s="6">
-        <v>10.62</v>
+        <v>11.79</v>
       </c>
       <c r="E16" s="8">
-        <v>0.7</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-12.47</v>
+        <v>-12.59</v>
       </c>
       <c r="D17" s="6">
-        <v>-12.59</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.12</v>
+        <v>-12.35</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.88</v>
+        <v>-1.85</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.03</v>
+        <v>-2.13</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.95</v>
+        <v>-3.29</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.29</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.34</v>
+        <v>-2.76</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1694,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-20.55</v>
+        <v>-20.4</v>
       </c>
       <c r="D20" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.15</v>
+        <v>-20.6</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1711,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-24.93</v>
+        <v>-25.48</v>
       </c>
       <c r="D21" s="6">
-        <v>-25.48</v>
+        <v>-25.66</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.55</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1728,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="D22" s="6">
-        <v>1415</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5</v>
+        <v>1422.7</v>
+      </c>
+      <c r="E22" s="8">
+        <v>7.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1745,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="D23" s="6">
-        <v>1620</v>
-      </c>
-      <c r="E23" s="8">
-        <v>3</v>
+        <v>1616</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1762,13 +1762,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>515</v>
+        <v>511.25</v>
       </c>
       <c r="D24" s="6">
-        <v>511.25</v>
+        <v>510</v>
       </c>
       <c r="E24" s="7">
-        <v>-3.75</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1779,13 +1779,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>50.45</v>
+        <v>48.6</v>
       </c>
       <c r="D25" s="6">
-        <v>48.6</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.85</v>
+        <v>51.54</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.94</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1796,13 +1796,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
+        <v>41.67</v>
+      </c>
+      <c r="D26" s="6">
         <v>40.86</v>
       </c>
-      <c r="D26" s="6">
-        <v>41.67</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.8100000000000001</v>
+      <c r="E26" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>56.92</v>
+        <v>53.97</v>
       </c>
       <c r="D27" s="6">
-        <v>53.97</v>
+        <v>52.98</v>
       </c>
       <c r="E27" s="7">
-        <v>-2.95</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1830,13 +1830,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-58</v>
+        <v>-49.44</v>
       </c>
       <c r="D28" s="6">
-        <v>-49.44</v>
+        <v>-22.06</v>
       </c>
       <c r="E28" s="8">
-        <v>8.56</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1847,13 +1847,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>11.05</v>
+        <v>-22.65</v>
       </c>
       <c r="D29" s="6">
-        <v>-22.65</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-33.7</v>
+        <v>-6.16</v>
+      </c>
+      <c r="E29" s="8">
+        <v>16.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1864,13 +1864,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>11.66</v>
+        <v>-46.49</v>
       </c>
       <c r="D30" s="6">
-        <v>-46.49</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-58.15</v>
+        <v>-35.34</v>
+      </c>
+      <c r="E30" s="8">
+        <v>11.15</v>
       </c>
     </row>
   </sheetData>
@@ -1935,16 +1935,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,13 +2063,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.16</v>
+        <v>0.1624</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0277</v>
+        <v>0.0273</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0509</v>
+        <v>-0.0474</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.6 → 51.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
-  </si>
-  <si>
-    <t>51.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -389,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -912,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1422.7</v>
+        <v>1430</v>
       </c>
       <c r="D2">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,25 +896,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.76</v>
+        <v>-2.26</v>
       </c>
       <c r="H2">
-        <v>17.98</v>
+        <v>18.58</v>
       </c>
       <c r="I2">
-        <v>0.76</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>-1.59</v>
+        <v>-0.06</v>
       </c>
       <c r="K2">
-        <v>11.79</v>
+        <v>12.36</v>
       </c>
       <c r="L2">
-        <v>-0.55</v>
+        <v>-1.11</v>
       </c>
       <c r="M2">
-        <v>16.24</v>
+        <v>16.1</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -951,19 +923,19 @@
         <v>60</v>
       </c>
       <c r="P2">
-        <v>1414.32</v>
+        <v>1419.92</v>
       </c>
       <c r="Q2">
-        <v>1428.31</v>
+        <v>1427.92</v>
       </c>
       <c r="R2">
-        <v>1410.8</v>
+        <v>1412.71</v>
       </c>
       <c r="S2">
-        <v>1352.89</v>
+        <v>1353.33</v>
       </c>
       <c r="T2">
-        <v>5.16</v>
+        <v>5.67</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +950,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.54</v>
+        <v>54.22</v>
       </c>
       <c r="Z2">
-        <v>0.44</v>
+        <v>1.22</v>
       </c>
       <c r="AA2">
-        <v>3.88</v>
+        <v>3.35</v>
       </c>
       <c r="AB2">
-        <v>-3.44</v>
+        <v>-2.13</v>
       </c>
       <c r="AC2">
-        <v>33.16</v>
+        <v>55.03</v>
       </c>
       <c r="AD2">
-        <v>25.37</v>
+        <v>37.95</v>
       </c>
       <c r="AE2">
-        <v>20.01</v>
+        <v>20.25</v>
       </c>
       <c r="AF2">
-        <v>-22.06</v>
+        <v>-58.69</v>
       </c>
       <c r="AG2">
-        <v>1462.46</v>
+        <v>1461.78</v>
       </c>
       <c r="AH2">
-        <v>1394.16</v>
+        <v>1394.05</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.6</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1616</v>
+        <v>1596.9</v>
       </c>
       <c r="D3">
-        <v>-0.25</v>
+        <v>-1.18</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1037,46 +1009,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-20.6</v>
+        <v>-21.53</v>
       </c>
       <c r="H3">
-        <v>2.05</v>
+        <v>0.85</v>
       </c>
       <c r="I3">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="J3">
-        <v>-3.87</v>
+        <v>-5.16</v>
       </c>
       <c r="K3">
-        <v>-12.35</v>
+        <v>-13.38</v>
       </c>
       <c r="L3">
-        <v>-17.33</v>
+        <v>-18.25</v>
       </c>
       <c r="M3">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>1618.74</v>
+        <v>1614.98</v>
       </c>
       <c r="Q3">
-        <v>1637.02</v>
+        <v>1634.42</v>
       </c>
       <c r="R3">
-        <v>1705.15</v>
+        <v>1701.42</v>
       </c>
       <c r="S3">
-        <v>1824.48</v>
+        <v>1822.4</v>
       </c>
       <c r="T3">
-        <v>-11.43</v>
+        <v>-12.37</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1063,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.86</v>
+        <v>37.16</v>
       </c>
       <c r="Z3">
-        <v>-21.62</v>
+        <v>-22.48</v>
       </c>
       <c r="AA3">
-        <v>-23.61</v>
+        <v>-23.38</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>0.9</v>
       </c>
       <c r="AC3">
-        <v>15.13</v>
+        <v>11.81</v>
       </c>
       <c r="AD3">
-        <v>17.17</v>
+        <v>15.24</v>
       </c>
       <c r="AE3">
-        <v>34.83</v>
+        <v>35.41</v>
       </c>
       <c r="AF3">
-        <v>-6.16</v>
+        <v>658.08</v>
       </c>
       <c r="AG3">
-        <v>1674.87</v>
+        <v>1675.83</v>
       </c>
       <c r="AH3">
-        <v>1599.16</v>
+        <v>1593.01</v>
       </c>
       <c r="AI3">
-        <v>1716.65</v>
+        <v>1714.38</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>9.300000000000001</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>510</v>
+        <v>515.05</v>
       </c>
       <c r="D4">
-        <v>-0.24</v>
+        <v>0.99</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1122,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-25.66</v>
+        <v>-24.93</v>
       </c>
       <c r="H4">
-        <v>10.77</v>
+        <v>11.87</v>
       </c>
       <c r="I4">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="J4">
-        <v>0.04</v>
+        <v>0.97</v>
       </c>
       <c r="K4">
-        <v>-2.13</v>
+        <v>-1.16</v>
       </c>
       <c r="L4">
-        <v>-19.03</v>
+        <v>-17.86</v>
       </c>
       <c r="M4">
-        <v>-4.74</v>
+        <v>-4.45</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>507.55</v>
+        <v>510.66</v>
       </c>
       <c r="Q4">
-        <v>508.35</v>
+        <v>508.52</v>
       </c>
       <c r="R4">
-        <v>503.13</v>
+        <v>503.62</v>
       </c>
       <c r="S4">
-        <v>569.72</v>
+        <v>569.23</v>
       </c>
       <c r="T4">
-        <v>-10.48</v>
+        <v>-9.52</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>52.98</v>
+        <v>56.45</v>
       </c>
       <c r="Z4">
-        <v>1.12</v>
+        <v>1.65</v>
       </c>
       <c r="AA4">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="AB4">
-        <v>0.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AC4">
-        <v>81.39</v>
+        <v>80.11</v>
       </c>
       <c r="AD4">
-        <v>62.8</v>
+        <v>75.53</v>
       </c>
       <c r="AE4">
-        <v>11.52</v>
+        <v>11.82</v>
       </c>
       <c r="AF4">
-        <v>-35.34</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="AG4">
-        <v>521.46</v>
+        <v>521.89</v>
       </c>
       <c r="AH4">
-        <v>495.25</v>
+        <v>495.15</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.29</v>
+        <v>28.02</v>
       </c>
     </row>
   </sheetData>
@@ -1401,47 +1373,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1449,428 +1386,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-1.59</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.34</v>
+      <c r="D7" s="5">
+        <v>-0.06</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.52</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-3.87</v>
       </c>
+      <c r="D8" s="5">
+        <v>-5.16</v>
+      </c>
       <c r="E8" s="7">
-        <v>-1.35</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>2.14</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>0.04</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.1</v>
+      <c r="D9" s="5">
+        <v>0.97</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>0.76</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.78</v>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-0.39</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-0.48</v>
       </c>
+      <c r="D11" s="5">
+        <v>-1.16</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.09</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>2.37</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.96</v>
+      <c r="D12" s="5">
+        <v>3.11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.74</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-0.55</v>
       </c>
-      <c r="E13" s="8">
-        <v>0.93</v>
+      <c r="D13" s="5">
+        <v>-1.11</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-17.33</v>
       </c>
+      <c r="D14" s="5">
+        <v>-18.25</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.87</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-19.01</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-19.03</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.02</v>
+      <c r="D15" s="5">
+        <v>-17.86</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>10.62</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>11.79</v>
       </c>
-      <c r="E16" s="8">
-        <v>1.17</v>
+      <c r="D16" s="5">
+        <v>12.36</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-12.59</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-12.35</v>
       </c>
-      <c r="E17" s="8">
-        <v>0.24</v>
+      <c r="D17" s="5">
+        <v>-13.38</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-2.13</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.28</v>
+      <c r="D18" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.97</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="6">
-        <v>-3.29</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-2.76</v>
       </c>
-      <c r="E19" s="8">
-        <v>0.53</v>
+      <c r="D19" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="6">
-        <v>-20.4</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-20.6</v>
       </c>
+      <c r="D20" s="5">
+        <v>-21.53</v>
+      </c>
       <c r="E20" s="7">
-        <v>-0.2</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="6">
-        <v>-25.48</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-25.66</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.18</v>
+      <c r="D21" s="5">
+        <v>-24.93</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.73</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="6">
-        <v>1415</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>1422.7</v>
       </c>
-      <c r="E22" s="8">
-        <v>7.7</v>
+      <c r="D22" s="5">
+        <v>1430</v>
+      </c>
+      <c r="E22" s="6">
+        <v>7.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="6">
-        <v>1620</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>1616</v>
       </c>
+      <c r="D23" s="5">
+        <v>1596.9</v>
+      </c>
       <c r="E23" s="7">
-        <v>-4</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="6">
-        <v>511.25</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>510</v>
       </c>
-      <c r="E24" s="7">
-        <v>-1.25</v>
+      <c r="D24" s="5">
+        <v>515.05</v>
+      </c>
+      <c r="E24" s="6">
+        <v>5.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="6">
-        <v>48.6</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>51.54</v>
       </c>
-      <c r="E25" s="8">
-        <v>2.94</v>
+      <c r="D25" s="5">
+        <v>54.22</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="6">
-        <v>41.67</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>40.86</v>
       </c>
+      <c r="D26" s="5">
+        <v>37.16</v>
+      </c>
       <c r="E26" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="6">
-        <v>53.97</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>52.98</v>
       </c>
-      <c r="E27" s="7">
-        <v>-0.99</v>
+      <c r="D27" s="5">
+        <v>56.45</v>
+      </c>
+      <c r="E27" s="6">
+        <v>3.47</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-49.44</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>-22.06</v>
       </c>
-      <c r="E28" s="8">
-        <v>27.38</v>
+      <c r="D28" s="5">
+        <v>-58.69</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-36.63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-22.65</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-6.16</v>
       </c>
-      <c r="E29" s="8">
-        <v>16.49</v>
+      <c r="D29" s="5">
+        <v>658.08</v>
+      </c>
+      <c r="E29" s="6">
+        <v>664.24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6">
-        <v>-46.49</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-35.34</v>
       </c>
-      <c r="E30" s="8">
-        <v>11.15</v>
+      <c r="D30" s="5">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E30" s="6">
+        <v>25.46</v>
       </c>
     </row>
   </sheetData>
@@ -1896,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>49.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-1.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2051,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1624</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0273</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0474</v>
+      <c r="A2" s="13">
+        <v>0.161</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.024</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0445</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.3% → -1.4%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>-1.4%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -884,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1430</v>
+        <v>1443</v>
       </c>
       <c r="D2">
-        <v>0.51</v>
+        <v>0.91</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.26</v>
+        <v>-1.37</v>
       </c>
       <c r="H2">
-        <v>18.58</v>
+        <v>19.66</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J2">
-        <v>-0.06</v>
+        <v>0.35</v>
       </c>
       <c r="K2">
-        <v>12.36</v>
+        <v>14.85</v>
       </c>
       <c r="L2">
-        <v>-1.11</v>
+        <v>0.46</v>
       </c>
       <c r="M2">
-        <v>16.1</v>
+        <v>16.28</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>1419.92</v>
+        <v>1426.14</v>
       </c>
       <c r="Q2">
-        <v>1427.92</v>
+        <v>1428.37</v>
       </c>
       <c r="R2">
-        <v>1412.71</v>
+        <v>1414.84</v>
       </c>
       <c r="S2">
-        <v>1353.33</v>
+        <v>1353.8</v>
       </c>
       <c r="T2">
-        <v>5.67</v>
+        <v>6.59</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.22</v>
+        <v>58.6</v>
       </c>
       <c r="Z2">
-        <v>1.22</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AB2">
-        <v>-2.13</v>
+        <v>-0.39</v>
       </c>
       <c r="AC2">
-        <v>55.03</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="AD2">
-        <v>37.95</v>
+        <v>56.05</v>
       </c>
       <c r="AE2">
-        <v>20.25</v>
+        <v>20.5</v>
       </c>
       <c r="AF2">
-        <v>-58.69</v>
+        <v>23.05</v>
       </c>
       <c r="AG2">
-        <v>1461.78</v>
+        <v>1462.81</v>
       </c>
       <c r="AH2">
-        <v>1394.05</v>
+        <v>1393.93</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -986,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.03</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1596.9</v>
+        <v>1588.1</v>
       </c>
       <c r="D3">
-        <v>-1.18</v>
+        <v>-0.55</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1009,46 +1037,46 @@
         <v>1583.5</v>
       </c>
       <c r="G3">
-        <v>-21.53</v>
+        <v>-21.97</v>
       </c>
       <c r="H3">
-        <v>0.85</v>
+        <v>0.29</v>
       </c>
       <c r="I3">
-        <v>-1.16</v>
+        <v>-2.27</v>
       </c>
       <c r="J3">
-        <v>-5.16</v>
+        <v>-3.68</v>
       </c>
       <c r="K3">
-        <v>-13.38</v>
+        <v>-11.39</v>
       </c>
       <c r="L3">
-        <v>-18.25</v>
+        <v>-16.3</v>
       </c>
       <c r="M3">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>1614.98</v>
+        <v>1607.6</v>
       </c>
       <c r="Q3">
-        <v>1634.42</v>
+        <v>1631.93</v>
       </c>
       <c r="R3">
-        <v>1701.42</v>
+        <v>1697.37</v>
       </c>
       <c r="S3">
-        <v>1822.4</v>
+        <v>1820.25</v>
       </c>
       <c r="T3">
-        <v>-12.37</v>
+        <v>-12.75</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1063,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.16</v>
+        <v>35.57</v>
       </c>
       <c r="Z3">
-        <v>-22.48</v>
+        <v>-23.61</v>
       </c>
       <c r="AA3">
-        <v>-23.38</v>
+        <v>-23.43</v>
       </c>
       <c r="AB3">
-        <v>0.9</v>
+        <v>-0.18</v>
       </c>
       <c r="AC3">
-        <v>11.81</v>
+        <v>5.32</v>
       </c>
       <c r="AD3">
-        <v>15.24</v>
+        <v>10.75</v>
       </c>
       <c r="AE3">
-        <v>35.41</v>
+        <v>34.35</v>
       </c>
       <c r="AF3">
-        <v>658.08</v>
+        <v>-12.46</v>
       </c>
       <c r="AG3">
-        <v>1675.83</v>
+        <v>1678.16</v>
       </c>
       <c r="AH3">
-        <v>1593.01</v>
+        <v>1585.7</v>
       </c>
       <c r="AI3">
-        <v>1714.38</v>
+        <v>1698.76</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>11.5</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>515.05</v>
+        <v>510</v>
       </c>
       <c r="D4">
-        <v>0.99</v>
+        <v>-0.98</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-24.93</v>
+        <v>-25.66</v>
       </c>
       <c r="H4">
-        <v>11.87</v>
+        <v>10.77</v>
       </c>
       <c r="I4">
-        <v>3.11</v>
+        <v>1.59</v>
       </c>
       <c r="J4">
-        <v>0.97</v>
+        <v>-0.32</v>
       </c>
       <c r="K4">
-        <v>-1.16</v>
+        <v>1.55</v>
       </c>
       <c r="L4">
-        <v>-17.86</v>
+        <v>-18.25</v>
       </c>
       <c r="M4">
-        <v>-4.45</v>
+        <v>-4.77</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>510.66</v>
+        <v>512.26</v>
       </c>
       <c r="Q4">
-        <v>508.52</v>
+        <v>508.49</v>
       </c>
       <c r="R4">
-        <v>503.62</v>
+        <v>503.75</v>
       </c>
       <c r="S4">
-        <v>569.23</v>
+        <v>568.71</v>
       </c>
       <c r="T4">
-        <v>-9.52</v>
+        <v>-10.32</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>56.45</v>
+        <v>52.3</v>
       </c>
       <c r="Z4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA4">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AB4">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="AC4">
-        <v>80.11</v>
+        <v>75.59</v>
       </c>
       <c r="AD4">
-        <v>75.53</v>
+        <v>79.03</v>
       </c>
       <c r="AE4">
-        <v>11.82</v>
+        <v>11.69</v>
       </c>
       <c r="AF4">
-        <v>-9.880000000000001</v>
+        <v>-63.93</v>
       </c>
       <c r="AG4">
-        <v>521.89</v>
+        <v>521.85</v>
       </c>
       <c r="AH4">
-        <v>495.15</v>
+        <v>495.14</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1212,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>28.02</v>
+        <v>31.07</v>
       </c>
     </row>
   </sheetData>
@@ -1373,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
+        <v>-0.06</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.16</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.68</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.32</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>2.2</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.27</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3.11</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1.59</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-18.25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-16.3</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-17.86</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-18.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>12.36</v>
+      </c>
+      <c r="D16" s="6">
+        <v>14.85</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-13.38</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-11.39</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.37</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-21.53</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-21.97</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-24.93</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-25.66</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1430</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1443</v>
+      </c>
+      <c r="E22" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1596.9</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1588.1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-8.800000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>515.05</v>
+      </c>
+      <c r="D24" s="6">
+        <v>510</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>54.22</v>
+      </c>
+      <c r="D25" s="6">
+        <v>58.6</v>
+      </c>
+      <c r="E25" s="7">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>37.16</v>
+      </c>
+      <c r="D26" s="6">
+        <v>35.57</v>
+      </c>
+      <c r="E26" s="8">
         <v>-1.59</v>
       </c>
-      <c r="D7" s="5">
-        <v>-0.06</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>56.45</v>
+      </c>
+      <c r="D27" s="6">
+        <v>52.3</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-58.69</v>
+      </c>
+      <c r="D28" s="6">
+        <v>23.05</v>
+      </c>
+      <c r="E28" s="7">
+        <v>81.73999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-5.16</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>658.08</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.46</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-670.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.97</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0.76</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-0.48</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-1.16</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2.37</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3.11</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-17.33</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-19.03</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-17.86</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>11.79</v>
-      </c>
-      <c r="D16" s="5">
-        <v>12.36</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-12.35</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-13.38</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.13</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.16</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-20.6</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-21.53</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-25.66</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-24.93</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1422.7</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1430</v>
-      </c>
-      <c r="E22" s="6">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1616</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1596.9</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-19.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>510</v>
-      </c>
-      <c r="D24" s="5">
-        <v>515.05</v>
-      </c>
-      <c r="E24" s="6">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>51.54</v>
-      </c>
-      <c r="D25" s="5">
-        <v>54.22</v>
-      </c>
-      <c r="E25" s="6">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>40.86</v>
-      </c>
-      <c r="D26" s="5">
-        <v>37.16</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>52.98</v>
-      </c>
-      <c r="D27" s="5">
-        <v>56.45</v>
-      </c>
-      <c r="E27" s="6">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-22.06</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-58.69</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-36.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-6.16</v>
-      </c>
-      <c r="D29" s="5">
-        <v>658.08</v>
-      </c>
-      <c r="E29" s="6">
-        <v>664.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-35.34</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-9.880000000000001</v>
       </c>
-      <c r="E30" s="6">
-        <v>25.46</v>
+      <c r="D30" s="6">
+        <v>-63.93</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-54.05</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>49.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>48.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-1.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-1.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1988,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.161</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.024</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0445</v>
+      <c r="A2" s="14">
+        <v>0.1628</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0112</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.04769999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,19 +175,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.3% → -1.4%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.4% → -2.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.4%</t>
+  </si>
+  <si>
+    <t>-2.8%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.3 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -239,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,7 +288,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -285,8 +300,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -313,13 +335,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -397,14 +425,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -413,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -772,14 +801,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +941,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1443</v>
+        <v>1422.8</v>
       </c>
       <c r="D2">
-        <v>0.91</v>
+        <v>-1.4</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +953,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-1.37</v>
+        <v>-2.75</v>
       </c>
       <c r="H2">
-        <v>19.66</v>
+        <v>17.99</v>
       </c>
       <c r="I2">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0.35</v>
+        <v>-0.77</v>
       </c>
       <c r="K2">
-        <v>14.85</v>
+        <v>14.77</v>
       </c>
       <c r="L2">
-        <v>0.46</v>
+        <v>-0.73</v>
       </c>
       <c r="M2">
-        <v>16.28</v>
+        <v>15.52</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>1426.14</v>
+        <v>1426.7</v>
       </c>
       <c r="Q2">
-        <v>1428.37</v>
+        <v>1427.74</v>
       </c>
       <c r="R2">
-        <v>1414.84</v>
+        <v>1416.45</v>
       </c>
       <c r="S2">
-        <v>1353.8</v>
+        <v>1354.12</v>
       </c>
       <c r="T2">
-        <v>6.59</v>
+        <v>5.07</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +1007,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>58.6</v>
+        <v>50.51</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="AA2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB2">
-        <v>-0.39</v>
+        <v>-0.6</v>
       </c>
       <c r="AC2">
-        <v>79.95999999999999</v>
+        <v>82.06</v>
       </c>
       <c r="AD2">
-        <v>56.05</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="AE2">
-        <v>20.5</v>
+        <v>20.76</v>
       </c>
       <c r="AF2">
-        <v>23.05</v>
+        <v>-8.32</v>
       </c>
       <c r="AG2">
-        <v>1462.81</v>
+        <v>1462.1</v>
       </c>
       <c r="AH2">
-        <v>1393.93</v>
+        <v>1393.38</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +1043,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>29.85</v>
+        <v>26.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,58 +1054,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1588.1</v>
+        <v>1562</v>
       </c>
       <c r="D3">
-        <v>-0.55</v>
+        <v>-1.64</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1583.5</v>
+        <v>1562</v>
       </c>
       <c r="G3">
-        <v>-21.97</v>
+        <v>-23.25</v>
       </c>
       <c r="H3">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.27</v>
+        <v>-3.4</v>
       </c>
       <c r="J3">
-        <v>-3.68</v>
+        <v>-4.63</v>
       </c>
       <c r="K3">
-        <v>-11.39</v>
+        <v>-10.64</v>
       </c>
       <c r="L3">
-        <v>-16.3</v>
+        <v>-18.03</v>
       </c>
       <c r="M3">
-        <v>1.12</v>
+        <v>0.43</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>1607.6</v>
+        <v>1596.6</v>
       </c>
       <c r="Q3">
-        <v>1631.93</v>
+        <v>1628.85</v>
       </c>
       <c r="R3">
-        <v>1697.37</v>
+        <v>1691.83</v>
       </c>
       <c r="S3">
-        <v>1820.25</v>
+        <v>1818.12</v>
       </c>
       <c r="T3">
-        <v>-12.75</v>
+        <v>-14.09</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1120,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.57</v>
+        <v>31.27</v>
       </c>
       <c r="Z3">
-        <v>-23.61</v>
+        <v>-26.3</v>
       </c>
       <c r="AA3">
-        <v>-23.43</v>
+        <v>-24</v>
       </c>
       <c r="AB3">
-        <v>-0.18</v>
+        <v>-2.3</v>
       </c>
       <c r="AC3">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>10.75</v>
+        <v>5.71</v>
       </c>
       <c r="AE3">
-        <v>34.35</v>
+        <v>34.68</v>
       </c>
       <c r="AF3">
-        <v>-12.46</v>
+        <v>-14.06</v>
       </c>
       <c r="AG3">
-        <v>1678.16</v>
+        <v>1684.64</v>
       </c>
       <c r="AH3">
-        <v>1585.7</v>
+        <v>1573.05</v>
       </c>
       <c r="AI3">
-        <v>1698.76</v>
+        <v>1673.58</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>13.59</v>
+        <v>18.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1167,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D4">
-        <v>-0.98</v>
+        <v>-0.78</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1179,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-25.66</v>
+        <v>-26.25</v>
       </c>
       <c r="H4">
-        <v>10.77</v>
+        <v>9.9</v>
       </c>
       <c r="I4">
-        <v>1.59</v>
+        <v>-1.75</v>
       </c>
       <c r="J4">
-        <v>-0.32</v>
+        <v>-0.9</v>
       </c>
       <c r="K4">
-        <v>1.55</v>
+        <v>3.92</v>
       </c>
       <c r="L4">
-        <v>-18.25</v>
+        <v>-19.36</v>
       </c>
       <c r="M4">
-        <v>-4.77</v>
+        <v>-5</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>512.26</v>
+        <v>510.46</v>
       </c>
       <c r="Q4">
-        <v>508.49</v>
+        <v>508.02</v>
       </c>
       <c r="R4">
-        <v>503.75</v>
+        <v>503.43</v>
       </c>
       <c r="S4">
-        <v>568.71</v>
+        <v>568.13</v>
       </c>
       <c r="T4">
-        <v>-10.32</v>
+        <v>-10.94</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1233,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>52.3</v>
+        <v>49.21</v>
       </c>
       <c r="Z4">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AA4">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AB4">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="AC4">
-        <v>75.59</v>
+        <v>65.41</v>
       </c>
       <c r="AD4">
-        <v>79.03</v>
+        <v>73.7</v>
       </c>
       <c r="AE4">
-        <v>11.69</v>
+        <v>11.42</v>
       </c>
       <c r="AF4">
-        <v>-63.93</v>
+        <v>12.05</v>
       </c>
       <c r="AG4">
-        <v>521.85</v>
+        <v>521.01</v>
       </c>
       <c r="AH4">
-        <v>495.14</v>
+        <v>495.04</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1269,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>31.07</v>
+        <v>29.98</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1439,444 +1468,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>0.35</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-0.77</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-3.68</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-4.63</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-0.32</v>
       </c>
-      <c r="E9" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="7">
+        <v>2.2</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-2.27</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-3.4</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.59</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-1.75</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-0.73</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-16.3</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-18.03</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-18.25</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-19.36</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="7">
+        <v>14.85</v>
+      </c>
+      <c r="D17" s="7">
+        <v>14.77</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-11.39</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-10.64</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="D19" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.37</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-2.75</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-21.97</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-23.25</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-25.66</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-26.25</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="C23" s="7">
+        <v>1443</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1422.8</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-20.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1588.1</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1562</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-26.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.59</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="7">
+        <v>510</v>
+      </c>
+      <c r="D25" s="7">
+        <v>506</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="7">
+        <v>58.6</v>
+      </c>
+      <c r="D26" s="7">
+        <v>50.51</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-8.09</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-18.25</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-16.3</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="7">
+        <v>35.57</v>
+      </c>
+      <c r="D27" s="7">
+        <v>31.27</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-17.86</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-18.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="7">
+        <v>52.3</v>
+      </c>
+      <c r="D28" s="7">
+        <v>49.21</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>12.36</v>
-      </c>
-      <c r="D16" s="6">
-        <v>14.85</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="7">
+        <v>23.05</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-8.32</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-31.37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-13.38</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-11.39</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-12.46</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-14.06</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-21.53</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-21.97</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-24.93</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-25.66</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1430</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1443</v>
-      </c>
-      <c r="E22" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1596.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1588.1</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-8.800000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>515.05</v>
-      </c>
-      <c r="D24" s="6">
-        <v>510</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>54.22</v>
-      </c>
-      <c r="D25" s="6">
-        <v>58.6</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>37.16</v>
-      </c>
-      <c r="D26" s="6">
-        <v>35.57</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>56.45</v>
-      </c>
-      <c r="D27" s="6">
-        <v>52.3</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-4.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-58.69</v>
-      </c>
-      <c r="D28" s="6">
-        <v>23.05</v>
-      </c>
-      <c r="E28" s="7">
-        <v>81.73999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>658.08</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-12.46</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-670.54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C31" s="7">
         <v>-63.93</v>
       </c>
-      <c r="E30" s="8">
-        <v>-54.05</v>
+      <c r="D31" s="7">
+        <v>12.05</v>
+      </c>
+      <c r="E31" s="9">
+        <v>75.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1896,60 +1945,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>43.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-2.1</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>30</v>
       </c>
     </row>
@@ -2051,25 +2100,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1628</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0112</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.04769999999999999</v>
+      <c r="A2" s="15">
+        <v>0.1552</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0043</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -175,34 +175,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.4% → -2.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.8% → -0.6%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
   </si>
   <si>
     <t>-2.8%</t>
   </si>
   <si>
+    <t>-0.6%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.3 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.3</t>
+    <t>49.2 → 56.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.2</t>
+  </si>
+  <si>
+    <t>56.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -254,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,27 +288,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,18 +316,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -425,15 +399,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -442,7 +414,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -801,14 +773,14 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -941,10 +913,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1422.8</v>
+        <v>1454</v>
       </c>
       <c r="D2">
-        <v>-1.4</v>
+        <v>2.19</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -953,46 +925,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.75</v>
+        <v>-0.62</v>
       </c>
       <c r="H2">
-        <v>17.99</v>
+        <v>20.57</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>2.76</v>
       </c>
       <c r="J2">
-        <v>-0.77</v>
+        <v>1.3</v>
       </c>
       <c r="K2">
-        <v>14.77</v>
+        <v>18.54</v>
       </c>
       <c r="L2">
-        <v>-0.73</v>
+        <v>2.64</v>
       </c>
       <c r="M2">
-        <v>15.52</v>
+        <v>15.83</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>1426.7</v>
+        <v>1434.5</v>
       </c>
       <c r="Q2">
-        <v>1427.74</v>
+        <v>1427.44</v>
       </c>
       <c r="R2">
-        <v>1416.45</v>
+        <v>1418.6</v>
       </c>
       <c r="S2">
-        <v>1354.12</v>
+        <v>1354.6</v>
       </c>
       <c r="T2">
-        <v>5.07</v>
+        <v>7.34</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -1007,34 +979,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.51</v>
+        <v>59.75</v>
       </c>
       <c r="Z2">
-        <v>2.49</v>
+        <v>4.67</v>
       </c>
       <c r="AA2">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="AB2">
-        <v>-0.6</v>
+        <v>1.26</v>
       </c>
       <c r="AC2">
         <v>82.06</v>
       </c>
       <c r="AD2">
-        <v>72.34999999999999</v>
+        <v>81.36</v>
       </c>
       <c r="AE2">
-        <v>20.76</v>
+        <v>21.78</v>
       </c>
       <c r="AF2">
-        <v>-8.32</v>
+        <v>67.56</v>
       </c>
       <c r="AG2">
-        <v>1462.1</v>
+        <v>1460.7</v>
       </c>
       <c r="AH2">
-        <v>1393.38</v>
+        <v>1394.18</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1043,7 +1015,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.63</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1054,10 +1026,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1562</v>
+        <v>1566.9</v>
       </c>
       <c r="D3">
-        <v>-1.64</v>
+        <v>0.31</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1066,46 +1038,46 @@
         <v>1562</v>
       </c>
       <c r="G3">
-        <v>-23.25</v>
+        <v>-23.01</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I3">
-        <v>-3.4</v>
+        <v>-3.28</v>
       </c>
       <c r="J3">
-        <v>-4.63</v>
+        <v>-3.5</v>
       </c>
       <c r="K3">
-        <v>-10.64</v>
+        <v>-10.28</v>
       </c>
       <c r="L3">
-        <v>-18.03</v>
+        <v>-15.74</v>
       </c>
       <c r="M3">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>1596.6</v>
+        <v>1585.98</v>
       </c>
       <c r="Q3">
-        <v>1628.85</v>
+        <v>1623.44</v>
       </c>
       <c r="R3">
-        <v>1691.83</v>
+        <v>1685.77</v>
       </c>
       <c r="S3">
-        <v>1818.12</v>
+        <v>1815.85</v>
       </c>
       <c r="T3">
-        <v>-14.09</v>
+        <v>-13.71</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1120,43 +1092,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.27</v>
+        <v>32.91</v>
       </c>
       <c r="Z3">
-        <v>-26.3</v>
+        <v>-27.72</v>
       </c>
       <c r="AA3">
-        <v>-24</v>
+        <v>-24.75</v>
       </c>
       <c r="AB3">
-        <v>-2.3</v>
+        <v>-2.98</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AD3">
-        <v>5.71</v>
+        <v>3.34</v>
       </c>
       <c r="AE3">
-        <v>34.68</v>
+        <v>34.17</v>
       </c>
       <c r="AF3">
-        <v>-14.06</v>
+        <v>38.11</v>
       </c>
       <c r="AG3">
-        <v>1684.64</v>
+        <v>1681.31</v>
       </c>
       <c r="AH3">
-        <v>1573.05</v>
+        <v>1565.57</v>
       </c>
       <c r="AI3">
-        <v>1673.58</v>
+        <v>1656.31</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>18.87</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1167,10 +1139,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>506</v>
+        <v>517.05</v>
       </c>
       <c r="D4">
-        <v>-0.78</v>
+        <v>2.18</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1179,46 +1151,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-26.25</v>
+        <v>-24.64</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>12.3</v>
       </c>
       <c r="I4">
-        <v>-1.75</v>
+        <v>1.13</v>
       </c>
       <c r="J4">
-        <v>-0.9</v>
+        <v>0.32</v>
       </c>
       <c r="K4">
-        <v>3.92</v>
+        <v>7.54</v>
       </c>
       <c r="L4">
-        <v>-19.36</v>
+        <v>-15.81</v>
       </c>
       <c r="M4">
-        <v>-5</v>
+        <v>-4.59</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>510.46</v>
+        <v>511.62</v>
       </c>
       <c r="Q4">
-        <v>508.02</v>
+        <v>507.76</v>
       </c>
       <c r="R4">
-        <v>503.43</v>
+        <v>503.76</v>
       </c>
       <c r="S4">
-        <v>568.13</v>
+        <v>567.5599999999999</v>
       </c>
       <c r="T4">
-        <v>-10.94</v>
+        <v>-8.9</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1233,34 +1205,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.21</v>
+        <v>56.8</v>
       </c>
       <c r="Z4">
-        <v>1.29</v>
+        <v>1.89</v>
       </c>
       <c r="AA4">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AB4">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AC4">
-        <v>65.41</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="AD4">
-        <v>73.7</v>
+        <v>69.12</v>
       </c>
       <c r="AE4">
-        <v>11.42</v>
+        <v>11.97</v>
       </c>
       <c r="AF4">
-        <v>12.05</v>
+        <v>138.67</v>
       </c>
       <c r="AG4">
-        <v>521.01</v>
+        <v>519.6900000000001</v>
       </c>
       <c r="AH4">
-        <v>495.04</v>
+        <v>495.83</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1269,7 +1241,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>29.98</v>
+        <v>30.86</v>
       </c>
     </row>
   </sheetData>
@@ -1469,22 +1441,22 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1515,411 +1487,411 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="6">
         <v>-0.77</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.12</v>
+      <c r="D8" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.07</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>-3.68</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="6">
         <v>-4.63</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.95</v>
+      <c r="D9" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="6">
         <v>-0.9</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.58</v>
+      <c r="D10" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7">
-        <v>2.2</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="6">
         <v>0.2</v>
       </c>
-      <c r="E11" s="8">
-        <v>-2</v>
+      <c r="D11" s="6">
+        <v>2.76</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="7">
-        <v>-2.27</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="6">
         <v>-3.4</v>
       </c>
-      <c r="E12" s="8">
-        <v>-1.13</v>
+      <c r="D12" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="7">
-        <v>1.59</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="6">
         <v>-1.75</v>
       </c>
-      <c r="E13" s="8">
-        <v>-3.34</v>
+      <c r="D13" s="6">
+        <v>1.13</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="7">
-        <v>0.46</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="6">
         <v>-0.73</v>
       </c>
-      <c r="E14" s="8">
-        <v>-1.19</v>
+      <c r="D14" s="6">
+        <v>2.64</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.37</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="7">
-        <v>-16.3</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="6">
         <v>-18.03</v>
       </c>
-      <c r="E15" s="8">
-        <v>-1.73</v>
+      <c r="D15" s="6">
+        <v>-15.74</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="7">
-        <v>-18.25</v>
-      </c>
-      <c r="D16" s="7">
+      <c r="C16" s="6">
         <v>-19.36</v>
       </c>
-      <c r="E16" s="8">
-        <v>-1.11</v>
+      <c r="D16" s="6">
+        <v>-15.81</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="7">
-        <v>14.85</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="C17" s="6">
         <v>14.77</v>
       </c>
-      <c r="E17" s="8">
-        <v>-0.08</v>
+      <c r="D17" s="6">
+        <v>18.54</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="7">
-        <v>-11.39</v>
-      </c>
-      <c r="D18" s="7">
+      <c r="C18" s="6">
         <v>-10.64</v>
       </c>
-      <c r="E18" s="9">
-        <v>0.75</v>
+      <c r="D18" s="6">
+        <v>-10.28</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="C19" s="6">
         <v>3.92</v>
       </c>
-      <c r="E19" s="9">
-        <v>2.37</v>
+      <c r="D19" s="6">
+        <v>7.54</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="7">
-        <v>-1.37</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="C20" s="6">
         <v>-2.75</v>
       </c>
-      <c r="E20" s="8">
-        <v>-1.38</v>
+      <c r="D20" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="7">
-        <v>-21.97</v>
-      </c>
-      <c r="D21" s="7">
+      <c r="C21" s="6">
         <v>-23.25</v>
       </c>
-      <c r="E21" s="8">
-        <v>-1.28</v>
+      <c r="D21" s="6">
+        <v>-23.01</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="7">
-        <v>-25.66</v>
-      </c>
-      <c r="D22" s="7">
+      <c r="C22" s="6">
         <v>-26.25</v>
       </c>
-      <c r="E22" s="8">
-        <v>-0.59</v>
+      <c r="D22" s="6">
+        <v>-24.64</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.61</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="7">
-        <v>1443</v>
-      </c>
-      <c r="D23" s="7">
+      <c r="C23" s="6">
         <v>1422.8</v>
       </c>
-      <c r="E23" s="8">
-        <v>-20.2</v>
+      <c r="D23" s="6">
+        <v>1454</v>
+      </c>
+      <c r="E23" s="7">
+        <v>31.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="7">
-        <v>1588.1</v>
-      </c>
-      <c r="D24" s="7">
+      <c r="C24" s="6">
         <v>1562</v>
       </c>
-      <c r="E24" s="8">
-        <v>-26.1</v>
+      <c r="D24" s="6">
+        <v>1566.9</v>
+      </c>
+      <c r="E24" s="7">
+        <v>4.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="7">
-        <v>510</v>
-      </c>
-      <c r="D25" s="7">
+      <c r="C25" s="6">
         <v>506</v>
       </c>
-      <c r="E25" s="8">
-        <v>-4</v>
+      <c r="D25" s="6">
+        <v>517.05</v>
+      </c>
+      <c r="E25" s="7">
+        <v>11.05</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="7">
-        <v>58.6</v>
-      </c>
-      <c r="D26" s="7">
+      <c r="C26" s="6">
         <v>50.51</v>
       </c>
-      <c r="E26" s="8">
-        <v>-8.09</v>
+      <c r="D26" s="6">
+        <v>59.75</v>
+      </c>
+      <c r="E26" s="7">
+        <v>9.24</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="7">
-        <v>35.57</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="C27" s="6">
         <v>31.27</v>
       </c>
-      <c r="E27" s="8">
-        <v>-4.3</v>
+      <c r="D27" s="6">
+        <v>32.91</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="7">
-        <v>52.3</v>
-      </c>
-      <c r="D28" s="7">
+      <c r="C28" s="6">
         <v>49.21</v>
       </c>
-      <c r="E28" s="8">
-        <v>-3.09</v>
+      <c r="D28" s="6">
+        <v>56.8</v>
+      </c>
+      <c r="E28" s="7">
+        <v>7.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="7">
-        <v>23.05</v>
-      </c>
-      <c r="D29" s="7">
+      <c r="C29" s="6">
         <v>-8.32</v>
       </c>
-      <c r="E29" s="8">
-        <v>-31.37</v>
+      <c r="D29" s="6">
+        <v>67.56</v>
+      </c>
+      <c r="E29" s="7">
+        <v>75.88</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="7">
-        <v>-12.46</v>
-      </c>
-      <c r="D30" s="7">
+      <c r="C30" s="6">
         <v>-14.06</v>
       </c>
-      <c r="E30" s="8">
-        <v>-1.6</v>
+      <c r="D30" s="6">
+        <v>38.11</v>
+      </c>
+      <c r="E30" s="7">
+        <v>52.17</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="7">
-        <v>-63.93</v>
-      </c>
-      <c r="D31" s="7">
+      <c r="C31" s="6">
         <v>12.05</v>
       </c>
-      <c r="E31" s="9">
-        <v>75.98</v>
+      <c r="D31" s="6">
+        <v>138.67</v>
+      </c>
+      <c r="E31" s="7">
+        <v>126.62</v>
       </c>
     </row>
   </sheetData>
@@ -1945,60 +1917,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="12">
-        <v>43.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>49.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="12">
-        <v>-2.1</v>
-      </c>
-      <c r="G2" s="12">
-        <v>2.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2100,25 +2072,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.1552</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.0043</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.05</v>
+      <c r="A2" s="13">
+        <v>0.1583</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0038</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0459</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,34 +175,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.8% → -0.6%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.8%</t>
-  </si>
-  <si>
-    <t>-0.6%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.2 → 56.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>56.8 → 43.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>56.8</t>
+  </si>
+  <si>
+    <t>43.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -254,7 +239,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,13 +273,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,6 +308,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -402,10 +400,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -414,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -913,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1454</v>
+        <v>1438</v>
       </c>
       <c r="D2">
-        <v>2.19</v>
+        <v>-1.1</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -925,46 +924,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-0.62</v>
+        <v>-1.72</v>
       </c>
       <c r="H2">
-        <v>20.57</v>
+        <v>19.25</v>
       </c>
       <c r="I2">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
       <c r="J2">
-        <v>1.3</v>
+        <v>-1.51</v>
       </c>
       <c r="K2">
-        <v>18.54</v>
+        <v>15.78</v>
       </c>
       <c r="L2">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="M2">
-        <v>15.83</v>
+        <v>15.54</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>1434.5</v>
+        <v>1437.56</v>
       </c>
       <c r="Q2">
-        <v>1427.44</v>
+        <v>1426.61</v>
       </c>
       <c r="R2">
-        <v>1418.6</v>
+        <v>1420.31</v>
       </c>
       <c r="S2">
-        <v>1354.6</v>
+        <v>1354.86</v>
       </c>
       <c r="T2">
-        <v>7.34</v>
+        <v>6.14</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -979,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.75</v>
+        <v>54.17</v>
       </c>
       <c r="Z2">
-        <v>4.67</v>
+        <v>5.05</v>
       </c>
       <c r="AA2">
-        <v>3.41</v>
+        <v>3.74</v>
       </c>
       <c r="AB2">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AC2">
-        <v>82.06</v>
+        <v>70.56</v>
       </c>
       <c r="AD2">
-        <v>81.36</v>
+        <v>78.23</v>
       </c>
       <c r="AE2">
-        <v>21.78</v>
+        <v>22.45</v>
       </c>
       <c r="AF2">
-        <v>67.56</v>
+        <v>12.04</v>
       </c>
       <c r="AG2">
-        <v>1460.7</v>
+        <v>1457.78</v>
       </c>
       <c r="AH2">
-        <v>1394.18</v>
+        <v>1395.44</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1015,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.37</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,7 +1028,7 @@
         <v>1566.9</v>
       </c>
       <c r="D3">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
@@ -1044,40 +1043,40 @@
         <v>0.31</v>
       </c>
       <c r="I3">
-        <v>-3.28</v>
+        <v>-3.04</v>
       </c>
       <c r="J3">
-        <v>-3.5</v>
+        <v>-6.45</v>
       </c>
       <c r="K3">
-        <v>-10.28</v>
+        <v>-9.99</v>
       </c>
       <c r="L3">
-        <v>-15.74</v>
+        <v>-15.18</v>
       </c>
       <c r="M3">
-        <v>0.38</v>
+        <v>-0.1</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3">
-        <v>1585.98</v>
+        <v>1576.16</v>
       </c>
       <c r="Q3">
-        <v>1623.44</v>
+        <v>1619.55</v>
       </c>
       <c r="R3">
-        <v>1685.77</v>
+        <v>1679.9</v>
       </c>
       <c r="S3">
-        <v>1815.85</v>
+        <v>1813.55</v>
       </c>
       <c r="T3">
-        <v>-13.71</v>
+        <v>-13.6</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1095,31 +1094,31 @@
         <v>32.91</v>
       </c>
       <c r="Z3">
-        <v>-27.72</v>
+        <v>-28.52</v>
       </c>
       <c r="AA3">
-        <v>-24.75</v>
+        <v>-25.5</v>
       </c>
       <c r="AB3">
-        <v>-2.98</v>
+        <v>-3.02</v>
       </c>
       <c r="AC3">
-        <v>4.71</v>
+        <v>9.65</v>
       </c>
       <c r="AD3">
-        <v>3.34</v>
+        <v>4.79</v>
       </c>
       <c r="AE3">
-        <v>34.17</v>
+        <v>33.95</v>
       </c>
       <c r="AF3">
-        <v>38.11</v>
+        <v>-58.08</v>
       </c>
       <c r="AG3">
-        <v>1681.31</v>
+        <v>1681.69</v>
       </c>
       <c r="AH3">
-        <v>1565.57</v>
+        <v>1557.4</v>
       </c>
       <c r="AI3">
         <v>1656.31</v>
@@ -1128,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>24.1</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1139,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>517.05</v>
+        <v>495.45</v>
       </c>
       <c r="D4">
-        <v>2.18</v>
+        <v>-4.18</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1151,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-24.64</v>
+        <v>-27.78</v>
       </c>
       <c r="H4">
-        <v>12.3</v>
+        <v>7.61</v>
       </c>
       <c r="I4">
-        <v>1.13</v>
+        <v>-2.85</v>
       </c>
       <c r="J4">
-        <v>0.32</v>
+        <v>-5.15</v>
       </c>
       <c r="K4">
-        <v>7.54</v>
+        <v>4.25</v>
       </c>
       <c r="L4">
-        <v>-15.81</v>
+        <v>-18.44</v>
       </c>
       <c r="M4">
-        <v>-4.59</v>
+        <v>-5.38</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>511.62</v>
+        <v>508.71</v>
       </c>
       <c r="Q4">
-        <v>507.76</v>
+        <v>506.85</v>
       </c>
       <c r="R4">
-        <v>503.76</v>
+        <v>503.55</v>
       </c>
       <c r="S4">
-        <v>567.5599999999999</v>
+        <v>566.9</v>
       </c>
       <c r="T4">
-        <v>-8.9</v>
+        <v>-12.6</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1205,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>56.8</v>
+        <v>43.21</v>
       </c>
       <c r="Z4">
-        <v>1.89</v>
+        <v>0.61</v>
       </c>
       <c r="AA4">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AB4">
-        <v>0.54</v>
+        <v>-0.59</v>
       </c>
       <c r="AC4">
-        <v>66.34999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="AD4">
-        <v>69.12</v>
+        <v>59.09</v>
       </c>
       <c r="AE4">
-        <v>11.97</v>
+        <v>12.69</v>
       </c>
       <c r="AF4">
-        <v>138.67</v>
+        <v>40.63</v>
       </c>
       <c r="AG4">
-        <v>519.6900000000001</v>
+        <v>519.65</v>
       </c>
       <c r="AH4">
-        <v>495.83</v>
+        <v>494.06</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1241,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.86</v>
+        <v>30.09</v>
       </c>
     </row>
   </sheetData>
@@ -1382,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1422,7 +1421,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1440,288 +1439,285 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-2.81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.77</v>
+        <v>-3.5</v>
       </c>
       <c r="D8" s="6">
-        <v>1.3</v>
+        <v>-6.45</v>
       </c>
       <c r="E8" s="7">
-        <v>2.07</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.63</v>
+        <v>0.32</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.5</v>
+        <v>-5.15</v>
       </c>
       <c r="E9" s="7">
-        <v>1.13</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-0.9</v>
+        <v>2.76</v>
       </c>
       <c r="D10" s="6">
-        <v>0.32</v>
+        <v>1.08</v>
       </c>
       <c r="E10" s="7">
-        <v>1.22</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>0.2</v>
+        <v>-3.28</v>
       </c>
       <c r="D11" s="6">
-        <v>2.76</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.56</v>
+        <v>-3.04</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.4</v>
+        <v>1.13</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.28</v>
+        <v>-2.85</v>
       </c>
       <c r="E12" s="7">
-        <v>0.12</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.75</v>
+        <v>2.64</v>
       </c>
       <c r="D13" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.88</v>
+        <v>2.78</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.73</v>
+        <v>-15.74</v>
       </c>
       <c r="D14" s="6">
-        <v>2.64</v>
-      </c>
-      <c r="E14" s="7">
-        <v>3.37</v>
+        <v>-15.18</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-18.03</v>
+        <v>-15.81</v>
       </c>
       <c r="D15" s="6">
-        <v>-15.74</v>
+        <v>-18.44</v>
       </c>
       <c r="E15" s="7">
-        <v>2.29</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-19.36</v>
+        <v>18.54</v>
       </c>
       <c r="D16" s="6">
-        <v>-15.81</v>
+        <v>15.78</v>
       </c>
       <c r="E16" s="7">
-        <v>3.55</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>14.77</v>
+        <v>-10.28</v>
       </c>
       <c r="D17" s="6">
-        <v>18.54</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.77</v>
+        <v>-9.99</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.64</v>
+        <v>7.54</v>
       </c>
       <c r="D18" s="6">
-        <v>-10.28</v>
+        <v>4.25</v>
       </c>
       <c r="E18" s="7">
-        <v>0.36</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>3.92</v>
+        <v>-0.62</v>
       </c>
       <c r="D19" s="6">
-        <v>7.54</v>
+        <v>-1.72</v>
       </c>
       <c r="E19" s="7">
-        <v>3.62</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.75</v>
+        <v>-24.64</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.62</v>
+        <v>-27.78</v>
       </c>
       <c r="E20" s="7">
-        <v>2.13</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.25</v>
+        <v>1454</v>
       </c>
       <c r="D21" s="6">
-        <v>-23.01</v>
+        <v>1438</v>
       </c>
       <c r="E21" s="7">
-        <v>0.24</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1729,16 +1725,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>-26.25</v>
+        <v>517.05</v>
       </c>
       <c r="D22" s="6">
-        <v>-24.64</v>
+        <v>495.45</v>
       </c>
       <c r="E22" s="7">
-        <v>1.61</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1746,158 +1742,90 @@
         <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6">
-        <v>1422.8</v>
+        <v>59.75</v>
       </c>
       <c r="D23" s="6">
-        <v>1454</v>
+        <v>54.17</v>
       </c>
       <c r="E23" s="7">
-        <v>31.2</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6">
-        <v>1562</v>
+        <v>56.8</v>
       </c>
       <c r="D24" s="6">
-        <v>1566.9</v>
+        <v>43.21</v>
       </c>
       <c r="E24" s="7">
-        <v>4.9</v>
+        <v>-13.59</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C25" s="6">
-        <v>506</v>
+        <v>67.56</v>
       </c>
       <c r="D25" s="6">
-        <v>517.05</v>
+        <v>12.04</v>
       </c>
       <c r="E25" s="7">
-        <v>11.05</v>
+        <v>-55.52</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C26" s="6">
-        <v>50.51</v>
+        <v>38.11</v>
       </c>
       <c r="D26" s="6">
-        <v>59.75</v>
+        <v>-58.08</v>
       </c>
       <c r="E26" s="7">
-        <v>9.24</v>
+        <v>-96.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="6">
-        <v>31.27</v>
+        <v>138.67</v>
       </c>
       <c r="D27" s="6">
-        <v>32.91</v>
+        <v>40.63</v>
       </c>
       <c r="E27" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>49.21</v>
-      </c>
-      <c r="D28" s="6">
-        <v>56.8</v>
-      </c>
-      <c r="E28" s="7">
-        <v>7.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-8.32</v>
-      </c>
-      <c r="D29" s="6">
-        <v>67.56</v>
-      </c>
-      <c r="E29" s="7">
-        <v>75.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-14.06</v>
-      </c>
-      <c r="D30" s="6">
-        <v>38.11</v>
-      </c>
-      <c r="E30" s="7">
-        <v>52.17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>12.05</v>
-      </c>
-      <c r="D31" s="6">
-        <v>138.67</v>
-      </c>
-      <c r="E31" s="7">
-        <v>126.62</v>
+        <v>-98.04000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1917,60 +1845,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>49.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>43.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-0.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-4.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -2072,25 +2000,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1583</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0459</v>
+      <c r="A2" s="14">
+        <v>0.1554</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0538</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,19 +175,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>56.8 → 43.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.8</t>
-  </si>
-  <si>
-    <t>43.2</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.7% → -2.5%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.7%</t>
+  </si>
+  <si>
+    <t>-2.5%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -239,7 +239,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,6 +273,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -286,7 +293,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +315,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,12 +412,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -413,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -778,8 +791,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +924,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1438</v>
+        <v>1426.5</v>
       </c>
       <c r="D2">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,46 +936,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-1.72</v>
+        <v>-2.5</v>
       </c>
       <c r="H2">
-        <v>19.25</v>
+        <v>18.29</v>
       </c>
       <c r="I2">
-        <v>1.08</v>
+        <v>-0.24</v>
       </c>
       <c r="J2">
-        <v>-1.51</v>
+        <v>-1.93</v>
       </c>
       <c r="K2">
-        <v>15.78</v>
+        <v>13.97</v>
       </c>
       <c r="L2">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="M2">
-        <v>15.54</v>
+        <v>15.19</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>1437.56</v>
+        <v>1436.86</v>
       </c>
       <c r="Q2">
-        <v>1426.61</v>
+        <v>1425.43</v>
       </c>
       <c r="R2">
-        <v>1420.31</v>
+        <v>1422.07</v>
       </c>
       <c r="S2">
-        <v>1354.86</v>
+        <v>1355.13</v>
       </c>
       <c r="T2">
-        <v>6.14</v>
+        <v>5.27</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.17</v>
+        <v>50.51</v>
       </c>
       <c r="Z2">
-        <v>5.05</v>
+        <v>4.36</v>
       </c>
       <c r="AA2">
-        <v>3.74</v>
+        <v>3.86</v>
       </c>
       <c r="AB2">
-        <v>1.31</v>
+        <v>0.5</v>
       </c>
       <c r="AC2">
-        <v>70.56</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="AD2">
-        <v>78.23</v>
+        <v>74.03</v>
       </c>
       <c r="AE2">
-        <v>22.45</v>
+        <v>22.08</v>
       </c>
       <c r="AF2">
-        <v>12.04</v>
+        <v>-11.29</v>
       </c>
       <c r="AG2">
-        <v>1457.78</v>
+        <v>1454.58</v>
       </c>
       <c r="AH2">
-        <v>1395.44</v>
+        <v>1396.28</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +1026,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.15</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,37 +1037,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1566.9</v>
+        <v>1537</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-1.91</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1562</v>
+        <v>1537</v>
       </c>
       <c r="G3">
-        <v>-23.01</v>
+        <v>-24.48</v>
       </c>
       <c r="H3">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.04</v>
+        <v>-3.75</v>
       </c>
       <c r="J3">
-        <v>-6.45</v>
+        <v>-6.55</v>
       </c>
       <c r="K3">
-        <v>-9.99</v>
+        <v>-11.3</v>
       </c>
       <c r="L3">
-        <v>-15.18</v>
+        <v>-15.86</v>
       </c>
       <c r="M3">
-        <v>-0.1</v>
+        <v>-0.43</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1064,19 +1076,19 @@
         <v>28</v>
       </c>
       <c r="P3">
-        <v>1576.16</v>
+        <v>1564.18</v>
       </c>
       <c r="Q3">
-        <v>1619.55</v>
+        <v>1612.2</v>
       </c>
       <c r="R3">
-        <v>1679.9</v>
+        <v>1673.99</v>
       </c>
       <c r="S3">
-        <v>1813.55</v>
+        <v>1811.25</v>
       </c>
       <c r="T3">
-        <v>-13.6</v>
+        <v>-15.14</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1091,43 +1103,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.91</v>
+        <v>28.16</v>
       </c>
       <c r="Z3">
-        <v>-28.52</v>
+        <v>-31.2</v>
       </c>
       <c r="AA3">
-        <v>-25.5</v>
+        <v>-26.64</v>
       </c>
       <c r="AB3">
-        <v>-3.02</v>
+        <v>-4.56</v>
       </c>
       <c r="AC3">
         <v>9.65</v>
       </c>
       <c r="AD3">
-        <v>4.79</v>
+        <v>8</v>
       </c>
       <c r="AE3">
-        <v>33.95</v>
+        <v>34.8</v>
       </c>
       <c r="AF3">
-        <v>-58.08</v>
+        <v>-41.99</v>
       </c>
       <c r="AG3">
-        <v>1681.69</v>
+        <v>1676.96</v>
       </c>
       <c r="AH3">
-        <v>1557.4</v>
+        <v>1547.43</v>
       </c>
       <c r="AI3">
-        <v>1656.31</v>
+        <v>1642.14</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>27.26</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1150,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>495.45</v>
+        <v>499.5</v>
       </c>
       <c r="D4">
-        <v>-4.18</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,46 +1162,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.78</v>
+        <v>-27.19</v>
       </c>
       <c r="H4">
-        <v>7.61</v>
+        <v>8.49</v>
       </c>
       <c r="I4">
-        <v>-2.85</v>
+        <v>-3.02</v>
       </c>
       <c r="J4">
-        <v>-5.15</v>
+        <v>-2.74</v>
       </c>
       <c r="K4">
-        <v>4.25</v>
+        <v>5.06</v>
       </c>
       <c r="L4">
-        <v>-18.44</v>
+        <v>-16.44</v>
       </c>
       <c r="M4">
-        <v>-5.38</v>
+        <v>-5.73</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>508.71</v>
+        <v>505.6</v>
       </c>
       <c r="Q4">
-        <v>506.85</v>
+        <v>506</v>
       </c>
       <c r="R4">
-        <v>503.55</v>
+        <v>503.57</v>
       </c>
       <c r="S4">
-        <v>566.9</v>
+        <v>566.26</v>
       </c>
       <c r="T4">
-        <v>-12.6</v>
+        <v>-11.79</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.21</v>
+        <v>45.83</v>
       </c>
       <c r="Z4">
-        <v>0.61</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA4">
-        <v>1.2</v>
+        <v>0.95</v>
       </c>
       <c r="AB4">
-        <v>-0.59</v>
+        <v>-1.02</v>
       </c>
       <c r="AC4">
-        <v>45.5</v>
+        <v>39.35</v>
       </c>
       <c r="AD4">
-        <v>59.09</v>
+        <v>50.4</v>
       </c>
       <c r="AE4">
-        <v>12.69</v>
+        <v>12.81</v>
       </c>
       <c r="AF4">
-        <v>40.63</v>
+        <v>-29.83</v>
       </c>
       <c r="AG4">
-        <v>519.65</v>
+        <v>518.34</v>
       </c>
       <c r="AH4">
-        <v>494.06</v>
+        <v>493.66</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1240,7 +1252,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.09</v>
+        <v>26.13</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1421,7 +1433,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1473,13 +1485,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>1.3</v>
+        <v>-1.51</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.51</v>
+        <v>-1.93</v>
       </c>
       <c r="E7" s="7">
-        <v>-2.81</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1502,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.5</v>
+        <v>-6.45</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.45</v>
+        <v>-6.55</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.95</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1519,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.32</v>
+        <v>-5.15</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.15</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-5.47</v>
+        <v>-2.74</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.41</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1536,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
       <c r="D10" s="6">
-        <v>1.08</v>
+        <v>-0.24</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.68</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1553,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.28</v>
+        <v>-3.04</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.24</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1570,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.13</v>
+        <v>-2.85</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.85</v>
+        <v>-3.02</v>
       </c>
       <c r="E12" s="7">
-        <v>-3.98</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1587,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="D13" s="6">
-        <v>2.78</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.14</v>
+        <v>2.05</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1604,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>-15.74</v>
+        <v>-15.18</v>
       </c>
       <c r="D14" s="6">
-        <v>-15.18</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.5600000000000001</v>
+        <v>-15.86</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1621,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-15.81</v>
+        <v>-18.44</v>
       </c>
       <c r="D15" s="6">
-        <v>-18.44</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.63</v>
+        <v>-16.44</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1638,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>18.54</v>
+        <v>15.78</v>
       </c>
       <c r="D16" s="6">
-        <v>15.78</v>
+        <v>13.97</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.76</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1655,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-10.28</v>
+        <v>-9.99</v>
       </c>
       <c r="D17" s="6">
-        <v>-9.99</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.29</v>
+        <v>-11.3</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1672,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>7.54</v>
+        <v>4.25</v>
       </c>
       <c r="D18" s="6">
-        <v>4.25</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.29</v>
+        <v>5.06</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,81 +1689,81 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.62</v>
+        <v>-1.72</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.72</v>
+        <v>-2.5</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.1</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-24.64</v>
+        <v>-23.01</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.78</v>
+        <v>-24.48</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.14</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>1454</v>
+        <v>-27.78</v>
       </c>
       <c r="D21" s="6">
-        <v>1438</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-16</v>
+        <v>-27.19</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>517.05</v>
+        <v>1438</v>
       </c>
       <c r="D22" s="6">
-        <v>495.45</v>
+        <v>1426.5</v>
       </c>
       <c r="E22" s="7">
-        <v>-21.6</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>59.75</v>
+        <v>1566.9</v>
       </c>
       <c r="D23" s="6">
-        <v>54.17</v>
+        <v>1537</v>
       </c>
       <c r="E23" s="7">
-        <v>-5.58</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1759,16 +1771,16 @@
         <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>56.8</v>
+        <v>495.45</v>
       </c>
       <c r="D24" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-13.59</v>
+        <v>499.5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>4.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1776,16 +1788,16 @@
         <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>67.56</v>
+        <v>54.17</v>
       </c>
       <c r="D25" s="6">
-        <v>12.04</v>
+        <v>50.51</v>
       </c>
       <c r="E25" s="7">
-        <v>-55.52</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1793,16 +1805,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>38.11</v>
+        <v>32.91</v>
       </c>
       <c r="D26" s="6">
-        <v>-58.08</v>
+        <v>28.16</v>
       </c>
       <c r="E26" s="7">
-        <v>-96.19</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1810,16 +1822,67 @@
         <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>43.21</v>
+      </c>
+      <c r="D27" s="6">
+        <v>45.83</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6">
-        <v>138.67</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="6">
+        <v>12.04</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-11.29</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-23.33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-58.08</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-41.99</v>
+      </c>
+      <c r="E29" s="8">
+        <v>16.09</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
         <v>40.63</v>
       </c>
-      <c r="E27" s="7">
-        <v>-98.04000000000001</v>
+      <c r="D30" s="6">
+        <v>-29.83</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-70.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1884,16 +1947,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>43.4</v>
+        <v>41.5</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
       <c r="G2" s="11">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2012,13 +2075,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.1554</v>
+        <v>0.1519</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.001</v>
+        <v>-0.0043</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0538</v>
+        <v>-0.0573</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.7% → -2.5%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.7%</t>
-  </si>
-  <si>
-    <t>-2.5%</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -239,7 +212,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -273,7 +246,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -285,15 +258,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,19 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,22 +362,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -426,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -785,13 +744,16 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -924,10 +886,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1426.5</v>
+        <v>1430</v>
       </c>
       <c r="D2">
-        <v>-0.8</v>
+        <v>0.25</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -936,46 +898,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.5</v>
+        <v>-2.26</v>
       </c>
       <c r="H2">
-        <v>18.29</v>
+        <v>18.58</v>
       </c>
       <c r="I2">
-        <v>-0.24</v>
+        <v>-0.9</v>
       </c>
       <c r="J2">
-        <v>-1.93</v>
+        <v>-1.39</v>
       </c>
       <c r="K2">
-        <v>13.97</v>
+        <v>13.3</v>
       </c>
       <c r="L2">
-        <v>2.05</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
-        <v>15.19</v>
+        <v>15.28</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>1436.86</v>
+        <v>1434.26</v>
       </c>
       <c r="Q2">
-        <v>1425.43</v>
+        <v>1424.06</v>
       </c>
       <c r="R2">
-        <v>1422.07</v>
+        <v>1423.2</v>
       </c>
       <c r="S2">
-        <v>1355.13</v>
+        <v>1355.38</v>
       </c>
       <c r="T2">
-        <v>5.27</v>
+        <v>5.51</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -990,34 +952,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.51</v>
+        <v>51.58</v>
       </c>
       <c r="Z2">
-        <v>4.36</v>
+        <v>4.06</v>
       </c>
       <c r="AA2">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AB2">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="AC2">
-        <v>69.45999999999999</v>
+        <v>52.63</v>
       </c>
       <c r="AD2">
-        <v>74.03</v>
+        <v>64.22</v>
       </c>
       <c r="AE2">
-        <v>22.08</v>
+        <v>22.33</v>
       </c>
       <c r="AF2">
-        <v>-11.29</v>
+        <v>10.35</v>
       </c>
       <c r="AG2">
-        <v>1454.58</v>
+        <v>1449.15</v>
       </c>
       <c r="AH2">
-        <v>1396.28</v>
+        <v>1398.96</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1026,7 +988,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.32</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,58 +999,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1537</v>
+        <v>1521.7</v>
       </c>
       <c r="D3">
-        <v>-1.91</v>
+        <v>-1</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1537</v>
+        <v>1521.7</v>
       </c>
       <c r="G3">
-        <v>-24.48</v>
+        <v>-25.23</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.75</v>
+        <v>-4.18</v>
       </c>
       <c r="J3">
-        <v>-6.55</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="K3">
-        <v>-11.3</v>
+        <v>-13.44</v>
       </c>
       <c r="L3">
-        <v>-15.86</v>
+        <v>-16.73</v>
       </c>
       <c r="M3">
-        <v>-0.43</v>
+        <v>-0.64</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>1564.18</v>
+        <v>1550.9</v>
       </c>
       <c r="Q3">
-        <v>1612.2</v>
+        <v>1605.38</v>
       </c>
       <c r="R3">
-        <v>1673.99</v>
+        <v>1668</v>
       </c>
       <c r="S3">
-        <v>1811.25</v>
+        <v>1808.68</v>
       </c>
       <c r="T3">
-        <v>-15.14</v>
+        <v>-15.87</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1103,43 +1065,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.16</v>
+        <v>26.09</v>
       </c>
       <c r="Z3">
-        <v>-31.2</v>
+        <v>-34.17</v>
       </c>
       <c r="AA3">
-        <v>-26.64</v>
+        <v>-28.15</v>
       </c>
       <c r="AB3">
-        <v>-4.56</v>
+        <v>-6.02</v>
       </c>
       <c r="AC3">
-        <v>9.65</v>
+        <v>4.94</v>
       </c>
       <c r="AD3">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="AE3">
-        <v>34.8</v>
+        <v>34.55</v>
       </c>
       <c r="AF3">
-        <v>-41.99</v>
+        <v>-48.55</v>
       </c>
       <c r="AG3">
-        <v>1676.96</v>
+        <v>1678.05</v>
       </c>
       <c r="AH3">
-        <v>1547.43</v>
+        <v>1532.71</v>
       </c>
       <c r="AI3">
-        <v>1642.14</v>
+        <v>1629.39</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>31.5</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1112,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>499.5</v>
+        <v>495.05</v>
       </c>
       <c r="D4">
-        <v>0.82</v>
+        <v>-0.89</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1162,46 +1124,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.19</v>
+        <v>-27.84</v>
       </c>
       <c r="H4">
-        <v>8.49</v>
+        <v>7.53</v>
       </c>
       <c r="I4">
-        <v>-3.02</v>
+        <v>-2.93</v>
       </c>
       <c r="J4">
-        <v>-2.74</v>
+        <v>-4.16</v>
       </c>
       <c r="K4">
-        <v>5.06</v>
+        <v>2.44</v>
       </c>
       <c r="L4">
-        <v>-16.44</v>
+        <v>-18.4</v>
       </c>
       <c r="M4">
-        <v>-5.73</v>
+        <v>-6.49</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P4">
-        <v>505.6</v>
+        <v>502.61</v>
       </c>
       <c r="Q4">
-        <v>506</v>
+        <v>505.4</v>
       </c>
       <c r="R4">
-        <v>503.57</v>
+        <v>503.54</v>
       </c>
       <c r="S4">
-        <v>566.26</v>
+        <v>565.59</v>
       </c>
       <c r="T4">
-        <v>-11.79</v>
+        <v>-12.47</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1216,34 +1178,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>45.83</v>
+        <v>43.46</v>
       </c>
       <c r="Z4">
-        <v>-0.07000000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="AA4">
-        <v>0.95</v>
+        <v>0.57</v>
       </c>
       <c r="AB4">
-        <v>-1.02</v>
+        <v>-1.53</v>
       </c>
       <c r="AC4">
-        <v>39.35</v>
+        <v>6.96</v>
       </c>
       <c r="AD4">
-        <v>50.4</v>
+        <v>30.61</v>
       </c>
       <c r="AE4">
-        <v>12.81</v>
+        <v>12.75</v>
       </c>
       <c r="AF4">
-        <v>-29.83</v>
+        <v>-63.31</v>
       </c>
       <c r="AG4">
-        <v>518.34</v>
+        <v>518.66</v>
       </c>
       <c r="AH4">
-        <v>493.66</v>
+        <v>492.15</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1252,7 +1214,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>26.13</v>
+        <v>23.68</v>
       </c>
     </row>
   </sheetData>
@@ -1413,47 +1375,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1461,428 +1388,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-1.51</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-1.93</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.42</v>
+      <c r="D7" s="5">
+        <v>-1.39</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-6.55</v>
       </c>
+      <c r="D8" s="5">
+        <v>-9.640000000000001</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.1</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.15</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-2.74</v>
       </c>
-      <c r="E9" s="8">
-        <v>2.41</v>
+      <c r="D9" s="5">
+        <v>-4.16</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>1.08</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-0.24</v>
       </c>
+      <c r="D10" s="5">
+        <v>-0.9</v>
+      </c>
       <c r="E10" s="7">
-        <v>-1.32</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-3.75</v>
       </c>
+      <c r="D11" s="5">
+        <v>-4.18</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.71</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-3.02</v>
       </c>
-      <c r="E12" s="7">
-        <v>-0.17</v>
+      <c r="D12" s="5">
+        <v>-2.93</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>2.78</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>2.05</v>
       </c>
+      <c r="D13" s="5">
+        <v>1.35</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.73</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-15.18</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-15.86</v>
       </c>
+      <c r="D14" s="5">
+        <v>-16.73</v>
+      </c>
       <c r="E14" s="7">
-        <v>-0.68</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-18.44</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-16.44</v>
       </c>
-      <c r="E15" s="8">
+      <c r="D15" s="5">
+        <v>-18.4</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>13.97</v>
+      </c>
+      <c r="D16" s="5">
+        <v>13.3</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-11.3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-13.44</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5.06</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-2.5</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-24.48</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-25.23</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-27.19</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-27.84</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="C22" s="5">
+        <v>1426.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1430</v>
+      </c>
+      <c r="E22" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1537</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1521.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>499.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>495.05</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>15.78</v>
-      </c>
-      <c r="D16" s="6">
-        <v>13.97</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>50.51</v>
+      </c>
+      <c r="D25" s="5">
+        <v>51.58</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-9.99</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>28.16</v>
+      </c>
+      <c r="D26" s="5">
+        <v>26.09</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.25</v>
-      </c>
-      <c r="D18" s="6">
-        <v>5.06</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>45.83</v>
+      </c>
+      <c r="D27" s="5">
+        <v>43.46</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-11.29</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10.35</v>
+      </c>
+      <c r="E28" s="6">
+        <v>21.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-23.01</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-24.48</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-41.99</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-48.55</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-6.56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-27.78</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-27.19</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1438</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1426.5</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1566.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1537</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-29.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>495.45</v>
-      </c>
-      <c r="D24" s="6">
-        <v>499.5</v>
-      </c>
-      <c r="E24" s="8">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>54.17</v>
-      </c>
-      <c r="D25" s="6">
-        <v>50.51</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>32.91</v>
-      </c>
-      <c r="D26" s="6">
-        <v>28.16</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="D27" s="6">
-        <v>45.83</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>12.04</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-11.29</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-23.33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-58.08</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-41.99</v>
-      </c>
-      <c r="E29" s="8">
-        <v>16.09</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>40.63</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-29.83</v>
       </c>
+      <c r="D30" s="5">
+        <v>-63.31</v>
+      </c>
       <c r="E30" s="7">
-        <v>-70.45999999999999</v>
+        <v>-33.48</v>
       </c>
     </row>
   </sheetData>
@@ -1908,60 +1835,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2063,25 +1990,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1519</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0043</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0573</v>
+      <c r="A2" s="13">
+        <v>0.1528</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0064</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0649</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.6 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -744,9 +772,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -886,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1430</v>
+        <v>1423.2</v>
       </c>
       <c r="D2">
-        <v>0.25</v>
+        <v>-0.48</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -898,22 +924,22 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.26</v>
+        <v>-2.73</v>
       </c>
       <c r="H2">
-        <v>18.58</v>
+        <v>18.02</v>
       </c>
       <c r="I2">
-        <v>-0.9</v>
+        <v>0.03</v>
       </c>
       <c r="J2">
-        <v>-1.39</v>
+        <v>-2.35</v>
       </c>
       <c r="K2">
-        <v>13.3</v>
+        <v>13.84</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="M2">
         <v>15.28</v>
@@ -922,22 +948,22 @@
         <v>99</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>1434.26</v>
+        <v>1434.34</v>
       </c>
       <c r="Q2">
-        <v>1424.06</v>
+        <v>1424.17</v>
       </c>
       <c r="R2">
-        <v>1423.2</v>
+        <v>1423.91</v>
       </c>
       <c r="S2">
-        <v>1355.38</v>
+        <v>1355.63</v>
       </c>
       <c r="T2">
-        <v>5.51</v>
+        <v>4.98</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -952,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.58</v>
+        <v>49.35</v>
       </c>
       <c r="Z2">
-        <v>4.06</v>
+        <v>3.23</v>
       </c>
       <c r="AA2">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="AB2">
-        <v>0.16</v>
+        <v>-0.53</v>
       </c>
       <c r="AC2">
-        <v>52.63</v>
+        <v>42.71</v>
       </c>
       <c r="AD2">
-        <v>64.22</v>
+        <v>54.93</v>
       </c>
       <c r="AE2">
-        <v>22.33</v>
+        <v>21.94</v>
       </c>
       <c r="AF2">
-        <v>10.35</v>
+        <v>-28.81</v>
       </c>
       <c r="AG2">
-        <v>1449.15</v>
+        <v>1449.22</v>
       </c>
       <c r="AH2">
-        <v>1398.96</v>
+        <v>1399.11</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -988,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>27.28</v>
+        <v>26.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -999,58 +1025,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1521.7</v>
+        <v>1510</v>
       </c>
       <c r="D3">
-        <v>-1</v>
+        <v>-0.77</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1521.7</v>
+        <v>1510</v>
       </c>
       <c r="G3">
-        <v>-25.23</v>
+        <v>-25.8</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.18</v>
+        <v>-3.33</v>
       </c>
       <c r="J3">
-        <v>-9.640000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="K3">
-        <v>-13.44</v>
+        <v>-13.14</v>
       </c>
       <c r="L3">
-        <v>-16.73</v>
+        <v>-16.57</v>
       </c>
       <c r="M3">
-        <v>-0.64</v>
+        <v>0.03</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>1550.9</v>
+        <v>1540.5</v>
       </c>
       <c r="Q3">
-        <v>1605.38</v>
+        <v>1598.93</v>
       </c>
       <c r="R3">
-        <v>1668</v>
+        <v>1661.93</v>
       </c>
       <c r="S3">
-        <v>1808.68</v>
+        <v>1806.14</v>
       </c>
       <c r="T3">
-        <v>-15.87</v>
+        <v>-16.4</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1065,43 +1091,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>26.09</v>
+        <v>24.6</v>
       </c>
       <c r="Z3">
-        <v>-34.17</v>
+        <v>-37.04</v>
       </c>
       <c r="AA3">
-        <v>-28.15</v>
+        <v>-29.92</v>
       </c>
       <c r="AB3">
-        <v>-6.02</v>
+        <v>-7.11</v>
       </c>
       <c r="AC3">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>8.08</v>
+        <v>4.86</v>
       </c>
       <c r="AE3">
-        <v>34.55</v>
+        <v>33.97</v>
       </c>
       <c r="AF3">
-        <v>-48.55</v>
+        <v>-11.58</v>
       </c>
       <c r="AG3">
-        <v>1678.05</v>
+        <v>1681.29</v>
       </c>
       <c r="AH3">
-        <v>1532.71</v>
+        <v>1516.57</v>
       </c>
       <c r="AI3">
-        <v>1629.39</v>
+        <v>1622.5</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>35.81</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1112,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>495.05</v>
+        <v>494.55</v>
       </c>
       <c r="D4">
-        <v>-0.89</v>
+        <v>-0.1</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1124,46 +1150,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.84</v>
+        <v>-27.92</v>
       </c>
       <c r="H4">
-        <v>7.53</v>
+        <v>7.42</v>
       </c>
       <c r="I4">
-        <v>-2.93</v>
+        <v>-2.26</v>
       </c>
       <c r="J4">
-        <v>-4.16</v>
+        <v>-2.46</v>
       </c>
       <c r="K4">
-        <v>2.44</v>
+        <v>4.03</v>
       </c>
       <c r="L4">
-        <v>-18.4</v>
+        <v>-18.73</v>
       </c>
       <c r="M4">
-        <v>-6.49</v>
+        <v>-6.41</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>502.61</v>
+        <v>500.32</v>
       </c>
       <c r="Q4">
-        <v>505.4</v>
+        <v>505.08</v>
       </c>
       <c r="R4">
-        <v>503.54</v>
+        <v>503.61</v>
       </c>
       <c r="S4">
-        <v>565.59</v>
+        <v>564.9400000000001</v>
       </c>
       <c r="T4">
-        <v>-12.47</v>
+        <v>-12.46</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1178,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.46</v>
+        <v>43.19</v>
       </c>
       <c r="Z4">
-        <v>-0.96</v>
+        <v>-1.69</v>
       </c>
       <c r="AA4">
-        <v>0.57</v>
+        <v>0.12</v>
       </c>
       <c r="AB4">
-        <v>-1.53</v>
+        <v>-1.8</v>
       </c>
       <c r="AC4">
         <v>6.96</v>
       </c>
       <c r="AD4">
-        <v>30.61</v>
+        <v>17.76</v>
       </c>
       <c r="AE4">
-        <v>12.75</v>
+        <v>12.63</v>
       </c>
       <c r="AF4">
-        <v>-63.31</v>
+        <v>-27.86</v>
       </c>
       <c r="AG4">
-        <v>518.66</v>
+        <v>519.08</v>
       </c>
       <c r="AH4">
-        <v>492.15</v>
+        <v>491.07</v>
       </c>
       <c r="AI4">
         <v>483.02</v>
@@ -1214,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.68</v>
+        <v>21.38</v>
       </c>
     </row>
   </sheetData>
@@ -1375,12 +1401,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1388,428 +1449,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-1.93</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-1.39</v>
       </c>
-      <c r="E7" s="6">
+      <c r="D7" s="6">
+        <v>-2.35</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-8.93</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-4.16</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.93</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.08</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-16.73</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-16.57</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-18.4</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-18.73</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>13.3</v>
+      </c>
+      <c r="D16" s="6">
+        <v>13.84</v>
+      </c>
+      <c r="E16" s="8">
         <v>0.54</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-6.55</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-13.44</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-13.14</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-2.74</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-4.16</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="D18" s="6">
+        <v>4.03</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.24</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-3.75</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-25.23</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-25.8</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.02</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-2.93</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-27.84</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-27.92</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>2.05</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.35</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1430</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1423.2</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-15.86</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-16.73</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1521.7</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1510</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-11.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-16.44</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-18.4</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>495.05</v>
+      </c>
+      <c r="D24" s="6">
+        <v>494.55</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>13.97</v>
-      </c>
-      <c r="D16" s="5">
-        <v>13.3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>51.58</v>
+      </c>
+      <c r="D25" s="6">
+        <v>49.35</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-11.3</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-13.44</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>26.09</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.6</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>5.06</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>43.46</v>
+      </c>
+      <c r="D27" s="6">
+        <v>43.19</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-2.5</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>10.35</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-28.81</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-39.16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-24.48</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-25.23</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-48.55</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-11.58</v>
+      </c>
+      <c r="E29" s="8">
+        <v>36.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-27.19</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-27.84</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1426.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1430</v>
-      </c>
-      <c r="E22" s="6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1537</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1521.7</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>499.5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>495.05</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>50.51</v>
-      </c>
-      <c r="D25" s="5">
-        <v>51.58</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>28.16</v>
-      </c>
-      <c r="D26" s="5">
-        <v>26.09</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>45.83</v>
-      </c>
-      <c r="D27" s="5">
-        <v>43.46</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-11.29</v>
-      </c>
-      <c r="D28" s="5">
-        <v>10.35</v>
-      </c>
-      <c r="E28" s="6">
-        <v>21.64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-41.99</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-48.55</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-6.56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-29.83</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-63.31</v>
       </c>
-      <c r="E30" s="7">
-        <v>-33.48</v>
+      <c r="D30" s="6">
+        <v>-27.86</v>
+      </c>
+      <c r="E30" s="8">
+        <v>35.45</v>
       </c>
     </row>
   </sheetData>
@@ -1835,60 +1896,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>40.4</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="10">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-4.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1990,25 +2051,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>0.1528</v>
       </c>
-      <c r="B2" s="13">
-        <v>-0.0064</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0649</v>
+      <c r="B2" s="14">
+        <v>0.0003</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0641</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -145,12 +145,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -178,16 +178,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.6 → 49.4</t>
+    <t>49.4 → 50.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -397,6 +406,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -912,10 +922,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1423.2</v>
+        <v>1427.5</v>
       </c>
       <c r="D2">
-        <v>-0.48</v>
+        <v>0.3</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -924,88 +934,88 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.73</v>
+        <v>-2.43</v>
       </c>
       <c r="H2">
-        <v>18.02</v>
+        <v>18.38</v>
       </c>
       <c r="I2">
-        <v>0.03</v>
+        <v>-1.82</v>
       </c>
       <c r="J2">
-        <v>-2.35</v>
+        <v>0.46</v>
       </c>
       <c r="K2">
-        <v>13.84</v>
+        <v>11.96</v>
       </c>
       <c r="L2">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="M2">
-        <v>15.28</v>
+        <v>15.47</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>1434.34</v>
+        <v>1429.04</v>
       </c>
       <c r="Q2">
-        <v>1424.17</v>
+        <v>1423.95</v>
       </c>
       <c r="R2">
-        <v>1423.91</v>
+        <v>1424.71</v>
       </c>
       <c r="S2">
-        <v>1355.63</v>
+        <v>1355.85</v>
       </c>
       <c r="T2">
-        <v>4.98</v>
+        <v>5.28</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>49.35</v>
+        <v>50.8</v>
       </c>
       <c r="Z2">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="AA2">
-        <v>3.77</v>
+        <v>3.59</v>
       </c>
       <c r="AB2">
-        <v>-0.53</v>
+        <v>-0.7</v>
       </c>
       <c r="AC2">
-        <v>42.71</v>
+        <v>43.3</v>
       </c>
       <c r="AD2">
-        <v>54.93</v>
+        <v>46.22</v>
       </c>
       <c r="AE2">
-        <v>21.94</v>
+        <v>21.21</v>
       </c>
       <c r="AF2">
-        <v>-28.81</v>
+        <v>-10.97</v>
       </c>
       <c r="AG2">
-        <v>1449.22</v>
+        <v>1448.8</v>
       </c>
       <c r="AH2">
-        <v>1399.11</v>
+        <v>1399.1</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1014,7 +1024,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.47</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,109 +1035,109 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1510</v>
+        <v>1493.4</v>
       </c>
       <c r="D3">
-        <v>-0.77</v>
+        <v>-1.1</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1510</v>
+        <v>1493.4</v>
       </c>
       <c r="G3">
-        <v>-25.8</v>
+        <v>-26.62</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.33</v>
+        <v>-4.69</v>
       </c>
       <c r="J3">
-        <v>-8.93</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="K3">
-        <v>-13.14</v>
+        <v>-15.99</v>
       </c>
       <c r="L3">
-        <v>-16.57</v>
+        <v>-17.46</v>
       </c>
       <c r="M3">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>1540.5</v>
+        <v>1525.8</v>
       </c>
       <c r="Q3">
-        <v>1598.93</v>
+        <v>1591.16</v>
       </c>
       <c r="R3">
-        <v>1661.93</v>
+        <v>1656.44</v>
       </c>
       <c r="S3">
-        <v>1806.14</v>
+        <v>1803.44</v>
       </c>
       <c r="T3">
-        <v>-16.4</v>
+        <v>-17.19</v>
       </c>
       <c r="U3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X3">
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>24.6</v>
+        <v>22.62</v>
       </c>
       <c r="Z3">
-        <v>-37.04</v>
+        <v>-40.19</v>
       </c>
       <c r="AA3">
-        <v>-29.92</v>
+        <v>-31.98</v>
       </c>
       <c r="AB3">
-        <v>-7.11</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>4.86</v>
+        <v>1.65</v>
       </c>
       <c r="AE3">
-        <v>33.97</v>
+        <v>33.25</v>
       </c>
       <c r="AF3">
-        <v>-11.58</v>
+        <v>-51.84</v>
       </c>
       <c r="AG3">
-        <v>1681.29</v>
+        <v>1682.54</v>
       </c>
       <c r="AH3">
-        <v>1516.57</v>
+        <v>1499.78</v>
       </c>
       <c r="AI3">
-        <v>1622.5</v>
+        <v>1604.79</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>39.69</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1148,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>494.55</v>
+        <v>470.65</v>
       </c>
       <c r="D4">
-        <v>-0.1</v>
+        <v>-4.83</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1150,97 +1160,97 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-27.92</v>
+        <v>-31.4</v>
       </c>
       <c r="H4">
-        <v>7.42</v>
+        <v>2.23</v>
       </c>
       <c r="I4">
-        <v>-2.26</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="J4">
-        <v>-2.46</v>
+        <v>-6.07</v>
       </c>
       <c r="K4">
-        <v>4.03</v>
+        <v>-0.86</v>
       </c>
       <c r="L4">
-        <v>-18.73</v>
+        <v>-22.49</v>
       </c>
       <c r="M4">
-        <v>-6.41</v>
+        <v>-7.54</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>500.32</v>
+        <v>491.04</v>
       </c>
       <c r="Q4">
-        <v>505.08</v>
+        <v>503.62</v>
       </c>
       <c r="R4">
-        <v>503.61</v>
+        <v>503.23</v>
       </c>
       <c r="S4">
-        <v>564.9400000000001</v>
+        <v>564.24</v>
       </c>
       <c r="T4">
-        <v>-12.46</v>
+        <v>-16.59</v>
       </c>
       <c r="U4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" t="s">
         <v>41</v>
       </c>
-      <c r="V4" t="s">
-        <v>42</v>
-      </c>
       <c r="W4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.19</v>
+        <v>32.72</v>
       </c>
       <c r="Z4">
-        <v>-1.69</v>
+        <v>-4.14</v>
       </c>
       <c r="AA4">
-        <v>0.12</v>
+        <v>-0.74</v>
       </c>
       <c r="AB4">
-        <v>-1.8</v>
+        <v>-3.41</v>
       </c>
       <c r="AC4">
-        <v>6.96</v>
+        <v>0.6</v>
       </c>
       <c r="AD4">
-        <v>17.76</v>
+        <v>4.84</v>
       </c>
       <c r="AE4">
-        <v>12.63</v>
+        <v>13.43</v>
       </c>
       <c r="AF4">
-        <v>-27.86</v>
+        <v>35.96</v>
       </c>
       <c r="AG4">
-        <v>519.08</v>
+        <v>524.38</v>
       </c>
       <c r="AH4">
-        <v>491.07</v>
+        <v>482.87</v>
       </c>
       <c r="AI4">
-        <v>483.02</v>
+        <v>521.62</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>21.38</v>
+        <v>23.94</v>
       </c>
     </row>
   </sheetData>
@@ -1381,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1439,444 +1449,484 @@
         <v>55</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="D5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C9" s="7">
         <v>-2.35</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D9" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>-8.93</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.16</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="7">
         <v>-2.46</v>
       </c>
-      <c r="E9" s="8">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-6.07</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C12" s="7">
         <v>0.03</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-1.82</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>-4.18</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C13" s="7">
         <v>-3.33</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C14" s="7">
         <v>-2.26</v>
       </c>
-      <c r="E12" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-6.71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
-        <v>1.35</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C15" s="7">
         <v>2.08</v>
       </c>
-      <c r="E13" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D15" s="7">
+        <v>2.18</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="6">
-        <v>-16.73</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C16" s="7">
         <v>-16.57</v>
       </c>
-      <c r="E14" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-17.46</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
-        <v>-18.4</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C17" s="7">
         <v>-18.73</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D17" s="7">
+        <v>-22.49</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-3.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="6">
-        <v>13.3</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C18" s="7">
         <v>13.84</v>
       </c>
-      <c r="E16" s="8">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D18" s="7">
+        <v>11.96</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6">
-        <v>-13.44</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C19" s="7">
         <v>-13.14</v>
       </c>
-      <c r="E17" s="8">
+      <c r="D19" s="7">
+        <v>-15.99</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="7">
+        <v>4.03</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-0.86</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-4.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-2.73</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-2.43</v>
+      </c>
+      <c r="E21" s="8">
         <v>0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-25.8</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-26.62</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="D18" s="6">
-        <v>4.03</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-27.92</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-31.4</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-3.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1423.2</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1427.5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-25.23</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-25.8</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="7">
+        <v>1510</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1493.4</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-16.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-27.84</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-27.92</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="7">
+        <v>494.55</v>
+      </c>
+      <c r="D26" s="7">
+        <v>470.65</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-23.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1430</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1423.2</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="7">
+        <v>49.35</v>
+      </c>
+      <c r="D27" s="7">
+        <v>50.8</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1521.7</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1510</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-11.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="D28" s="7">
+        <v>22.62</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>495.05</v>
-      </c>
-      <c r="D24" s="6">
-        <v>494.55</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="7">
+        <v>43.19</v>
+      </c>
+      <c r="D29" s="7">
+        <v>32.72</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-10.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>51.58</v>
-      </c>
-      <c r="D25" s="6">
-        <v>49.35</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-28.81</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-10.97</v>
+      </c>
+      <c r="E30" s="8">
+        <v>17.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>26.09</v>
-      </c>
-      <c r="D26" s="6">
-        <v>24.6</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-11.58</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-51.84</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-40.26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>43.46</v>
-      </c>
-      <c r="D27" s="6">
-        <v>43.19</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-28.81</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-39.16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-48.55</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-11.58</v>
-      </c>
-      <c r="E29" s="8">
-        <v>36.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-63.31</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C32" s="7">
         <v>-27.86</v>
       </c>
-      <c r="E30" s="8">
-        <v>35.45</v>
+      <c r="D32" s="7">
+        <v>35.96</v>
+      </c>
+      <c r="E32" s="8">
+        <v>63.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1896,61 +1946,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>39</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>35.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>1.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-4.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-1.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
-        <v>30</v>
+      <c r="I2" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2051,25 +2101,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1528</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0003</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0641</v>
+      <c r="A2" s="15">
+        <v>0.1547</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0052</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.07539999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,25 +178,22 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.4 → 50.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>50.8 → 42.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.8</t>
   </si>
   <si>
+    <t>42.3</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -406,7 +403,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -922,10 +918,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1427.5</v>
+        <v>1399.4</v>
       </c>
       <c r="D2">
-        <v>0.3</v>
+        <v>-1.97</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -934,46 +930,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-2.43</v>
+        <v>-4.35</v>
       </c>
       <c r="H2">
-        <v>18.38</v>
+        <v>16.05</v>
       </c>
       <c r="I2">
-        <v>-1.82</v>
+        <v>-2.68</v>
       </c>
       <c r="J2">
-        <v>0.46</v>
+        <v>-2.26</v>
       </c>
       <c r="K2">
-        <v>11.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L2">
-        <v>2.18</v>
+        <v>-0.43</v>
       </c>
       <c r="M2">
-        <v>15.47</v>
+        <v>14.88</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>1429.04</v>
+        <v>1421.32</v>
       </c>
       <c r="Q2">
-        <v>1423.95</v>
+        <v>1422.44</v>
       </c>
       <c r="R2">
-        <v>1424.71</v>
+        <v>1425.2</v>
       </c>
       <c r="S2">
-        <v>1355.85</v>
+        <v>1355.94</v>
       </c>
       <c r="T2">
-        <v>5.28</v>
+        <v>3.21</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -988,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>50.8</v>
+        <v>42.28</v>
       </c>
       <c r="Z2">
-        <v>2.89</v>
+        <v>0.35</v>
       </c>
       <c r="AA2">
-        <v>3.59</v>
+        <v>2.95</v>
       </c>
       <c r="AB2">
-        <v>-0.7</v>
+        <v>-2.59</v>
       </c>
       <c r="AC2">
-        <v>43.3</v>
+        <v>26.8</v>
       </c>
       <c r="AD2">
-        <v>46.22</v>
+        <v>37.6</v>
       </c>
       <c r="AE2">
-        <v>21.21</v>
+        <v>21.93</v>
       </c>
       <c r="AF2">
-        <v>-10.97</v>
+        <v>38.99</v>
       </c>
       <c r="AG2">
-        <v>1448.8</v>
+        <v>1449.43</v>
       </c>
       <c r="AH2">
-        <v>1399.1</v>
+        <v>1395.45</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1024,7 +1020,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.76</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1035,58 +1031,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1493.4</v>
+        <v>1484.4</v>
       </c>
       <c r="D3">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1493.4</v>
+        <v>1484.4</v>
       </c>
       <c r="G3">
-        <v>-26.62</v>
+        <v>-27.06</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.69</v>
+        <v>-5.27</v>
       </c>
       <c r="J3">
-        <v>-8.880000000000001</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K3">
-        <v>-15.99</v>
+        <v>-14.31</v>
       </c>
       <c r="L3">
-        <v>-17.46</v>
+        <v>-20.12</v>
       </c>
       <c r="M3">
-        <v>-0.52</v>
+        <v>-0.9</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>1525.8</v>
+        <v>1509.3</v>
       </c>
       <c r="Q3">
-        <v>1591.16</v>
+        <v>1583.21</v>
       </c>
       <c r="R3">
-        <v>1656.44</v>
+        <v>1651.29</v>
       </c>
       <c r="S3">
-        <v>1803.44</v>
+        <v>1800.71</v>
       </c>
       <c r="T3">
-        <v>-17.19</v>
+        <v>-17.57</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1101,43 +1097,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>22.62</v>
+        <v>21.61</v>
       </c>
       <c r="Z3">
-        <v>-40.19</v>
+        <v>-42.92</v>
       </c>
       <c r="AA3">
-        <v>-31.98</v>
+        <v>-34.16</v>
       </c>
       <c r="AB3">
-        <v>-8.210000000000001</v>
+        <v>-8.75</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>33.25</v>
+        <v>32.93</v>
       </c>
       <c r="AF3">
-        <v>-51.84</v>
+        <v>-48.29</v>
       </c>
       <c r="AG3">
-        <v>1682.54</v>
+        <v>1682.74</v>
       </c>
       <c r="AH3">
-        <v>1499.78</v>
+        <v>1483.67</v>
       </c>
       <c r="AI3">
-        <v>1604.79</v>
+        <v>1587.69</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>43.8</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1148,10 +1144,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>470.65</v>
+        <v>469.3</v>
       </c>
       <c r="D4">
-        <v>-4.83</v>
+        <v>-0.29</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1160,49 +1156,49 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-31.4</v>
+        <v>-31.6</v>
       </c>
       <c r="H4">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="I4">
-        <v>-8.970000000000001</v>
+        <v>-5.28</v>
       </c>
       <c r="J4">
-        <v>-6.07</v>
+        <v>-6.09</v>
       </c>
       <c r="K4">
-        <v>-0.86</v>
+        <v>0.75</v>
       </c>
       <c r="L4">
-        <v>-22.49</v>
+        <v>-21.49</v>
       </c>
       <c r="M4">
-        <v>-7.54</v>
+        <v>-7.99</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>491.04</v>
+        <v>485.81</v>
       </c>
       <c r="Q4">
-        <v>503.62</v>
+        <v>502.01</v>
       </c>
       <c r="R4">
-        <v>503.23</v>
+        <v>502.86</v>
       </c>
       <c r="S4">
-        <v>564.24</v>
+        <v>563.5</v>
       </c>
       <c r="T4">
-        <v>-16.59</v>
+        <v>-16.72</v>
       </c>
       <c r="U4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V4" t="s">
         <v>41</v>
@@ -1211,46 +1207,46 @@
         <v>41</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.72</v>
+        <v>32.25</v>
       </c>
       <c r="Z4">
-        <v>-4.14</v>
+        <v>-6.13</v>
       </c>
       <c r="AA4">
-        <v>-0.74</v>
+        <v>-1.81</v>
       </c>
       <c r="AB4">
-        <v>-3.41</v>
+        <v>-4.31</v>
       </c>
       <c r="AC4">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>4.84</v>
+        <v>2.52</v>
       </c>
       <c r="AE4">
-        <v>13.43</v>
+        <v>13.34</v>
       </c>
       <c r="AF4">
-        <v>35.96</v>
+        <v>-5.94</v>
       </c>
       <c r="AG4">
-        <v>524.38</v>
+        <v>527.84</v>
       </c>
       <c r="AH4">
-        <v>482.87</v>
+        <v>476.19</v>
       </c>
       <c r="AI4">
-        <v>521.62</v>
+        <v>512.3099999999999</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>23.94</v>
+        <v>26.91</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1450,483 +1446,463 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.46</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-6.07</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.68</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.27</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-5.28</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-2.35</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.46</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2.18</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-8.93</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-17.46</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-20.12</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.46</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-6.07</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-22.49</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-21.49</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-1.82</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>11.96</v>
+      </c>
+      <c r="D17" s="6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.33</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-4.69</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-15.99</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-14.31</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-6.71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.86</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.08</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2.18</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.43</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-16.57</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-17.46</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-26.62</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-27.06</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-18.73</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-22.49</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-3.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-31.4</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-31.6</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="7">
-        <v>13.84</v>
-      </c>
-      <c r="D18" s="7">
-        <v>11.96</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1427.5</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1399.4</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-28.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-13.14</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-15.99</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1493.4</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1484.4</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7">
-        <v>4.03</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.86</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-4.89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6">
+        <v>470.65</v>
+      </c>
+      <c r="D25" s="6">
+        <v>469.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-2.73</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.43</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>50.8</v>
+      </c>
+      <c r="D26" s="6">
+        <v>42.28</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-8.52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-25.8</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-26.62</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>22.62</v>
+      </c>
+      <c r="D27" s="6">
+        <v>21.61</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-27.92</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-31.4</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>32.72</v>
+      </c>
+      <c r="D28" s="6">
+        <v>32.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="7">
-        <v>1423.2</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1427.5</v>
-      </c>
-      <c r="E24" s="8">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-10.97</v>
+      </c>
+      <c r="D29" s="6">
+        <v>38.99</v>
+      </c>
+      <c r="E29" s="8">
+        <v>49.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="7">
-        <v>1510</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1493.4</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-16.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-51.84</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-48.29</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="7">
-        <v>494.55</v>
-      </c>
-      <c r="D26" s="7">
-        <v>470.65</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-23.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="7">
-        <v>49.35</v>
-      </c>
-      <c r="D27" s="7">
-        <v>50.8</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="7">
-        <v>24.6</v>
-      </c>
-      <c r="D28" s="7">
-        <v>22.62</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="7">
-        <v>43.19</v>
-      </c>
-      <c r="D29" s="7">
-        <v>32.72</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-10.47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="7">
-        <v>-28.81</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-10.97</v>
-      </c>
-      <c r="E30" s="8">
-        <v>17.84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-11.58</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-51.84</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-40.26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-27.86</v>
-      </c>
-      <c r="D32" s="7">
+      <c r="C31" s="6">
         <v>35.96</v>
       </c>
-      <c r="E32" s="8">
-        <v>63.82</v>
+      <c r="D31" s="6">
+        <v>-5.94</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-41.9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1946,60 +1922,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="12">
-        <v>35.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>32</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="12">
-        <v>-4.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-1.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2101,25 +2077,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="15">
-        <v>0.1547</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0052</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.07539999999999999</v>
+      <c r="A2" s="14">
+        <v>0.1488</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0799</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,40 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.8 → 42.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>42.3</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1399.4</v>
+        <v>1389.1</v>
       </c>
       <c r="D2">
-        <v>-1.97</v>
+        <v>-0.74</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -930,46 +896,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-4.35</v>
+        <v>-5.06</v>
       </c>
       <c r="H2">
-        <v>16.05</v>
+        <v>15.19</v>
       </c>
       <c r="I2">
-        <v>-2.68</v>
+        <v>-2.62</v>
       </c>
       <c r="J2">
-        <v>-2.26</v>
+        <v>-2.83</v>
       </c>
       <c r="K2">
-        <v>8.199999999999999</v>
+        <v>5.47</v>
       </c>
       <c r="L2">
-        <v>-0.43</v>
+        <v>-0.98</v>
       </c>
       <c r="M2">
-        <v>14.88</v>
+        <v>14.74</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>1421.32</v>
+        <v>1413.84</v>
       </c>
       <c r="Q2">
-        <v>1422.44</v>
+        <v>1420.31</v>
       </c>
       <c r="R2">
-        <v>1425.2</v>
+        <v>1425.38</v>
       </c>
       <c r="S2">
-        <v>1355.94</v>
+        <v>1356.03</v>
       </c>
       <c r="T2">
-        <v>3.21</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -984,34 +950,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.28</v>
+        <v>39.65</v>
       </c>
       <c r="Z2">
-        <v>0.35</v>
+        <v>-2.47</v>
       </c>
       <c r="AA2">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB2">
-        <v>-2.59</v>
+        <v>-4.33</v>
       </c>
       <c r="AC2">
-        <v>26.8</v>
+        <v>14.89</v>
       </c>
       <c r="AD2">
-        <v>37.6</v>
+        <v>28.33</v>
       </c>
       <c r="AE2">
-        <v>21.93</v>
+        <v>21.58</v>
       </c>
       <c r="AF2">
-        <v>38.99</v>
+        <v>63.2</v>
       </c>
       <c r="AG2">
-        <v>1449.43</v>
+        <v>1450.72</v>
       </c>
       <c r="AH2">
-        <v>1395.45</v>
+        <v>1389.9</v>
       </c>
       <c r="AI2">
         <v>1386.94</v>
@@ -1020,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.22</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,58 +997,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1484.4</v>
+        <v>1474</v>
       </c>
       <c r="D3">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1484.4</v>
+        <v>1474</v>
       </c>
       <c r="G3">
-        <v>-27.06</v>
+        <v>-27.57</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.27</v>
+        <v>-4.1</v>
       </c>
       <c r="J3">
-        <v>-9.970000000000001</v>
+        <v>-10.31</v>
       </c>
       <c r="K3">
-        <v>-14.31</v>
+        <v>-13.92</v>
       </c>
       <c r="L3">
-        <v>-20.12</v>
+        <v>-19.34</v>
       </c>
       <c r="M3">
-        <v>-0.9</v>
+        <v>-1.18</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P3">
-        <v>1509.3</v>
+        <v>1496.7</v>
       </c>
       <c r="Q3">
-        <v>1583.21</v>
+        <v>1575.16</v>
       </c>
       <c r="R3">
-        <v>1651.29</v>
+        <v>1645.62</v>
       </c>
       <c r="S3">
-        <v>1800.71</v>
+        <v>1798.1</v>
       </c>
       <c r="T3">
-        <v>-17.57</v>
+        <v>-18.02</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1097,16 +1063,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>21.61</v>
+        <v>20.47</v>
       </c>
       <c r="Z3">
-        <v>-42.92</v>
+        <v>-45.39</v>
       </c>
       <c r="AA3">
-        <v>-34.16</v>
+        <v>-36.41</v>
       </c>
       <c r="AB3">
-        <v>-8.75</v>
+        <v>-8.98</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1115,25 +1081,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>32.93</v>
+        <v>32.4</v>
       </c>
       <c r="AF3">
-        <v>-48.29</v>
+        <v>11.44</v>
       </c>
       <c r="AG3">
-        <v>1682.74</v>
+        <v>1682.76</v>
       </c>
       <c r="AH3">
-        <v>1483.67</v>
+        <v>1467.55</v>
       </c>
       <c r="AI3">
-        <v>1587.69</v>
+        <v>1570.15</v>
       </c>
       <c r="AJ3" t="s">
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>48.14</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>469.3</v>
+        <v>462.5</v>
       </c>
       <c r="D4">
-        <v>-0.29</v>
+        <v>-1.45</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1156,25 +1122,25 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-31.6</v>
+        <v>-32.59</v>
       </c>
       <c r="H4">
-        <v>1.93</v>
+        <v>0.46</v>
       </c>
       <c r="I4">
-        <v>-5.28</v>
+        <v>-7.41</v>
       </c>
       <c r="J4">
-        <v>-6.09</v>
+        <v>-7.78</v>
       </c>
       <c r="K4">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="L4">
-        <v>-21.49</v>
+        <v>-22.23</v>
       </c>
       <c r="M4">
-        <v>-7.99</v>
+        <v>-7.72</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1183,19 +1149,19 @@
         <v>31</v>
       </c>
       <c r="P4">
-        <v>485.81</v>
+        <v>478.41</v>
       </c>
       <c r="Q4">
-        <v>502.01</v>
+        <v>499.82</v>
       </c>
       <c r="R4">
-        <v>502.86</v>
+        <v>502.25</v>
       </c>
       <c r="S4">
-        <v>563.5</v>
+        <v>562.77</v>
       </c>
       <c r="T4">
-        <v>-16.72</v>
+        <v>-17.82</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1210,43 +1176,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.25</v>
+        <v>29.89</v>
       </c>
       <c r="Z4">
-        <v>-6.13</v>
+        <v>-8.16</v>
       </c>
       <c r="AA4">
-        <v>-1.81</v>
+        <v>-3.08</v>
       </c>
       <c r="AB4">
-        <v>-4.31</v>
+        <v>-5.07</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2.52</v>
+        <v>0.2</v>
       </c>
       <c r="AE4">
-        <v>13.34</v>
+        <v>13.27</v>
       </c>
       <c r="AF4">
-        <v>-5.94</v>
+        <v>-26.16</v>
       </c>
       <c r="AG4">
-        <v>527.84</v>
+        <v>530.98</v>
       </c>
       <c r="AH4">
-        <v>476.19</v>
+        <v>468.65</v>
       </c>
       <c r="AI4">
-        <v>512.3099999999999</v>
+        <v>502.26</v>
       </c>
       <c r="AJ4" t="s">
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>26.91</v>
+        <v>30.83</v>
       </c>
     </row>
   </sheetData>
@@ -1387,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1407,502 +1373,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.83</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-10.31</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.09</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.78</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.62</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.27</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-5.28</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.41</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.98</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-20.12</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-19.34</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-21.49</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-22.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D16" s="5">
+        <v>5.47</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-14.31</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-13.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D18" s="5">
         <v>0.46</v>
       </c>
-      <c r="D8" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="E18" s="6">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-27.06</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-27.57</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-6.07</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-31.6</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-32.59</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1399.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1389.1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.27</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1484.4</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1474</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-10.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.970000000000001</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>469.3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>462.5</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2.18</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>42.28</v>
+      </c>
+      <c r="D25" s="5">
+        <v>39.65</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-17.46</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-20.12</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>21.61</v>
+      </c>
+      <c r="D26" s="5">
+        <v>20.47</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-22.49</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-21.49</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>32.25</v>
+      </c>
+      <c r="D27" s="5">
+        <v>29.89</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>11.96</v>
-      </c>
-      <c r="D17" s="6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>38.99</v>
+      </c>
+      <c r="D28" s="5">
+        <v>63.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>24.21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-15.99</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-14.31</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-48.29</v>
+      </c>
+      <c r="D29" s="5">
+        <v>11.44</v>
+      </c>
+      <c r="E29" s="7">
+        <v>59.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-26.62</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-27.06</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-31.4</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-31.6</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1427.5</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1399.4</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-28.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1493.4</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1484.4</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>470.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>469.3</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>50.8</v>
-      </c>
-      <c r="D26" s="6">
-        <v>42.28</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-8.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>22.62</v>
-      </c>
-      <c r="D27" s="6">
-        <v>21.61</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>32.72</v>
-      </c>
-      <c r="D28" s="6">
-        <v>32.25</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-10.97</v>
-      </c>
-      <c r="D29" s="6">
-        <v>38.99</v>
-      </c>
-      <c r="E29" s="8">
-        <v>49.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-51.84</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-48.29</v>
-      </c>
-      <c r="E30" s="8">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>35.96</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>-5.94</v>
       </c>
-      <c r="E31" s="7">
-        <v>-41.9</v>
+      <c r="D30" s="5">
+        <v>-26.16</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-20.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1922,60 +1833,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>32</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="E2" s="10">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2077,25 +1988,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.1488</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.009000000000000001</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0799</v>
+      <c r="A2" s="13">
+        <v>0.1474</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0118</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07719999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,16 +151,40 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.9 → 36.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.9</t>
+  </si>
+  <si>
+    <t>36.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +270,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +310,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,17 +386,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -884,10 +909,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1389.1</v>
+        <v>1384.5</v>
       </c>
       <c r="D2">
-        <v>-0.74</v>
+        <v>-0.33</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -896,25 +921,25 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.06</v>
+        <v>-5.37</v>
       </c>
       <c r="H2">
-        <v>15.19</v>
+        <v>14.81</v>
       </c>
       <c r="I2">
-        <v>-2.62</v>
+        <v>-3.18</v>
       </c>
       <c r="J2">
-        <v>-2.83</v>
+        <v>-3.3</v>
       </c>
       <c r="K2">
-        <v>5.47</v>
+        <v>3.26</v>
       </c>
       <c r="L2">
-        <v>-0.98</v>
+        <v>-1.3</v>
       </c>
       <c r="M2">
-        <v>14.74</v>
+        <v>15.1</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -923,19 +948,19 @@
         <v>55</v>
       </c>
       <c r="P2">
-        <v>1413.84</v>
+        <v>1404.74</v>
       </c>
       <c r="Q2">
-        <v>1420.31</v>
+        <v>1419.2</v>
       </c>
       <c r="R2">
-        <v>1425.38</v>
+        <v>1425.07</v>
       </c>
       <c r="S2">
-        <v>1356.03</v>
+        <v>1356.11</v>
       </c>
       <c r="T2">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +975,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>39.65</v>
+        <v>38.5</v>
       </c>
       <c r="Z2">
-        <v>-2.47</v>
+        <v>-5.01</v>
       </c>
       <c r="AA2">
-        <v>1.86</v>
+        <v>0.49</v>
       </c>
       <c r="AB2">
-        <v>-4.33</v>
+        <v>-5.5</v>
       </c>
       <c r="AC2">
-        <v>14.89</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>28.33</v>
+        <v>13.9</v>
       </c>
       <c r="AE2">
-        <v>21.58</v>
+        <v>21.4</v>
       </c>
       <c r="AF2">
-        <v>63.2</v>
+        <v>18.55</v>
       </c>
       <c r="AG2">
-        <v>1450.72</v>
+        <v>1453.13</v>
       </c>
       <c r="AH2">
-        <v>1389.9</v>
+        <v>1385.26</v>
       </c>
       <c r="AI2">
-        <v>1386.94</v>
+        <v>1447.65</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.26</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,58 +1022,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="D3">
-        <v>-0.7</v>
+        <v>-0.61</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="G3">
-        <v>-27.57</v>
+        <v>-28.02</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.1</v>
+        <v>-3.73</v>
       </c>
       <c r="J3">
-        <v>-10.31</v>
+        <v>-10.4</v>
       </c>
       <c r="K3">
-        <v>-13.92</v>
+        <v>-13.61</v>
       </c>
       <c r="L3">
-        <v>-19.34</v>
+        <v>-19.51</v>
       </c>
       <c r="M3">
-        <v>-1.18</v>
+        <v>-1.48</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>1496.7</v>
+        <v>1485.36</v>
       </c>
       <c r="Q3">
-        <v>1575.16</v>
+        <v>1567.01</v>
       </c>
       <c r="R3">
-        <v>1645.62</v>
+        <v>1639.7</v>
       </c>
       <c r="S3">
-        <v>1798.1</v>
+        <v>1795.48</v>
       </c>
       <c r="T3">
-        <v>-18.02</v>
+        <v>-18.41</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>20.47</v>
+        <v>19.51</v>
       </c>
       <c r="Z3">
-        <v>-45.39</v>
+        <v>-47.54</v>
       </c>
       <c r="AA3">
-        <v>-36.41</v>
+        <v>-38.64</v>
       </c>
       <c r="AB3">
-        <v>-8.98</v>
+        <v>-8.9</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1081,25 +1106,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>32.4</v>
+        <v>31.29</v>
       </c>
       <c r="AF3">
-        <v>11.44</v>
+        <v>-65.12</v>
       </c>
       <c r="AG3">
-        <v>1682.76</v>
+        <v>1682.18</v>
       </c>
       <c r="AH3">
-        <v>1467.55</v>
+        <v>1451.83</v>
       </c>
       <c r="AI3">
-        <v>1570.15</v>
+        <v>1561.43</v>
       </c>
       <c r="AJ3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>52.36</v>
+        <v>56.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1135,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>462.5</v>
+        <v>471</v>
       </c>
       <c r="D4">
-        <v>-1.45</v>
+        <v>1.84</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1122,46 +1147,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-32.59</v>
+        <v>-31.35</v>
       </c>
       <c r="H4">
-        <v>0.46</v>
+        <v>2.3</v>
       </c>
       <c r="I4">
-        <v>-7.41</v>
+        <v>-4.86</v>
       </c>
       <c r="J4">
-        <v>-7.78</v>
+        <v>-6.99</v>
       </c>
       <c r="K4">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="L4">
-        <v>-22.23</v>
+        <v>-20.32</v>
       </c>
       <c r="M4">
-        <v>-7.72</v>
+        <v>-7.31</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>478.41</v>
+        <v>473.6</v>
       </c>
       <c r="Q4">
-        <v>499.82</v>
+        <v>498.02</v>
       </c>
       <c r="R4">
-        <v>502.25</v>
+        <v>501.75</v>
       </c>
       <c r="S4">
-        <v>562.77</v>
+        <v>562.1</v>
       </c>
       <c r="T4">
-        <v>-17.82</v>
+        <v>-16.21</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,43 +1201,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.89</v>
+        <v>36.17</v>
       </c>
       <c r="Z4">
-        <v>-8.16</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="AA4">
-        <v>-3.08</v>
+        <v>-4.26</v>
       </c>
       <c r="AB4">
-        <v>-5.07</v>
+        <v>-4.71</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>7.78</v>
       </c>
       <c r="AD4">
-        <v>0.2</v>
+        <v>2.59</v>
       </c>
       <c r="AE4">
-        <v>13.27</v>
+        <v>13.74</v>
       </c>
       <c r="AF4">
-        <v>-26.16</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AG4">
-        <v>530.98</v>
+        <v>531.51</v>
       </c>
       <c r="AH4">
-        <v>468.65</v>
+        <v>464.53</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
       </c>
       <c r="AJ4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.83</v>
+        <v>31.26</v>
       </c>
     </row>
   </sheetData>
@@ -1363,7 +1388,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1373,12 +1398,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1386,428 +1446,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.83</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.57</v>
+      <c r="D7" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-10.31</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.34</v>
+      <c r="D8" s="6">
+        <v>-10.4</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.09</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-7.78</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.69</v>
+      <c r="D9" s="6">
+        <v>-6.99</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.62</v>
       </c>
+      <c r="D10" s="6">
+        <v>-3.18</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-5.27</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-4.1</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.17</v>
+      <c r="D11" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.37</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.28</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-7.41</v>
       </c>
-      <c r="E12" s="6">
-        <v>-2.13</v>
+      <c r="D12" s="6">
+        <v>-4.86</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.43</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-0.98</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.55</v>
+      <c r="D13" s="6">
+        <v>-1.3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>-20.12</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-19.34</v>
       </c>
+      <c r="D14" s="6">
+        <v>-19.51</v>
+      </c>
       <c r="E14" s="7">
-        <v>0.78</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-21.49</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-22.23</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.74</v>
+      <c r="D15" s="6">
+        <v>-20.32</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.91</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>5.47</v>
       </c>
-      <c r="E16" s="6">
-        <v>-2.73</v>
+      <c r="D16" s="6">
+        <v>3.26</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>-14.31</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-13.92</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.39</v>
+      <c r="D17" s="6">
+        <v>-13.61</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>0.46</v>
       </c>
-      <c r="E18" s="6">
-        <v>-0.29</v>
+      <c r="D18" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-4.35</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-5.06</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.71</v>
+      <c r="D19" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-27.06</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-27.57</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.51</v>
+      <c r="D20" s="6">
+        <v>-28.02</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-31.6</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-32.59</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.99</v>
+      <c r="D21" s="6">
+        <v>-31.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>1399.4</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>1389.1</v>
       </c>
-      <c r="E22" s="6">
-        <v>-10.3</v>
+      <c r="D22" s="6">
+        <v>1384.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-4.6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>1484.4</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>1474</v>
       </c>
-      <c r="E23" s="6">
-        <v>-10.4</v>
+      <c r="D23" s="6">
+        <v>1465</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>469.3</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>462.5</v>
       </c>
-      <c r="E24" s="6">
-        <v>-6.8</v>
+      <c r="D24" s="6">
+        <v>471</v>
+      </c>
+      <c r="E24" s="8">
+        <v>8.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>42.28</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>39.65</v>
       </c>
-      <c r="E25" s="6">
-        <v>-2.63</v>
+      <c r="D25" s="6">
+        <v>38.5</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>21.61</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>20.47</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.14</v>
+      <c r="D26" s="6">
+        <v>19.51</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>32.25</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>29.89</v>
       </c>
-      <c r="E27" s="6">
-        <v>-2.36</v>
+      <c r="D27" s="6">
+        <v>36.17</v>
+      </c>
+      <c r="E27" s="8">
+        <v>6.28</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>38.99</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>63.2</v>
       </c>
+      <c r="D28" s="6">
+        <v>18.55</v>
+      </c>
       <c r="E28" s="7">
-        <v>24.21</v>
+        <v>-44.65</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-48.29</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>11.44</v>
       </c>
+      <c r="D29" s="6">
+        <v>-65.12</v>
+      </c>
       <c r="E29" s="7">
-        <v>59.73</v>
+        <v>-76.56</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-5.94</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-26.16</v>
       </c>
-      <c r="E30" s="6">
-        <v>-20.22</v>
+      <c r="D30" s="6">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>100.65</v>
       </c>
     </row>
   </sheetData>
@@ -1833,60 +1893,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="11">
+        <v>31.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="E2" s="10">
-        <v>30</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-3.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1988,25 +2048,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.1474</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0118</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.07719999999999999</v>
+      <c r="A2" s="14">
+        <v>0.151</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0148</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0731</v>
       </c>
     </row>
   </sheetData>

--- a/ICICI_GROUP_Technical_Metrics.xlsx
+++ b/ICICI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,34 +157,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.9 → 36.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.9</t>
-  </si>
-  <si>
-    <t>36.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -386,18 +359,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -909,10 +881,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>1384.5</v>
+        <v>1379.3</v>
       </c>
       <c r="D2">
-        <v>-0.33</v>
+        <v>-0.38</v>
       </c>
       <c r="E2">
         <v>1463.1</v>
@@ -921,46 +893,46 @@
         <v>1205.9</v>
       </c>
       <c r="G2">
-        <v>-5.37</v>
+        <v>-5.73</v>
       </c>
       <c r="H2">
-        <v>14.81</v>
+        <v>14.38</v>
       </c>
       <c r="I2">
-        <v>-3.18</v>
+        <v>-3.08</v>
       </c>
       <c r="J2">
-        <v>-3.3</v>
+        <v>-1.95</v>
       </c>
       <c r="K2">
-        <v>3.26</v>
+        <v>3.89</v>
       </c>
       <c r="L2">
-        <v>-1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="M2">
-        <v>15.1</v>
+        <v>15.01</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>1404.74</v>
+        <v>1395.96</v>
       </c>
       <c r="Q2">
-        <v>1419.2</v>
+        <v>1417.31</v>
       </c>
       <c r="R2">
-        <v>1425.07</v>
+        <v>1424.43</v>
       </c>
       <c r="S2">
-        <v>1356.11</v>
+        <v>1356.22</v>
       </c>
       <c r="T2">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -975,43 +947,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.5</v>
+        <v>37.19</v>
       </c>
       <c r="Z2">
-        <v>-5.01</v>
+        <v>-7.37</v>
       </c>
       <c r="AA2">
-        <v>0.49</v>
+        <v>-1.08</v>
       </c>
       <c r="AB2">
-        <v>-5.5</v>
+        <v>-6.28</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>13.9</v>
+        <v>4.96</v>
       </c>
       <c r="AE2">
         <v>21.4</v>
       </c>
       <c r="AF2">
-        <v>18.55</v>
+        <v>-21.38</v>
       </c>
       <c r="AG2">
-        <v>1453.13</v>
+        <v>1455.66</v>
       </c>
       <c r="AH2">
-        <v>1385.26</v>
+        <v>1378.96</v>
       </c>
       <c r="AI2">
-        <v>1447.65</v>
+        <v>1442.5</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>28.51</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1022,58 +994,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>1465</v>
+        <v>1459.8</v>
       </c>
       <c r="D3">
-        <v>-0.61</v>
+        <v>-0.35</v>
       </c>
       <c r="E3">
         <v>2035.17</v>
       </c>
       <c r="F3">
-        <v>1465</v>
+        <v>1459.8</v>
       </c>
       <c r="G3">
-        <v>-28.02</v>
+        <v>-28.27</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.73</v>
+        <v>-3.32</v>
       </c>
       <c r="J3">
-        <v>-10.4</v>
+        <v>-10.33</v>
       </c>
       <c r="K3">
-        <v>-13.61</v>
+        <v>-15.82</v>
       </c>
       <c r="L3">
-        <v>-19.51</v>
+        <v>-19.88</v>
       </c>
       <c r="M3">
-        <v>-1.48</v>
+        <v>-1.55</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P3">
-        <v>1485.36</v>
+        <v>1475.32</v>
       </c>
       <c r="Q3">
-        <v>1567.01</v>
+        <v>1558.5</v>
       </c>
       <c r="R3">
-        <v>1639.7</v>
+        <v>1633.44</v>
       </c>
       <c r="S3">
-        <v>1795.48</v>
+        <v>1792.82</v>
       </c>
       <c r="T3">
-        <v>-18.41</v>
+        <v>-18.58</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1088,16 +1060,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>19.51</v>
+        <v>18.95</v>
       </c>
       <c r="Z3">
-        <v>-47.54</v>
+        <v>-49.09</v>
       </c>
       <c r="AA3">
-        <v>-38.64</v>
+        <v>-40.73</v>
       </c>
       <c r="AB3">
-        <v>-8.9</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1106,25 +1078,25 @@
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>31.29</v>
+        <v>30.58</v>
       </c>
       <c r="AF3">
-        <v>-65.12</v>
+        <v>-24.25</v>
       </c>
       <c r="AG3">
-        <v>1682.18</v>
+        <v>1679.1</v>
       </c>
       <c r="AH3">
-        <v>1451.83</v>
+        <v>1437.89</v>
       </c>
       <c r="AI3">
-        <v>1561.43</v>
+        <v>1546.08</v>
       </c>
       <c r="AJ3" t="s">
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>56.05</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1135,10 +1107,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>471</v>
+        <v>471.5</v>
       </c>
       <c r="D4">
-        <v>1.84</v>
+        <v>0.11</v>
       </c>
       <c r="E4">
         <v>686.0700000000001</v>
@@ -1147,46 +1119,46 @@
         <v>460.4</v>
       </c>
       <c r="G4">
-        <v>-31.35</v>
+        <v>-31.28</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="I4">
-        <v>-4.86</v>
+        <v>-4.66</v>
       </c>
       <c r="J4">
-        <v>-6.99</v>
+        <v>-7</v>
       </c>
       <c r="K4">
-        <v>0.61</v>
+        <v>-3.01</v>
       </c>
       <c r="L4">
-        <v>-20.32</v>
+        <v>-20.9</v>
       </c>
       <c r="M4">
-        <v>-7.31</v>
+        <v>-7.29</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>473.6</v>
+        <v>468.99</v>
       </c>
       <c r="Q4">
-        <v>498.02</v>
+        <v>496.13</v>
       </c>
       <c r="R4">
-        <v>501.75</v>
+        <v>501.48</v>
       </c>
       <c r="S4">
-        <v>562.1</v>
+        <v>561.41</v>
       </c>
       <c r="T4">
-        <v>-16.21</v>
+        <v>-16.01</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1201,34 +1173,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.17</v>
+        <v>36.53</v>
       </c>
       <c r="Z4">
-        <v>-8.970000000000001</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="AA4">
-        <v>-4.26</v>
+        <v>-5.3</v>
       </c>
       <c r="AB4">
-        <v>-4.71</v>
+        <v>-4.17</v>
       </c>
       <c r="AC4">
-        <v>7.78</v>
+        <v>16</v>
       </c>
       <c r="AD4">
-        <v>2.59</v>
+        <v>7.93</v>
       </c>
       <c r="AE4">
-        <v>13.74</v>
+        <v>13.78</v>
       </c>
       <c r="AF4">
-        <v>74.48999999999999</v>
+        <v>5.06</v>
       </c>
       <c r="AG4">
-        <v>531.51</v>
+        <v>531.1900000000001</v>
       </c>
       <c r="AH4">
-        <v>464.53</v>
+        <v>461.08</v>
       </c>
       <c r="AI4">
         <v>502.26</v>
@@ -1237,7 +1209,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>31.26</v>
+        <v>31.49</v>
       </c>
     </row>
   </sheetData>
@@ -1398,47 +1370,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1446,428 +1383,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>59</v>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-3.3</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.47</v>
+      <c r="D7" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-10.31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-10.4</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.09</v>
+      <c r="D8" s="5">
+        <v>-10.33</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-7.78</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.99</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.79</v>
+      <c r="D9" s="5">
+        <v>-7</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-3.18</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D10" s="5">
+        <v>-3.08</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.73</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-3.32</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.86</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-4.66</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-1.74</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-19.51</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-19.88</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-20.32</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-20.9</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3.26</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3.89</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-13.61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-15.82</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.01</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-5.37</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-28.02</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-28.27</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-31.35</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-31.28</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1384.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1379.3</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1465</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1459.8</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>471</v>
+      </c>
+      <c r="D24" s="5">
+        <v>471.5</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="D25" s="5">
+        <v>37.19</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>19.51</v>
+      </c>
+      <c r="D26" s="5">
+        <v>18.95</v>
+      </c>
+      <c r="E26" s="7">
         <v>-0.5600000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>36.17</v>
+      </c>
+      <c r="D27" s="5">
+        <v>36.53</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>18.55</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-21.38</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-39.93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-4.1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-65.12</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-24.25</v>
+      </c>
+      <c r="E29" s="6">
+        <v>40.87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.86</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-0.98</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-1.3</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-19.34</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-19.51</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-22.23</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-20.32</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="D16" s="6">
-        <v>3.26</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-13.92</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-13.61</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-27.57</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-28.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-32.59</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-31.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1389.1</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1384.5</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1474</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1465</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>462.5</v>
-      </c>
-      <c r="D24" s="6">
-        <v>471</v>
-      </c>
-      <c r="E24" s="8">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>39.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>38.5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>20.47</v>
-      </c>
-      <c r="D26" s="6">
-        <v>19.51</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>29.89</v>
-      </c>
-      <c r="D27" s="6">
-        <v>36.17</v>
-      </c>
-      <c r="E27" s="8">
-        <v>6.28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>63.2</v>
-      </c>
-      <c r="D28" s="6">
-        <v>18.55</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-44.65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>11.44</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-65.12</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-76.56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-26.16</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>74.48999999999999</v>
       </c>
-      <c r="E30" s="8">
-        <v>100.65</v>
+      <c r="D30" s="5">
+        <v>5.06</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-69.43000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1893,60 +1830,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>67</v>
+      <c r="B1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>31.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>30.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-3.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-5</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2048,25 +1985,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.151</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0148</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0731</v>
+      <c r="A2" s="13">
+        <v>0.1501</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0155</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07290000000000001</v>
       </c>
     </row>
   </sheetData>
